--- a/[예제 015] 반도체 공정 DOE 분석 시스템/doe_results/doe_report.xlsx
+++ b/[예제 015] 반도체 공정 DOE 분석 시스템/doe_results/doe_report.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,47 +480,57 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AR_actual</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>N2_actual</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HE_actual</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>C3H6_actual</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>O2_actual</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>NF3_actual</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PRESSURE_actual</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SPACE_actual</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TIME_actual</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>RF_POWER_actual</t>
         </is>
       </c>
     </row>
@@ -556,31 +566,37 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L2" t="n">
         <v>100</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>500</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>100</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>120</v>
+      </c>
+      <c r="U2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -615,31 +631,37 @@
         <v>-1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>200</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>50</v>
-      </c>
-      <c r="O3" t="n">
-        <v>100</v>
       </c>
       <c r="P3" t="n">
         <v>100</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
         <v>5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>10</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -674,31 +696,37 @@
         <v>-1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>500</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>100</v>
       </c>
       <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -733,31 +761,37 @@
         <v>-1</v>
       </c>
       <c r="K5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L5" t="n">
         <v>100</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>50</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>30</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>10</v>
+      </c>
+      <c r="U5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -792,31 +826,37 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>200</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>100</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>10</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>30</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>120</v>
+      </c>
+      <c r="U6" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -851,31 +891,37 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>500</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>100</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
       <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>30</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>120</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="8">
@@ -910,7 +956,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -919,22 +965,28 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>50</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>10</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>120</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="9">
@@ -969,11 +1021,11 @@
         <v>-1</v>
       </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>100</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -981,19 +1033,25 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>100</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>30</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>10</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="10">
@@ -1028,14 +1086,14 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L10" t="n">
         <v>100</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>200</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -1043,16 +1101,22 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>100</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
       <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>120</v>
+      </c>
+      <c r="U10" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1087,17 +1151,17 @@
         <v>-1</v>
       </c>
       <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>100</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>200</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>500</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -1105,13 +1169,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>10</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>10</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="12">
@@ -1146,31 +1216,37 @@
         <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>200</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>500</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>50</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>30</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>10</v>
+      </c>
+      <c r="U12" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1205,7 +1281,7 @@
         <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1223,13 +1299,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>10</v>
+      </c>
+      <c r="U13" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1243,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,19 +1372,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.54285714285714</v>
+        <v>20.28571428571428</v>
       </c>
       <c r="C2" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>26.14285714285714</v>
+        <v>26.28571428571428</v>
       </c>
       <c r="E2" t="n">
-        <v>3.86869178276957</v>
+        <v>2.842548065111375</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003115795456486103</v>
+        <v>0.01747189510991559</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -1315,19 +1397,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.74285714285714</v>
+        <v>15.82857142857143</v>
       </c>
       <c r="C3" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="D3" t="n">
-        <v>24.14285714285714</v>
+        <v>24.42857142857143</v>
       </c>
       <c r="E3" t="n">
-        <v>2.215710132819749</v>
+        <v>1.93339797503578</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05106437188333781</v>
+        <v>0.08197214845378942</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -1336,23 +1418,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.428571428571427</v>
+        <v>13.65714285714286</v>
       </c>
       <c r="C4" t="n">
-        <v>16.57142857142857</v>
+        <v>12.14285714285714</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>25.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5950106929521348</v>
+        <v>-1.593779654130152</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5650566618411568</v>
+        <v>0.1420696783027579</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1361,23 +1443,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.057142857142857</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>17.14285714285714</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4069953552102313</v>
+        <v>-0.4634301275684286</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6925862143025636</v>
+        <v>0.6529784395182398</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -1390,19 +1472,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.371428571428574</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>17.42857142857143</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>19.8</v>
+        <v>20.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3146703726092921</v>
+        <v>-0.4634301275684286</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7594792866342769</v>
+        <v>0.6529784395182398</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1411,23 +1493,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.028571428571428</v>
+        <v>3.828571428571427</v>
       </c>
       <c r="C7" t="n">
-        <v>17.57142857142857</v>
+        <v>15.6</v>
       </c>
       <c r="D7" t="n">
-        <v>19.6</v>
+        <v>19.42857142857143</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2688190817421374</v>
+        <v>0.4021968028256938</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7935334733551261</v>
+        <v>0.6960014905225089</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1436,23 +1518,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7142857142857153</v>
+        <v>3.028571428571428</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>16.57142857142857</v>
       </c>
       <c r="D8" t="n">
-        <v>18.71428571428572</v>
+        <v>19.6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09435641951204977</v>
+        <v>-0.3171969855349738</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9266898994831709</v>
+        <v>0.7576175613373876</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1461,23 +1543,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3714285714285737</v>
+        <v>2.114285714285714</v>
       </c>
       <c r="C9" t="n">
-        <v>18.2</v>
+        <v>16.6</v>
       </c>
       <c r="D9" t="n">
-        <v>18.57142857142857</v>
+        <v>18.71428571428572</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04904941015478599</v>
+        <v>0.2208705288748774</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9618457548384991</v>
+        <v>0.8296376416232165</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1486,25 +1568,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3142857142857167</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>18.28571428571428</v>
+        <v>17</v>
       </c>
       <c r="D10" t="n">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04150192912996011</v>
+        <v>-0.2088779965721784</v>
       </c>
       <c r="F10" t="n">
-        <v>0.967712698173402</v>
+        <v>0.838736893770953</v>
       </c>
       <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.7428571428571438</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.14285714285714</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.07743776750423977</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9398028056970339</v>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1519,7 +1626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1567,236 +1674,236 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N2*HE</t>
+          <t>PRESSURE*RF_POWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.25</v>
+        <v>23.125</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="F2" t="n">
-        <v>9.666666666666666</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>11.33333333333333</v>
+        <v>13</v>
       </c>
       <c r="H2" t="n">
-        <v>23.5</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AR*O2</t>
+          <t>N2*HE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10.70833333333333</v>
+        <v>20.95833333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>17.5</v>
+        <v>34</v>
       </c>
       <c r="F3" t="n">
-        <v>18.66666666666667</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
-        <v>5.666666666666667</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>28.25</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O2*TIME</t>
+          <t>PRESSURE*SPACE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9.916666666666666</v>
+        <v>-17.25</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>4.666666666666667</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H4" t="n">
-        <v>26.5</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N2*SPACE</t>
+          <t>C3H6*TIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>9.666666666666666</v>
+        <v>15.79166666666666</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F5" t="n">
-        <v>14.33333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="G5" t="n">
-        <v>13.33333333333333</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>22</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AR*HE</t>
+          <t>N2*TIME</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9.333333333333332</v>
+        <v>-15.41666666666667</v>
       </c>
       <c r="E6" t="n">
-        <v>26</v>
+        <v>7.5</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>15.33333333333333</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C3H6*TIME</t>
+          <t>AR*O2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9.333333333333332</v>
+        <v>13.625</v>
       </c>
       <c r="E7" t="n">
-        <v>29.5</v>
+        <v>17.5</v>
       </c>
       <c r="F7" t="n">
-        <v>15.33333333333333</v>
+        <v>17.33333333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="H7" t="n">
-        <v>18.5</v>
+        <v>29.75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NF3*SPACE</t>
+          <t>AR*C3H6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.708333333333334</v>
+        <v>-12.875</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="G8" t="n">
-        <v>21.33333333333333</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>29.75</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N2*TIME</t>
+          <t>AR*TIME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1805,51 +1912,51 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-8.416666666666666</v>
+        <v>-11.625</v>
       </c>
       <c r="E9" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="n">
-        <v>21.33333333333333</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="G9" t="n">
-        <v>24</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="H9" t="n">
-        <v>14</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PRESSURE*TIME</t>
+          <t>NF3*SPACE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.25</v>
+        <v>11.54166666666667</v>
       </c>
       <c r="E10" t="n">
-        <v>27.5</v>
+        <v>11.5</v>
       </c>
       <c r="F10" t="n">
-        <v>14.66666666666667</v>
+        <v>2.333333333333333</v>
       </c>
       <c r="G10" t="n">
-        <v>15.33333333333333</v>
+        <v>18.33333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>19</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="11">
@@ -1869,57 +1976,57 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.166666666666666</v>
+        <v>11.29166666666667</v>
       </c>
       <c r="E11" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>19.66666666666667</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>27.5</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HE*PRESSURE</t>
+          <t>AR*HE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>HE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PRESSURE</t>
-        </is>
-      </c>
       <c r="D12" t="n">
-        <v>-7.875</v>
+        <v>11.29166666666666</v>
       </c>
       <c r="E12" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
-        <v>22.33333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="G12" t="n">
-        <v>22.66666666666667</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>13.75</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AR*NF3</t>
+          <t>AR*N2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1929,130 +2036,130 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7.708333333333334</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="E13" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>4.333333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>29.25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPACE*TIME</t>
+          <t>O2*PRESSURE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-6.833333333333334</v>
+        <v>-9.875</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>23.66666666666667</v>
+        <v>31.33333333333333</v>
       </c>
       <c r="H14" t="n">
-        <v>15</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N2*C3H6</t>
+          <t>O2*RF_POWER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-6.75</v>
+        <v>-9.250000000000002</v>
       </c>
       <c r="E15" t="n">
-        <v>16.5</v>
+        <v>10</v>
       </c>
       <c r="F15" t="n">
-        <v>20</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>24</v>
+        <v>36.33333333333334</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HE*C3H6</t>
+          <t>NF3*PRESSURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6.666666666666667</v>
+        <v>-8.916666666666664</v>
       </c>
       <c r="E16" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>14.66666666666667</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HE*TIME</t>
+          <t>PRESSURE*TIME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2061,217 +2168,217 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-6.333333333333332</v>
+        <v>8.791666666666668</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>28.5</v>
       </c>
       <c r="F17" t="n">
-        <v>21.33333333333333</v>
+        <v>15</v>
       </c>
       <c r="G17" t="n">
-        <v>22.33333333333333</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>14</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PRESSURE*SPACE</t>
+          <t>TIME*RF_POWER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-6.25</v>
+        <v>8.708333333333334</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>15.5</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AR*SPACE</t>
+          <t>NF3*TIME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-6.041666666666666</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="E19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>21.33333333333333</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" t="n">
-        <v>16.75</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N2*PRESSURE</t>
+          <t>HE*TIME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.625</v>
+        <v>-7.5</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="H20" t="n">
-        <v>19.25</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AR*C3H6</t>
+          <t>N2*PRESSURE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-5.458333333333334</v>
+        <v>7.499999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>24.5</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="G21" t="n">
-        <v>23.66666666666667</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>14.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HE*SPACE</t>
+          <t>AR*RF_POWER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.375000000000001</v>
+        <v>6.958333333333334</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>30.5</v>
       </c>
       <c r="F22" t="n">
-        <v>17.33333333333333</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>14.66666666666667</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="H22" t="n">
-        <v>19.75</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AR*TIME</t>
+          <t>C3H6*NF3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-5</v>
+        <v>-6.874999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>16.5</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>19.33333333333333</v>
+        <v>30.33333333333333</v>
       </c>
       <c r="G23" t="n">
-        <v>22.66666666666667</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="H23" t="n">
-        <v>15.5</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C3H6*NF3</t>
+          <t>C3H6*PRESSURE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,349 +2388,349 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-4.875000000000001</v>
+        <v>6.833333333333334</v>
       </c>
       <c r="E24" t="n">
-        <v>6.5</v>
+        <v>26.5</v>
       </c>
       <c r="F24" t="n">
-        <v>30.66666666666667</v>
+        <v>14</v>
       </c>
       <c r="G24" t="n">
-        <v>8.333333333333334</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>22.75</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NF3*TIME</t>
+          <t>HE*SPACE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.791666666666668</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="E25" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>4.333333333333333</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>25.33333333333333</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>26.75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AR*N2</t>
+          <t>NF3*RF_POWER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4.416666666666666</v>
+        <v>-6.166666666666665</v>
       </c>
       <c r="E26" t="n">
-        <v>21.5</v>
+        <v>9.5</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>16.66666666666667</v>
+        <v>36.66666666666666</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>O2*PRESSURE</t>
+          <t>N2*C3H6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-4.374999999999999</v>
+        <v>-6.041666666666668</v>
       </c>
       <c r="E27" t="n">
-        <v>8.5</v>
+        <v>13.5</v>
       </c>
       <c r="F27" t="n">
-        <v>11.66666666666667</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>27.33333333333333</v>
+        <v>22.66666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>21.75</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>C3H6*PRESSURE</t>
+          <t>N2*RF_POWER</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.25</v>
+        <v>-6.041666666666666</v>
       </c>
       <c r="E28" t="n">
-        <v>25.5</v>
+        <v>20.5</v>
       </c>
       <c r="F28" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AR*PRESSURE</t>
+          <t>SPACE*RF_POWER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.375000000000001</v>
+        <v>-6</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="F29" t="n">
-        <v>15.66666666666667</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>18.33333333333333</v>
+        <v>30</v>
       </c>
       <c r="H29" t="n">
-        <v>18.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C3H6*SPACE</t>
+          <t>SPACE*TIME</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3.333333333333333</v>
+        <v>-5.458333333333334</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="F30" t="n">
-        <v>19.66666666666667</v>
+        <v>17</v>
       </c>
       <c r="G30" t="n">
-        <v>14.66666666666667</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>C3H6*O2</t>
+          <t>O2*NF3</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-3.291666666666667</v>
+        <v>5.458333333333333</v>
       </c>
       <c r="E31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="G31" t="n">
-        <v>10.33333333333333</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>21.25</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NF3*PRESSURE</t>
+          <t>HE*O2</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-3.125000000000001</v>
+        <v>-4.916666666666667</v>
       </c>
       <c r="E32" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F32" t="n">
-        <v>8.333333333333334</v>
+        <v>29</v>
       </c>
       <c r="G32" t="n">
-        <v>28.66666666666667</v>
+        <v>9.333333333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>24.25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>HE*NF3</t>
+          <t>N2*SPACE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-2.833333333333334</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="E33" t="n">
-        <v>6.5</v>
+        <v>17.5</v>
       </c>
       <c r="F33" t="n">
-        <v>28.33333333333333</v>
+        <v>16</v>
       </c>
       <c r="G33" t="n">
-        <v>8.333333333333334</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="H33" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>N2*O2</t>
+          <t>AR*SPACE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-2.624999999999999</v>
+        <v>-4.375</v>
       </c>
       <c r="E34" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>25.33333333333333</v>
+        <v>21</v>
       </c>
       <c r="G34" t="n">
-        <v>11.66666666666667</v>
+        <v>18</v>
       </c>
       <c r="H34" t="n">
-        <v>23.25</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>N2*NF3</t>
+          <t>N2*O2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2633,61 +2740,61 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-2.083333333333332</v>
+        <v>-4.333333333333333</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>8.666666666666666</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H35" t="n">
-        <v>25.5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O2*NF3</t>
+          <t>C3H6*RF_POWER</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.375000000000002</v>
+        <v>-3.875000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="F36" t="n">
-        <v>17.33333333333333</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>12.66666666666667</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="H36" t="n">
-        <v>32.75</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HE*O2</t>
+          <t>HE*PRESSURE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2697,23 +2804,311 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>PRESSURE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-3.708333333333332</v>
+      </c>
+      <c r="E37" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F37" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="G37" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="H37" t="n">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AR*PRESSURE</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PRESSURE</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F38" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19</v>
+      </c>
+      <c r="H38" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>C3H6*O2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>C3H6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>-1.250000000000001</v>
-      </c>
-      <c r="E37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>25.66666666666667</v>
-      </c>
-      <c r="G37" t="n">
-        <v>10.33333333333333</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="D39" t="n">
+        <v>-2.875000000000001</v>
+      </c>
+      <c r="E39" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F39" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9.333333333333334</v>
+      </c>
+      <c r="H39" t="n">
+        <v>22.75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>O2*TIME</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="E40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.666666666666667</v>
+      </c>
+      <c r="G40" t="n">
+        <v>25</v>
+      </c>
+      <c r="H40" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HE*RF_POWER</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="E41" t="n">
+        <v>30</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14</v>
+      </c>
+      <c r="G41" t="n">
         <v>23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10.75</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>C3H6*SPACE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>C3H6</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-1.749999999999999</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="F42" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="G42" t="n">
+        <v>15.66666666666667</v>
+      </c>
+      <c r="H42" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HE*NF3</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1.708333333333332</v>
+      </c>
+      <c r="E43" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>27.66666666666667</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="H43" t="n">
+        <v>25.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>N2*NF3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F44" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="G44" t="n">
+        <v>7.666666666666667</v>
+      </c>
+      <c r="H44" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HE*C3H6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>C3H6</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>-0.9583333333333339</v>
+      </c>
+      <c r="E45" t="n">
+        <v>21</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="H45" t="n">
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AR*NF3</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4166666666666679</v>
+      </c>
+      <c r="E46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F46" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.333333333333333</v>
+      </c>
+      <c r="H46" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2727,7 +3122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2749,7 +3144,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8682230049155112</v>
+        <v>0.3062036664378853</v>
       </c>
     </row>
     <row r="3">
@@ -2759,7 +3154,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.47118839331564</v>
+        <v>13.30926445989503</v>
       </c>
     </row>
     <row r="4">
@@ -2769,7 +3164,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>183.1137153954285</v>
+        <v>95.18235500681067</v>
       </c>
     </row>
     <row r="5">
@@ -2779,7 +3174,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.7865259739381</v>
+        <v>70.75324088573412</v>
       </c>
     </row>
     <row r="6">
@@ -2789,7 +3184,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.70972880926129</v>
+        <v>5.456686464620145</v>
       </c>
     </row>
     <row r="7">
@@ -2799,7 +3194,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.92100878651955</v>
+        <v>69.77643002454771</v>
       </c>
     </row>
     <row r="8">
@@ -2809,7 +3204,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25.16504234873651</v>
+        <v>15.79630748380885</v>
       </c>
     </row>
     <row r="9">
@@ -2819,7 +3214,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.439145903970914</v>
+        <v>2.398730754112969</v>
       </c>
     </row>
     <row r="10">
@@ -2829,7 +3224,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12.7828603242349</v>
+        <v>19.80958867138343</v>
       </c>
     </row>
     <row r="11">
@@ -2839,37 +3234,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88.74562973311247</v>
+        <v>14.80196739651596</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PRED_THICKNESS</t>
+          <t>FACTOR_RF_POWER</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5000.00000193908</v>
+        <v>162.6913693848299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PRED_UNIFORMITY</t>
+          <t>PRED_THICKNESS</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.379268106377918</v>
+        <v>5000.000000239116</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>PRED_UNIFORMITY</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>6.629347876004163</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>PRED_PARTICLE</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0</v>
+      <c r="B15" t="n">
+        <v>18.34887404284403</v>
       </c>
     </row>
   </sheetData>
@@ -2883,7 +3288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2939,60 +3344,70 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>AR_actual</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>N2_actual</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>HE_actual</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>C3H6_actual</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>O2_actual</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>NF3_actual</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>PRESSURE_actual</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SPACE_actual</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>TIME_actual</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>RF_POWER_actual</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>THICKNESS</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>UNIFORMITY</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>PARTICLE</t>
         </is>
@@ -3030,40 +3445,46 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L2" t="n">
         <v>100</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>500</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>50</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>100</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
         <v>5</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>120</v>
       </c>
-      <c r="T2" t="n">
-        <v>4112.768231346889</v>
-      </c>
       <c r="U2" t="n">
-        <v>4.758536212755835</v>
+        <v>100</v>
       </c>
       <c r="V2" t="n">
-        <v>21</v>
+        <v>1448.875399810519</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6.123445502621537</v>
+      </c>
+      <c r="X2" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -3098,39 +3519,45 @@
         <v>-1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>200</v>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>50</v>
-      </c>
-      <c r="O3" t="n">
-        <v>100</v>
       </c>
       <c r="P3" t="n">
         <v>100</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
         <v>5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>10</v>
       </c>
-      <c r="T3" t="n">
-        <v>380.930507894461</v>
-      </c>
       <c r="U3" t="n">
-        <v>5.413814072285478</v>
+        <v>2000</v>
       </c>
       <c r="V3" t="n">
+        <v>536.0801465202061</v>
+      </c>
+      <c r="W3" t="n">
+        <v>6.924530716427356</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3166,39 +3593,45 @@
         <v>-1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>500</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>100</v>
       </c>
       <c r="Q4" t="n">
+        <v>100</v>
+      </c>
+      <c r="R4" t="n">
         <v>10</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>10</v>
       </c>
-      <c r="T4" t="n">
-        <v>697.4168775369814</v>
-      </c>
       <c r="U4" t="n">
-        <v>5.241096223909701</v>
+        <v>100</v>
       </c>
       <c r="V4" t="n">
+        <v>221.0714381654037</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6.655728390540196</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3234,40 +3667,46 @@
         <v>-1</v>
       </c>
       <c r="K5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L5" t="n">
         <v>100</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>50</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
       <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>10</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>30</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>10</v>
       </c>
-      <c r="T5" t="n">
-        <v>971.3875033170399</v>
-      </c>
       <c r="U5" t="n">
-        <v>5.351428601197602</v>
+        <v>100</v>
       </c>
       <c r="V5" t="n">
-        <v>13</v>
+        <v>373.3097058158371</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6.654321121709261</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -3302,40 +3741,46 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>200</v>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
         <v>100</v>
       </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>10</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>30</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>120</v>
       </c>
-      <c r="T6" t="n">
-        <v>7066.570166166227</v>
-      </c>
       <c r="U6" t="n">
-        <v>5.044448266542272</v>
+        <v>100</v>
       </c>
       <c r="V6" t="n">
-        <v>17</v>
+        <v>2477.048153306304</v>
+      </c>
+      <c r="W6" t="n">
+        <v>6.270353085550942</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="7">
@@ -3370,40 +3815,46 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>500</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>100</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
       <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
         <v>30</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>120</v>
       </c>
-      <c r="T7" t="n">
-        <v>1391.30596001325</v>
-      </c>
       <c r="U7" t="n">
-        <v>4.967742674978741</v>
+        <v>2000</v>
       </c>
       <c r="V7" t="n">
-        <v>13</v>
+        <v>1896.120281609519</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6.38298563887901</v>
+      </c>
+      <c r="X7" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -3438,7 +3889,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -3447,31 +3898,37 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>50</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>10</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>120</v>
       </c>
-      <c r="T8" t="n">
-        <v>16167.41278222422</v>
-      </c>
       <c r="U8" t="n">
-        <v>5.401582452394218</v>
+        <v>2000</v>
       </c>
       <c r="V8" t="n">
-        <v>38</v>
+        <v>22072.00783097594</v>
+      </c>
+      <c r="W8" t="n">
+        <v>6.840431926612766</v>
+      </c>
+      <c r="X8" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -3506,11 +3963,11 @@
         <v>-1</v>
       </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>100</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
@@ -3518,28 +3975,34 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>100</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
         <v>30</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>10</v>
       </c>
-      <c r="T9" t="n">
-        <v>147.8273502337526</v>
-      </c>
       <c r="U9" t="n">
-        <v>5.186471585549932</v>
+        <v>2000</v>
       </c>
       <c r="V9" t="n">
-        <v>14</v>
+        <v>185.446792446499</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6.715590806035896</v>
+      </c>
+      <c r="X9" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -3574,14 +4037,14 @@
         <v>1</v>
       </c>
       <c r="K10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L10" t="n">
         <v>100</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>200</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -3589,25 +4052,31 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>100</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1</v>
-      </c>
       <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>120</v>
       </c>
-      <c r="T10" t="n">
-        <v>2451.841821776539</v>
-      </c>
       <c r="U10" t="n">
-        <v>5.469158940038809</v>
+        <v>100</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>895.0591975927554</v>
+      </c>
+      <c r="W10" t="n">
+        <v>6.802548929552403</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3642,17 +4111,17 @@
         <v>-1</v>
       </c>
       <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>100</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>200</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>500</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
@@ -3660,22 +4129,28 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>10</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>10</v>
       </c>
-      <c r="T11" t="n">
-        <v>789.6864484476999</v>
-      </c>
       <c r="U11" t="n">
-        <v>4.933550856898417</v>
+        <v>2000</v>
       </c>
       <c r="V11" t="n">
-        <v>31</v>
+        <v>1092.039492531125</v>
+      </c>
+      <c r="W11" t="n">
+        <v>6.373113174193207</v>
+      </c>
+      <c r="X11" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -3710,40 +4185,46 @@
         <v>-1</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>200</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>500</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>50</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>30</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>10</v>
       </c>
-      <c r="T12" t="n">
-        <v>249.4088454100007</v>
-      </c>
       <c r="U12" t="n">
-        <v>5.550365900737998</v>
+        <v>100</v>
       </c>
       <c r="V12" t="n">
-        <v>33</v>
+        <v>80.44033973309952</v>
+      </c>
+      <c r="W12" t="n">
+        <v>7.024555973067538</v>
+      </c>
+      <c r="X12" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -3778,7 +4259,7 @@
         <v>-1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -3796,22 +4277,28 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
         <v>5</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>10</v>
       </c>
-      <c r="T13" t="n">
-        <v>182.0917984850659</v>
-      </c>
       <c r="U13" t="n">
-        <v>5.634479299820916</v>
+        <v>100</v>
       </c>
       <c r="V13" t="n">
-        <v>29</v>
+        <v>75.60079958908081</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7.005656434653595</v>
+      </c>
+      <c r="X13" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -3825,7 +4312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3862,16 +4349,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10840937.13856762</v>
+        <v>25889014.26854655</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.189923997026696</v>
+        <v>0.6801475747169696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3892416071385561</v>
+        <v>0.5609692924473513</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -3884,16 +4371,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3591312.704908143</v>
+        <v>20006646.36922295</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3941900145508713</v>
+        <v>0.5256079611644094</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5942360106094091</v>
+        <v>0.6006481049742656</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -3906,16 +4393,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15932556.09404006</v>
+        <v>21778181.50031037</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.74879077223181</v>
+        <v>0.5721491430895512</v>
       </c>
       <c r="E4" t="n">
-        <v>0.316995876929049</v>
+        <v>0.5877326860692146</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -3928,16 +4415,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18569966.88270213</v>
+        <v>42710978.77783172</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.038278511837019</v>
+        <v>1.122088632969845</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2895498193967931</v>
+        <v>0.4816767834711236</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -3950,16 +4437,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1130654.465664474</v>
+        <v>21096306.67264152</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.124103005472949</v>
+        <v>0.554235154341707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7582851331261792</v>
+        <v>0.5925936997739669</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -3972,16 +4459,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22616081.20746111</v>
+        <v>26312123.46354362</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.482388506038158</v>
+        <v>0.6912633588033239</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2558163435403836</v>
+        <v>0.5584344743260968</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -3994,16 +4481,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41856710.72002093</v>
+        <v>56438281.56254169</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.594280354709094</v>
+        <v>1.482727767375566</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1653103216077989</v>
+        <v>0.4377128517674951</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -4016,16 +4503,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6378076.910966911</v>
+        <v>20354318.34444431</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7000710984884645</v>
+        <v>0.5347418836958346</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4908057693730375</v>
+        <v>0.5980385649695298</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -4038,16 +4525,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91899512.91677304</v>
+        <v>80269465.4234421</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>10.08708327859389</v>
+        <v>2.108812705855365</v>
       </c>
       <c r="E10" t="n">
-        <v>0.08647161546320498</v>
+        <v>0.383912882245681</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -4056,18 +4543,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>52641523.9041604</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.382980612603686</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4486200168709873</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>18221226.17185005</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="b">
+      <c r="B12" t="n">
+        <v>38063819.13413389</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4082,7 +4591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4129,22 +4638,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5749.587030687569</v>
+        <v>5391.538070544543</v>
       </c>
       <c r="C2" t="n">
-        <v>488.3927616178573</v>
+        <v>366.2841021144644</v>
       </c>
       <c r="D2" t="n">
-        <v>6237.979792305426</v>
+        <v>5757.822172659007</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.603313004041148</v>
+        <v>-1.591298696851304</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0263413257381648</v>
+        <v>0.1426266217875517</v>
       </c>
       <c r="G2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -4154,19 +4663,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3864.755539087012</v>
+        <v>4516.006330258681</v>
       </c>
       <c r="C3" t="n">
-        <v>1273.739216451422</v>
+        <v>731.0889939002398</v>
       </c>
       <c r="D3" t="n">
-        <v>5138.494755538434</v>
+        <v>5247.095324158921</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.494211682758638</v>
+        <v>-1.285213880822037</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1659884699216997</v>
+        <v>0.2276850554620266</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -4175,23 +4684,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2923.675697651468</v>
+        <v>4360.423903957657</v>
       </c>
       <c r="C4" t="n">
-        <v>1178.576534107654</v>
+        <v>795.9150048589999</v>
       </c>
       <c r="D4" t="n">
-        <v>4102.252231759122</v>
+        <v>5156.338908816657</v>
       </c>
       <c r="E4" t="n">
-        <v>1.079976474549939</v>
+        <v>-1.234054222389421</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3055108879775533</v>
+        <v>0.2453979340714954</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -4204,19 +4713,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2558.275799372877</v>
+        <v>3924.658948108164</v>
       </c>
       <c r="C5" t="n">
-        <v>1818.105774665645</v>
+        <v>977.4837364629551</v>
       </c>
       <c r="D5" t="n">
-        <v>4376.381574038523</v>
+        <v>4902.142684571119</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9323458029166244</v>
+        <v>-1.095007726571729</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3731209567628554</v>
+        <v>0.2991852613342065</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -4225,23 +4734,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2461.60586032008</v>
+        <v>3134.451675829622</v>
       </c>
       <c r="C6" t="n">
-        <v>1448.117272550964</v>
+        <v>784.3281539407442</v>
       </c>
       <c r="D6" t="n">
-        <v>3909.723132871044</v>
+        <v>3918.779829770367</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8942379222054686</v>
+        <v>0.8561435740723891</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3922086891100598</v>
+        <v>0.4119633318538051</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -4254,19 +4763,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2038.888720079931</v>
+        <v>3109.39230948916</v>
       </c>
       <c r="C7" t="n">
-        <v>1694.702271024384</v>
+        <v>798.9461176393469</v>
       </c>
       <c r="D7" t="n">
-        <v>3733.590991104315</v>
+        <v>3908.338427128507</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7315494372214743</v>
+        <v>0.8488035924262539</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4812349395595988</v>
+        <v>0.415846884546948</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -4275,23 +4784,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1575.006958930783</v>
+        <v>2854.369556236727</v>
       </c>
       <c r="C8" t="n">
-        <v>1965.299965028054</v>
+        <v>947.709390369933</v>
       </c>
       <c r="D8" t="n">
-        <v>3540.306923958837</v>
+        <v>3802.07894660666</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5591085165853074</v>
+        <v>0.7748090790299632</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5883892052365056</v>
+        <v>0.4563821354671483</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -4300,23 +4809,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1193.771085369186</v>
+        <v>2809.806706499836</v>
       </c>
       <c r="C9" t="n">
-        <v>2187.687557938985</v>
+        <v>973.7043860497863</v>
       </c>
       <c r="D9" t="n">
-        <v>3381.458643308171</v>
+        <v>3783.511092549622</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4209837063627515</v>
+        <v>0.7620043633250929</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6826716631149961</v>
+        <v>0.4636505660864907</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -4325,25 +4834,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>690.7738247463117</v>
+        <v>2760.488989015609</v>
       </c>
       <c r="C10" t="n">
-        <v>2481.102626635662</v>
+        <v>1002.473054582252</v>
       </c>
       <c r="D10" t="n">
-        <v>3171.876451381974</v>
+        <v>3762.962043597861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.242178298276313</v>
+        <v>0.7478745335429455</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8135363561372075</v>
+        <v>0.4717571703255128</v>
       </c>
       <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2737.071140979416</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1016.133465936698</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3753.204606916114</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.7411800447295981</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4756293109347069</v>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4358,7 +4892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4406,108 +4940,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N2*C3H6</t>
+          <t>C3H6*RF_POWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-4800.029405603356</v>
+        <v>5264.580774297962</v>
       </c>
       <c r="E2" t="n">
-        <v>315.1696766522308</v>
+        <v>11304.04398874807</v>
       </c>
       <c r="F2" t="n">
-        <v>3436.032812130155</v>
+        <v>634.2084817864851</v>
       </c>
       <c r="G2" t="n">
-        <v>7083.85617229605</v>
+        <v>1057.868855529047</v>
       </c>
       <c r="H2" t="n">
-        <v>604.6604965672623</v>
+        <v>917.194897163386</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AR*PRESSURE</t>
+          <t>PRESSURE*TIME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-4391.570577964237</v>
+        <v>5259.214086602477</v>
       </c>
       <c r="E3" t="n">
-        <v>880.5369758823699</v>
+        <v>12274.52799214112</v>
       </c>
       <c r="F3" t="n">
-        <v>2237.479134452393</v>
+        <v>562.1402121707885</v>
       </c>
       <c r="G3" t="n">
-        <v>7977.133275309144</v>
+        <v>1413.351626337598</v>
       </c>
       <c r="H3" t="n">
-        <v>550.9342779506943</v>
+        <v>219.3920195722214</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HE*PRESSURE</t>
+          <t>PRESSURE*RF_POWER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-4226.029981784707</v>
+        <v>5155.329378323486</v>
       </c>
       <c r="E4" t="n">
-        <v>743.5516629923407</v>
+        <v>11582.02366175353</v>
       </c>
       <c r="F4" t="n">
-        <v>1917.82767892338</v>
+        <v>1023.809765762515</v>
       </c>
       <c r="G4" t="n">
-        <v>8068.456817235829</v>
+        <v>872.5490735254079</v>
       </c>
       <c r="H4" t="n">
-        <v>790.6728695974546</v>
+        <v>624.9939341813636</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PRESSURE*TIME</t>
+          <t>C3H6*TIME</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4516,25 +5050,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4192.793576110789</v>
+        <v>5033.980985608508</v>
       </c>
       <c r="E5" t="n">
-        <v>11616.99147419523</v>
+        <v>11760.44161539323</v>
       </c>
       <c r="F5" t="n">
-        <v>819.4969431005737</v>
+        <v>329.9433973563809</v>
       </c>
       <c r="G5" t="n">
-        <v>2651.972004378893</v>
+        <v>1756.075877502859</v>
       </c>
       <c r="H5" t="n">
-        <v>240.06462550582</v>
+        <v>393.5396306830271</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C3H6*SPACE</t>
+          <t>C3H6*PRESSURE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4544,189 +5078,189 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-4057.473794183921</v>
+        <v>5016.931939758233</v>
       </c>
       <c r="E6" t="n">
-        <v>610.3981743635203</v>
+        <v>11222.65876839589</v>
       </c>
       <c r="F6" t="n">
-        <v>6887.037173821857</v>
+        <v>688.465295354608</v>
       </c>
       <c r="G6" t="n">
-        <v>2868.567825471077</v>
+        <v>1263.386361334277</v>
       </c>
       <c r="H6" t="n">
-        <v>1030.259236561571</v>
+        <v>763.0567678094635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NF3*TIME</t>
+          <t>TIME*RF_POWER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3767.500593978125</v>
+        <v>4980.076616524723</v>
       </c>
       <c r="E7" t="n">
-        <v>1921.573890894894</v>
+        <v>11984.06405629273</v>
       </c>
       <c r="F7" t="n">
-        <v>683.2449629161607</v>
+        <v>1606.994250236526</v>
       </c>
       <c r="G7" t="n">
-        <v>9115.583726579112</v>
+        <v>604.5221438326099</v>
       </c>
       <c r="H7" t="n">
-        <v>342.2536106441297</v>
+        <v>187.6055708258553</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NF3*PRESSURE</t>
+          <t>O2*RF_POWER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-3704.244824355765</v>
+        <v>-4509.427442650112</v>
       </c>
       <c r="E8" t="n">
-        <v>834.4021904270106</v>
+        <v>360.7634694833525</v>
       </c>
       <c r="F8" t="n">
-        <v>1408.026096561416</v>
+        <v>1382.331663760742</v>
       </c>
       <c r="G8" t="n">
-        <v>8007.88979894605</v>
+        <v>8353.389201705526</v>
       </c>
       <c r="H8" t="n">
-        <v>1173.024056368927</v>
+        <v>356.1025106826932</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N2*SPACE</t>
+          <t>NF3*PRESSURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3451.792698812745</v>
+        <v>-4455.668481313263</v>
       </c>
       <c r="E9" t="n">
-        <v>3657.989505788114</v>
+        <v>297.1905719906204</v>
       </c>
       <c r="F9" t="n">
-        <v>1207.4862593729</v>
+        <v>1109.086541907493</v>
       </c>
       <c r="G9" t="n">
-        <v>836.840271188014</v>
+        <v>8547.031825604454</v>
       </c>
       <c r="H9" t="n">
-        <v>5289.92242239829</v>
+        <v>447.5908328947995</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AR*HE</t>
+          <t>C3H6*SPACE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3215.374600413634</v>
+        <v>-4370.354223406134</v>
       </c>
       <c r="E10" t="n">
-        <v>2451.227339897294</v>
+        <v>226.8750227744683</v>
       </c>
       <c r="F10" t="n">
-        <v>1190.352225109111</v>
+        <v>8018.987792435554</v>
       </c>
       <c r="G10" t="n">
-        <v>779.3772276534105</v>
+        <v>1519.538409120774</v>
       </c>
       <c r="H10" t="n">
-        <v>5949.251313692494</v>
+        <v>570.9427319695911</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C3H6*TIME</t>
+          <t>N2*C3H6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>C3H6</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
       <c r="D11" t="n">
-        <v>3211.932261967796</v>
+        <v>-4274.979927799107</v>
       </c>
       <c r="E11" t="n">
-        <v>10140.09050678556</v>
+        <v>308.2602431266528</v>
       </c>
       <c r="F11" t="n">
-        <v>533.9089522071671</v>
+        <v>1488.048947810061</v>
       </c>
       <c r="G11" t="n">
-        <v>3636.572649318672</v>
+        <v>7964.730978867431</v>
       </c>
       <c r="H11" t="n">
-        <v>454.2556186758749</v>
+        <v>594.5598279526256</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HE*TIME</t>
+          <t>HE*PRESSURE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4736,125 +5270,125 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2984.091297428954</v>
+        <v>-4184.832518849169</v>
       </c>
       <c r="E12" t="n">
-        <v>2752.037095680069</v>
+        <v>656.5554653482642</v>
       </c>
       <c r="F12" t="n">
-        <v>578.8373904648939</v>
+        <v>1141.812007051046</v>
       </c>
       <c r="G12" t="n">
-        <v>8561.941590055663</v>
+        <v>8307.455230032692</v>
       </c>
       <c r="H12" t="n">
-        <v>420.5592899825798</v>
+        <v>423.0467340371354</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O2*SPACE</t>
+          <t>AR*TIME</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2951.942164546916</v>
+        <v>-3982.529302929077</v>
       </c>
       <c r="E13" t="n">
-        <v>3607.19875819999</v>
+        <v>1171.967298701637</v>
       </c>
       <c r="F13" t="n">
-        <v>1730.371872259444</v>
+        <v>550.2653302644869</v>
       </c>
       <c r="G13" t="n">
-        <v>870.7007695800967</v>
+        <v>8815.058755297252</v>
       </c>
       <c r="H13" t="n">
-        <v>4897.758212733383</v>
+        <v>228.2981810019475</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C3H6*NF3</t>
+          <t>N2*RF_POWER</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-2817.007613165179</v>
+        <v>-3929.133354925248</v>
       </c>
       <c r="E14" t="n">
-        <v>676.1590056057504</v>
+        <v>814.0598195256653</v>
       </c>
       <c r="F14" t="n">
-        <v>6843.196619660372</v>
+        <v>1150.849230210719</v>
       </c>
       <c r="G14" t="n">
-        <v>1513.521553108923</v>
+        <v>8051.191635010651</v>
       </c>
       <c r="H14" t="n">
-        <v>2046.543940833186</v>
+        <v>529.71433584521</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>N2*O2</t>
+          <t>AR*RF_POWER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2792.741661561476</v>
+        <v>-3860.76709779382</v>
       </c>
       <c r="E15" t="n">
-        <v>3723.750337030344</v>
+        <v>638.7431424888118</v>
       </c>
       <c r="F15" t="n">
-        <v>1163.645705211413</v>
+        <v>905.748101073037</v>
       </c>
       <c r="G15" t="n">
-        <v>1652.670819705874</v>
+        <v>8168.069419701887</v>
       </c>
       <c r="H15" t="n">
-        <v>4678.049511009895</v>
+        <v>713.540182698472</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AR*TIME</t>
+          <t>AR*PRESSURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -4864,29 +5398,29 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-2592.481518120362</v>
+        <v>-3860.050639864674</v>
       </c>
       <c r="E16" t="n">
-        <v>3282.305026561714</v>
+        <v>732.6745991734808</v>
       </c>
       <c r="F16" t="n">
-        <v>636.3004339994974</v>
+        <v>843.1271299499243</v>
       </c>
       <c r="G16" t="n">
-        <v>8208.429636134568</v>
+        <v>8256.709140815881</v>
       </c>
       <c r="H16" t="n">
-        <v>377.4620073316272</v>
+        <v>647.0603918629763</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C3H6*PRESSURE</t>
+          <t>C3H6*NF3</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -4896,125 +5430,125 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2590.203258231848</v>
+        <v>-3729.481380163069</v>
       </c>
       <c r="E17" t="n">
-        <v>8569.400142770632</v>
+        <v>454.6949261680216</v>
       </c>
       <c r="F17" t="n">
-        <v>1581.03586155045</v>
+        <v>7867.107856839853</v>
       </c>
       <c r="G17" t="n">
-        <v>2851.224497383636</v>
+        <v>1004.083639122559</v>
       </c>
       <c r="H17" t="n">
-        <v>1043.266732627152</v>
+        <v>957.5338094682521</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AR*NF3</t>
+          <t>NF3*TIME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2560.670217730246</v>
+        <v>-3644.41298126099</v>
       </c>
       <c r="E18" t="n">
-        <v>1711.614662546789</v>
+        <v>1395.589739601137</v>
       </c>
       <c r="F18" t="n">
-        <v>1683.42734334278</v>
+        <v>376.820430167149</v>
       </c>
       <c r="G18" t="n">
-        <v>823.2177818148972</v>
+        <v>8665.97712803092</v>
       </c>
       <c r="H18" t="n">
-        <v>5916.37089807138</v>
+        <v>358.381856074951</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C3H6*O2</t>
+          <t>SPACE*RF_POWER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-2491.380149080715</v>
+        <v>-3588.019988571693</v>
       </c>
       <c r="E19" t="n">
-        <v>2246.849369620675</v>
+        <v>1040.783537028009</v>
       </c>
       <c r="F19" t="n">
-        <v>5796.069710317089</v>
+        <v>976.9327329517469</v>
       </c>
       <c r="G19" t="n">
-        <v>2637.271464645654</v>
+        <v>7900.042490009088</v>
       </c>
       <c r="H19" t="n">
-        <v>1203.731507180639</v>
+        <v>660.1517087894397</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HE*O2</t>
+          <t>N2*TIME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2003.183135752095</v>
+        <v>-3570.9718188032</v>
       </c>
       <c r="E20" t="n">
-        <v>2405.092554441935</v>
+        <v>1686.05367544953</v>
       </c>
       <c r="F20" t="n">
-        <v>810.1337512903168</v>
+        <v>569.5199929281433</v>
       </c>
       <c r="G20" t="n">
-        <v>2531.776008098147</v>
+        <v>8472.334504131992</v>
       </c>
       <c r="H20" t="n">
-        <v>4943.183476450718</v>
+        <v>213.8571840042052</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HE*NF3</t>
+          <t>HE*C3H6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5024,34 +5558,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1974.997911827445</v>
+        <v>-3528.631513183604</v>
       </c>
       <c r="E21" t="n">
-        <v>1044.361418775115</v>
+        <v>764.657869771809</v>
       </c>
       <c r="F21" t="n">
-        <v>1717.287841734863</v>
+        <v>1069.743737435349</v>
       </c>
       <c r="G21" t="n">
-        <v>1268.05327766268</v>
+        <v>7660.465894437327</v>
       </c>
       <c r="H21" t="n">
-        <v>5890.975524277318</v>
+        <v>908.2887357336598</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPACE*TIME</t>
+          <t>HE*TIME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5060,121 +5594,121 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-1646.039686794345</v>
+        <v>-3490.390807815975</v>
       </c>
       <c r="E22" t="n">
-        <v>4228.938063089739</v>
+        <v>1672.497840710019</v>
       </c>
       <c r="F22" t="n">
-        <v>456.2078996535977</v>
+        <v>464.5170901432093</v>
       </c>
       <c r="G22" t="n">
-        <v>7577.340945115884</v>
+        <v>8481.371727291666</v>
       </c>
       <c r="H22" t="n">
-        <v>512.531408091052</v>
+        <v>292.6093610929058</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>N2*NF3</t>
+          <t>C3H6*O2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1423.492969222125</v>
+        <v>-3243.796018742523</v>
       </c>
       <c r="E23" t="n">
-        <v>1416.3861648355</v>
+        <v>992.4777731653624</v>
       </c>
       <c r="F23" t="n">
-        <v>2701.888486674643</v>
+        <v>7508.585958841625</v>
       </c>
       <c r="G23" t="n">
-        <v>1020.03678028909</v>
+        <v>961.1887946394022</v>
       </c>
       <c r="H23" t="n">
-        <v>5152.525040572484</v>
+        <v>989.7049428306199</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NF3*SPACE</t>
+          <t>O2*PRESSURE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1414.835678559231</v>
+        <v>-3241.694086166537</v>
       </c>
       <c r="E24" t="n">
-        <v>1181.346731665145</v>
+        <v>1349.059795735854</v>
       </c>
       <c r="F24" t="n">
-        <v>1176.729735735994</v>
+        <v>723.4674462590746</v>
       </c>
       <c r="G24" t="n">
-        <v>2487.93545393666</v>
+        <v>7845.785676440966</v>
       </c>
       <c r="H24" t="n">
-        <v>5312.98981512597</v>
+        <v>736.8051546311136</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>O2*PRESSURE</t>
+          <t>PRESSURE*SPACE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-1286.340989774269</v>
+        <v>-3175.812954857325</v>
       </c>
       <c r="E25" t="n">
-        <v>3881.993521851604</v>
+        <v>1425.178929561071</v>
       </c>
       <c r="F25" t="n">
-        <v>1547.175363158367</v>
+        <v>7795.039587224154</v>
       </c>
       <c r="G25" t="n">
-        <v>5976.162244662988</v>
+        <v>720.6691379297057</v>
       </c>
       <c r="H25" t="n">
-        <v>1068.662106421214</v>
+        <v>738.9038858781403</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AR*O2</t>
+          <t>AR*HE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5184,29 +5718,29 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1254.28743113857</v>
+        <v>3171.746213490499</v>
       </c>
       <c r="E26" t="n">
-        <v>2130.297790790321</v>
+        <v>1270.457446170822</v>
       </c>
       <c r="F26" t="n">
-        <v>1404.305257847093</v>
+        <v>484.6052319516972</v>
       </c>
       <c r="G26" t="n">
-        <v>2714.972517199223</v>
+        <v>732.5440198360074</v>
       </c>
       <c r="H26" t="n">
-        <v>4497.554846533136</v>
+        <v>6290.184232597881</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N2*TIME</t>
+          <t>N2*O2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5216,61 +5750,61 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-1219.142024373791</v>
+        <v>3151.589792158857</v>
       </c>
       <c r="E27" t="n">
-        <v>4759.205993971383</v>
+        <v>1506.564149913255</v>
       </c>
       <c r="F27" t="n">
-        <v>473.3419339173872</v>
+        <v>689.1796766189931</v>
       </c>
       <c r="G27" t="n">
-        <v>7223.828991194787</v>
+        <v>618.4645434741404</v>
       </c>
       <c r="H27" t="n">
-        <v>499.6808823932099</v>
+        <v>6104.259654497593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HE*C3H6</t>
+          <t>O2*TIME</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-1078.104351967022</v>
+        <v>-3116.809600730538</v>
       </c>
       <c r="E28" t="n">
-        <v>2181.088538378445</v>
+        <v>1962.961776558411</v>
       </c>
       <c r="F28" t="n">
-        <v>959.4697619993103</v>
+        <v>314.1994590440363</v>
       </c>
       <c r="G28" t="n">
-        <v>5839.910264478574</v>
+        <v>8287.729103392738</v>
       </c>
       <c r="H28" t="n">
-        <v>2462.082784165396</v>
+        <v>405.3475844172855</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AR*N2</t>
+          <t>AR*C3H6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5280,98 +5814,98 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>960.3450607771049</v>
+        <v>-3104.235939476227</v>
       </c>
       <c r="E29" t="n">
-        <v>1620.764135112119</v>
+        <v>911.0925528131778</v>
       </c>
       <c r="F29" t="n">
-        <v>1743.99436163256</v>
+        <v>724.1818275234597</v>
       </c>
       <c r="G29" t="n">
-        <v>2565.63650649023</v>
+        <v>7562.842772409748</v>
       </c>
       <c r="H29" t="n">
-        <v>4609.55685456488</v>
+        <v>1167.460168167577</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AR*C3H6</t>
+          <t>NF3*RF_POWER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-926.3059253899399</v>
+        <v>-3021.526716000619</v>
       </c>
       <c r="E30" t="n">
-        <v>2542.077867331964</v>
+        <v>1216.100214064862</v>
       </c>
       <c r="F30" t="n">
-        <v>1129.78520681933</v>
+        <v>496.4801138579987</v>
       </c>
       <c r="G30" t="n">
-        <v>5599.250711842895</v>
+        <v>7783.164705317853</v>
       </c>
       <c r="H30" t="n">
-        <v>2334.346200550381</v>
+        <v>1020.491173109751</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N2*PRESSURE</t>
+          <t>O2*SPACE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-793.0864018631892</v>
+        <v>2923.145932915215</v>
       </c>
       <c r="E31" t="n">
-        <v>3928.128307306964</v>
+        <v>1331.247472876401</v>
       </c>
       <c r="F31" t="n">
-        <v>1027.393725027</v>
+        <v>735.3423281653762</v>
       </c>
       <c r="G31" t="n">
-        <v>5945.405721026081</v>
+        <v>783.2901090528184</v>
       </c>
       <c r="H31" t="n">
-        <v>1458.498335019739</v>
+        <v>6033.676830172224</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HE*SPACE</t>
+          <t>NF3*SPACE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5380,121 +5914,121 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>510.3538856452506</v>
+        <v>2920.898592592293</v>
       </c>
       <c r="E32" t="n">
-        <v>820.3574027116251</v>
+        <v>1134.714993712678</v>
       </c>
       <c r="F32" t="n">
-        <v>1866.623852443857</v>
+        <v>550.7369274261217</v>
       </c>
       <c r="G32" t="n">
-        <v>2728.59500657234</v>
+        <v>914.3117618286341</v>
       </c>
       <c r="H32" t="n">
-        <v>4795.569227595072</v>
+        <v>6172.130880726665</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>O2*TIME</t>
+          <t>HE*NF3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-470.5494594441134</v>
+        <v>2892.926829982868</v>
       </c>
       <c r="E33" t="n">
-        <v>5589.669198756557</v>
+        <v>1058.595859887461</v>
       </c>
       <c r="F33" t="n">
-        <v>408.7249118883983</v>
+        <v>873.7850773582476</v>
       </c>
       <c r="G33" t="n">
-        <v>6670.186854671338</v>
+        <v>601.4830166429329</v>
       </c>
       <c r="H33" t="n">
-        <v>548.1436489149515</v>
+        <v>6202.525894079455</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PRESSURE*SPACE</t>
+          <t>HE*RF_POWER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-340.0662483356321</v>
+        <v>-2865.986482368786</v>
       </c>
       <c r="E34" t="n">
-        <v>4018.978834741633</v>
+        <v>1494.079887070322</v>
       </c>
       <c r="F34" t="n">
-        <v>5884.838702736301</v>
+        <v>583.462392569674</v>
       </c>
       <c r="G34" t="n">
-        <v>596.1807185523343</v>
+        <v>7597.844923314214</v>
       </c>
       <c r="H34" t="n">
-        <v>1781.908089875738</v>
+        <v>955.2544640759944</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>O2*NF3</t>
+          <t>SPACE*TIME</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-247.1216747968811</v>
+        <v>-2841.965451066092</v>
       </c>
       <c r="E35" t="n">
-        <v>539.1736927157211</v>
+        <v>2186.584217457911</v>
       </c>
       <c r="F35" t="n">
-        <v>3775.721915915623</v>
+        <v>213.0656126651453</v>
       </c>
       <c r="G35" t="n">
-        <v>1604.845095035609</v>
+        <v>8138.647476126404</v>
       </c>
       <c r="H35" t="n">
-        <v>4347.149968641748</v>
+        <v>481.1979692014538</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N2*HE</t>
+          <t>N2*SPACE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5504,55 +6038,343 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-240.1085080421219</v>
+        <v>2786.890620741478</v>
       </c>
       <c r="E36" t="n">
-        <v>519.5476469288503</v>
+        <v>1278.744246519702</v>
       </c>
       <c r="F36" t="n">
-        <v>3299.780831945742</v>
+        <v>841.0596122146953</v>
       </c>
       <c r="G36" t="n">
-        <v>2067.163689632373</v>
+        <v>818.2922599572848</v>
       </c>
       <c r="H36" t="n">
-        <v>4367.179858565021</v>
+        <v>5954.388867135235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>N2*PRESSURE</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PRESSURE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-2686.634122492564</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1784.543822918714</v>
+      </c>
+      <c r="F37" t="n">
+        <v>503.8598946153537</v>
+      </c>
+      <c r="G37" t="n">
+        <v>7555.462991652393</v>
+      </c>
+      <c r="H37" t="n">
+        <v>901.5108183639043</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AR*N2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2679.674626718052</v>
+      </c>
+      <c r="E38" t="n">
+        <v>993.5493450619399</v>
+      </c>
+      <c r="F38" t="n">
+        <v>669.2106326909516</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1031.18954651987</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6066.200087584985</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>AR*NF3</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2508.623774455489</v>
+      </c>
+      <c r="E39" t="n">
+        <v>634.1844517042962</v>
+      </c>
+      <c r="F39" t="n">
+        <v>908.7872282627141</v>
+      </c>
+      <c r="G39" t="n">
+        <v>884.4239554317095</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6176.274280901105</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>AR*O2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2491.667015564104</v>
+      </c>
+      <c r="E40" t="n">
+        <v>817.1610961285088</v>
+      </c>
+      <c r="F40" t="n">
+        <v>786.8027986465722</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1078.066579330638</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6031.042312976909</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>HE*SPACE</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2475.185155157787</v>
+      </c>
+      <c r="E41" t="n">
+        <v>988.2803106713092</v>
+      </c>
+      <c r="F41" t="n">
+        <v>920.6621101690156</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1011.934883856213</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5894.686993669495</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>N2*NF3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2307.187953687447</v>
+      </c>
+      <c r="E42" t="n">
+        <v>715.5696720564807</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1216.509328523509</v>
+      </c>
+      <c r="G42" t="n">
+        <v>830.1671418635865</v>
+      </c>
+      <c r="H42" t="n">
+        <v>5945.482705705509</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HE*O2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2299.954700216223</v>
+      </c>
+      <c r="E43" t="n">
+        <v>834.9734189879612</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1022.866704624581</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1066.191697424336</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5853.994383493403</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>O2*NF3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1891.655698928152</v>
+      </c>
+      <c r="E44" t="n">
+        <v>378.5757923428049</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1370.45678185444</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1054.82972833937</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5830.02211570731</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>N2*HE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1885.706496335358</v>
+      </c>
+      <c r="E45" t="n">
+        <v>586.2399161321121</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1302.729165806422</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1188.689039861814</v>
+      </c>
+      <c r="H45" t="n">
+        <v>5676.591282206839</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>AR*SPACE</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>SPACE</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>-218.6450363714778</v>
-      </c>
-      <c r="E37" t="n">
-        <v>559.6074267753962</v>
-      </c>
-      <c r="F37" t="n">
-        <v>2451.432167190376</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2902.428323863159</v>
-      </c>
-      <c r="H37" t="n">
-        <v>4356.962991535183</v>
+      <c r="D46" t="n">
+        <v>1687.853674041359</v>
+      </c>
+      <c r="E46" t="n">
+        <v>279.3782491311681</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1145.3246966448</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1484.536258216307</v>
+      </c>
+      <c r="H46" t="n">
+        <v>5726.190053812657</v>
       </c>
     </row>
   </sheetData>
@@ -5566,7 +6388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5603,16 +6425,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1211193545916562</v>
+        <v>0.1438474045313101</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.595254003336472</v>
+        <v>0.8458489817241469</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3338835907128696</v>
+        <v>0.5266137744103445</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -5625,16 +6447,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003108370222004393</v>
+        <v>0.001030111921815774</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04094011281039293</v>
+        <v>0.00605724603074172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8583686526001819</v>
+        <v>0.950552635741479</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -5647,16 +6469,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2386735356217877</v>
+        <v>0.1946001992992975</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.143551371081663</v>
+        <v>1.144284674144393</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2182304689497541</v>
+        <v>0.4785653617484088</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -5669,16 +6491,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.008511539756825221</v>
+        <v>0.0168083887256069</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1121048565475791</v>
+        <v>0.09883639217754296</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7696148532674386</v>
+        <v>0.8060862426571186</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -5691,16 +6513,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.143701121694569</v>
+        <v>0.1351185139674339</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.892676776887275</v>
+        <v>0.7945215127364872</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3027090082813428</v>
+        <v>0.5365276235521461</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -5713,16 +6535,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.005452310675407155</v>
+        <v>0.002140600012155101</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07181197804183671</v>
+        <v>0.01258711859598402</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8138241801828262</v>
+        <v>0.9288735757524834</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -5735,16 +6557,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03735258581548857</v>
+        <v>0.09516804657112059</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4919681272907984</v>
+        <v>0.5596054760052153</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5556785885046291</v>
+        <v>0.5911224384945964</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -5757,16 +6579,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01452029927975856</v>
+        <v>0.02711536962036463</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.191245780938749</v>
+        <v>0.1594433202127544</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7045728634630379</v>
+        <v>0.7581444307349298</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -5779,16 +6601,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1449494044028645</v>
+        <v>0.2709090469483889</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.909117815517457</v>
+        <v>1.59299461987357</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3011612385148968</v>
+        <v>0.4265554462436378</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -5797,18 +6619,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.003326463003783124</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01956020933197005</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.911537550824345</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.151849616848897</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="b">
+      <c r="B12" t="n">
+        <v>0.1700627507266095</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -5823,7 +6667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5866,23 +6710,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2670820858337501</v>
+        <v>0.2808322143033894</v>
       </c>
       <c r="C2" t="n">
-        <v>5.090258373856139</v>
+        <v>6.483953016643332</v>
       </c>
       <c r="D2" t="n">
-        <v>5.357340459689889</v>
+        <v>6.764785230946721</v>
       </c>
       <c r="E2" t="n">
-        <v>1.853440079568726</v>
+        <v>1.756801880552288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.09351612016552359</v>
+        <v>0.1094692066293407</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -5891,23 +6735,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2018786535723169</v>
+        <v>0.2328104099314476</v>
       </c>
       <c r="C3" t="n">
-        <v>5.128293709341975</v>
+        <v>6.511965735860298</v>
       </c>
       <c r="D3" t="n">
-        <v>5.330172362914292</v>
+        <v>6.744776145791746</v>
       </c>
       <c r="E3" t="n">
-        <v>1.307958376883676</v>
+        <v>1.390812182750917</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2201546784078889</v>
+        <v>0.1944529181689583</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -5916,23 +6760,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2008851172294559</v>
+        <v>0.1953735454248822</v>
       </c>
       <c r="C4" t="n">
-        <v>5.128873272208644</v>
+        <v>6.53380390682246</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3297583894381</v>
+        <v>6.729177452247343</v>
       </c>
       <c r="E4" t="n">
-        <v>1.300429589588376</v>
+        <v>1.135145378227623</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2226242181357201</v>
+        <v>0.2827896054528098</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -5941,23 +6785,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1821034593789275</v>
+        <v>0.1883007567173554</v>
       </c>
       <c r="C5" t="n">
-        <v>5.139829239288119</v>
+        <v>6.537929700235185</v>
       </c>
       <c r="D5" t="n">
-        <v>5.321932698667046</v>
+        <v>6.72623045695254</v>
       </c>
       <c r="E5" t="n">
-        <v>1.161470947068448</v>
+        <v>1.089074640610028</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2724233419149499</v>
+        <v>0.301669943748706</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -5970,19 +6814,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08851710354980202</v>
+        <v>0.1525410318840583</v>
       </c>
       <c r="C6" t="n">
-        <v>5.194421280188442</v>
+        <v>6.558789539721275</v>
       </c>
       <c r="D6" t="n">
-        <v>5.282938383738244</v>
+        <v>6.711330571605333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5375565487088391</v>
+        <v>0.8647977193358158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6026394449746866</v>
+        <v>0.4074164889582377</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -5995,19 +6839,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08415289819725746</v>
+        <v>0.1126032681726565</v>
       </c>
       <c r="C7" t="n">
-        <v>5.210992549676969</v>
+        <v>6.600853779915036</v>
       </c>
       <c r="D7" t="n">
-        <v>5.295145447874226</v>
+        <v>6.713457048087692</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5103444388369447</v>
+        <v>-0.627785524769519</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6208852907233016</v>
+        <v>0.5442131905158705</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -6016,23 +6860,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07301459181069614</v>
+        <v>0.06550368560876496</v>
       </c>
       <c r="C8" t="n">
-        <v>5.21563351067137</v>
+        <v>6.609561325048529</v>
       </c>
       <c r="D8" t="n">
-        <v>5.288648102482066</v>
+        <v>6.675065010657294</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4413777081945162</v>
+        <v>0.3605259741164036</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6683301110536425</v>
+        <v>0.7259528091264967</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -6041,23 +6885,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06207660007103044</v>
+        <v>0.06214483045943364</v>
       </c>
       <c r="C9" t="n">
-        <v>5.220191007229564</v>
+        <v>6.621878128962211</v>
       </c>
       <c r="D9" t="n">
-        <v>5.282267607300595</v>
+        <v>6.684022959421645</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3742478294213754</v>
+        <v>-0.3418172516413256</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7160333943255652</v>
+        <v>0.7395629387559612</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -6066,25 +6910,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.04451117392774417</v>
+        <v>0.05356897275082328</v>
       </c>
       <c r="C10" t="n">
-        <v>5.220091405801309</v>
+        <v>6.625451403007466</v>
       </c>
       <c r="D10" t="n">
-        <v>5.264602579729053</v>
+        <v>6.679020375758289</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2674408425525635</v>
+        <v>-0.2942058773362928</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7945646045266234</v>
+        <v>0.7746169195545453</v>
       </c>
       <c r="G10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0007566100982785429</v>
+      </c>
+      <c r="C11" t="n">
+        <v>6.647330452429647</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.648087062527925</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.004137509991066784</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9967801304529638</v>
+      </c>
+      <c r="G11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -6099,7 +6968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6147,65 +7016,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N2*PRESSURE</t>
+          <t>O2*RF_POWER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.3416708625956182</v>
+        <v>0.4049060682557188</v>
       </c>
       <c r="E2" t="n">
-        <v>4.988999561720345</v>
+        <v>6.820060761231625</v>
       </c>
       <c r="F2" t="n">
-        <v>5.477779637687429</v>
+        <v>6.349842326237559</v>
       </c>
       <c r="G2" t="n">
-        <v>5.331369092500508</v>
+        <v>6.532176913228327</v>
       </c>
       <c r="H2" t="n">
-        <v>5.136807443276356</v>
+        <v>6.871770614745699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AR*NF3</t>
+          <t>N2*PRESSURE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3254711041830105</v>
+        <v>-0.3776931469417946</v>
       </c>
       <c r="E3" t="n">
-        <v>5.410293770618205</v>
+        <v>6.321733129872075</v>
       </c>
       <c r="F3" t="n">
-        <v>4.959519551734728</v>
+        <v>6.917211873015765</v>
       </c>
       <c r="G3" t="n">
-        <v>5.207550990391307</v>
+        <v>6.716827146287407</v>
       </c>
       <c r="H3" t="n">
-        <v>5.407718979873851</v>
+        <v>6.556919595547509</v>
       </c>
     </row>
     <row r="4">
@@ -6225,313 +7094,313 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.2834845316876522</v>
+        <v>0.3331060571172286</v>
       </c>
       <c r="E4" t="n">
-        <v>5.259054287858369</v>
+        <v>6.703770805973274</v>
       </c>
       <c r="F4" t="n">
-        <v>4.977727764521318</v>
+        <v>6.384095689118314</v>
       </c>
       <c r="G4" t="n">
-        <v>5.194116151096602</v>
+        <v>6.546755004432033</v>
       </c>
       <c r="H4" t="n">
-        <v>5.479758691134855</v>
+        <v>6.893292001811529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C3H6*SPACE</t>
+          <t>N2*C3H6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>C3H6</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>SPACE</t>
-        </is>
-      </c>
       <c r="D5" t="n">
-        <v>0.2564684131496349</v>
+        <v>0.3215645410972914</v>
       </c>
       <c r="E5" t="n">
-        <v>5.450897250967801</v>
+        <v>6.974543344747447</v>
       </c>
       <c r="F5" t="n">
-        <v>5.191310912478511</v>
+        <v>6.482005063098851</v>
       </c>
       <c r="G5" t="n">
-        <v>5.066220842356981</v>
+        <v>6.539399516981188</v>
       </c>
       <c r="H5" t="n">
-        <v>5.319571330166961</v>
+        <v>6.689990317527174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AR*SPACE</t>
+          <t>O2*NF3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.2252127440794949</v>
+        <v>0.308993617916268</v>
       </c>
       <c r="E6" t="n">
-        <v>5.268950093373768</v>
+        <v>6.790129553483776</v>
       </c>
       <c r="F6" t="n">
-        <v>5.053748669897687</v>
+        <v>6.369796464736125</v>
       </c>
       <c r="G6" t="n">
-        <v>5.18751894741967</v>
+        <v>6.613285230046891</v>
       </c>
       <c r="H6" t="n">
-        <v>5.422743012102579</v>
+        <v>6.810939377131777</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O2*NF3</t>
+          <t>AR*C3H6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.2240938409363737</v>
+        <v>-0.296346487862527</v>
       </c>
       <c r="E7" t="n">
-        <v>5.32745514809759</v>
+        <v>6.388883312165399</v>
       </c>
       <c r="F7" t="n">
-        <v>4.996485354949346</v>
+        <v>6.630417636593836</v>
       </c>
       <c r="G7" t="n">
-        <v>5.262776738738384</v>
+        <v>6.929839538702553</v>
       </c>
       <c r="H7" t="n">
-        <v>5.379994627462888</v>
+        <v>6.578680887405936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRESSURE*TIME</t>
+          <t>AR*SPACE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.214396785403562</v>
+        <v>0.2746043648214225</v>
       </c>
       <c r="E8" t="n">
-        <v>5.223015359468246</v>
+        <v>6.684955963872579</v>
       </c>
       <c r="F8" t="n">
-        <v>5.175358560668574</v>
+        <v>6.433035868789049</v>
       </c>
       <c r="G8" t="n">
-        <v>5.065145942591129</v>
+        <v>6.559298232499163</v>
       </c>
       <c r="H8" t="n">
-        <v>5.446282714598581</v>
+        <v>6.856586867058478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N2*C3H6</t>
+          <t>O2*TIME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.209984494650421</v>
+        <v>-0.2396472496785345</v>
       </c>
       <c r="E9" t="n">
-        <v>5.482089986511738</v>
+        <v>6.19689929408624</v>
       </c>
       <c r="F9" t="n">
-        <v>5.1490526878265</v>
+        <v>6.765283304334482</v>
       </c>
       <c r="G9" t="n">
-        <v>5.170515755449219</v>
+        <v>6.675322165014727</v>
       </c>
       <c r="H9" t="n">
-        <v>5.257447446064822</v>
+        <v>6.7644116759059</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C3H6*PRESSURE</t>
+          <t>PRESSURE*TIME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1885157370915547</v>
+        <v>0.2377975347313726</v>
       </c>
       <c r="E10" t="n">
-        <v>5.37650552679591</v>
+        <v>6.555392506081854</v>
       </c>
       <c r="F10" t="n">
-        <v>5.24090539525977</v>
+        <v>6.561054228814221</v>
       </c>
       <c r="G10" t="n">
-        <v>5.07303178245013</v>
+        <v>6.436326690350984</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3144631250971</v>
+        <v>6.917583482546096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AR*C3H6</t>
+          <t>C3H6*RF_POWER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.1873619563393292</v>
+        <v>0.2373578130460978</v>
       </c>
       <c r="E11" t="n">
-        <v>5.054982406976719</v>
+        <v>6.882481321520061</v>
       </c>
       <c r="F11" t="n">
-        <v>5.196393794162386</v>
+        <v>6.600774199132779</v>
       </c>
       <c r="G11" t="n">
-        <v>5.455254141805899</v>
+        <v>6.49056320636937</v>
       </c>
       <c r="H11" t="n">
-        <v>5.221941616312908</v>
+        <v>6.683571710074284</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AR*HE</t>
+          <t>C3H6*SPACE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.184565042274873</v>
+        <v>0.2314605271237071</v>
       </c>
       <c r="E12" t="n">
-        <v>4.846043534827126</v>
+        <v>6.839438547388399</v>
       </c>
       <c r="F12" t="n">
-        <v>5.335686375595448</v>
+        <v>6.629469381887219</v>
       </c>
       <c r="G12" t="n">
-        <v>5.253068266542146</v>
+        <v>6.456309843488616</v>
       </c>
       <c r="H12" t="n">
-        <v>5.373581022760722</v>
+        <v>6.70926173223485</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N2*HE</t>
+          <t>AR*NF3</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1685917000276311</v>
+        <v>0.2276098188514877</v>
       </c>
       <c r="E13" t="n">
-        <v>5.241958378818207</v>
+        <v>6.728435025630832</v>
       </c>
       <c r="F13" t="n">
-        <v>5.309140426288853</v>
+        <v>6.40404982761688</v>
       </c>
       <c r="G13" t="n">
-        <v>4.989125037214759</v>
+        <v>6.654414915282186</v>
       </c>
       <c r="H13" t="n">
-        <v>5.393490484740667</v>
+        <v>6.78524935497121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N2*NF3</t>
+          <t>N2*HE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6541,215 +7410,215 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1619381928520629</v>
+        <v>0.2248186123463856</v>
       </c>
       <c r="E14" t="n">
-        <v>5.441486506162144</v>
+        <v>6.698834573630373</v>
       </c>
       <c r="F14" t="n">
-        <v>5.176121674726229</v>
+        <v>6.665810910510234</v>
       </c>
       <c r="G14" t="n">
-        <v>5.186755833362015</v>
+        <v>6.387386510680248</v>
       </c>
       <c r="H14" t="n">
-        <v>5.245267387630226</v>
+        <v>6.80400007225288</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NF3*SPACE</t>
+          <t>N2*NF3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>NF3</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>SPACE</t>
-        </is>
-      </c>
       <c r="D15" t="n">
-        <v>-0.1467477430662725</v>
+        <v>0.2072342645787213</v>
       </c>
       <c r="E15" t="n">
-        <v>5.159585638088171</v>
+        <v>6.863539822989879</v>
       </c>
       <c r="F15" t="n">
-        <v>5.37468974541133</v>
+        <v>6.556007410937229</v>
       </c>
       <c r="G15" t="n">
-        <v>5.260428584276734</v>
+        <v>6.564345050376155</v>
       </c>
       <c r="H15" t="n">
-        <v>5.182037205467347</v>
+        <v>6.671281167480948</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O2*TIME</t>
+          <t>AR*HE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.1455034560364195</v>
+        <v>-0.2016939536881153</v>
       </c>
       <c r="E16" t="n">
-        <v>4.901492239649054</v>
+        <v>6.248279338407372</v>
       </c>
       <c r="F16" t="n">
-        <v>5.28046062724837</v>
+        <v>6.724153619099186</v>
       </c>
       <c r="G16" t="n">
-        <v>5.279494689137256</v>
+        <v>6.687756667495581</v>
       </c>
       <c r="H16" t="n">
-        <v>5.367456164663734</v>
+        <v>6.760243040811165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HE*TIME</t>
+          <t>TIME*RF_POWER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.1435231899631839</v>
+        <v>0.1884567623057114</v>
       </c>
       <c r="E17" t="n">
-        <v>4.863139443867288</v>
+        <v>6.611708782745888</v>
       </c>
       <c r="F17" t="n">
-        <v>5.241670993848705</v>
+        <v>6.398782505908294</v>
       </c>
       <c r="G17" t="n">
-        <v>5.305063219658433</v>
+        <v>6.671078232218819</v>
       </c>
       <c r="H17" t="n">
-        <v>5.396548389713482</v>
+        <v>6.835065479992648</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AR*TIME</t>
+          <t>HE*RF_POWER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.1393558190327258</v>
+        <v>-0.1834125695162188</v>
       </c>
       <c r="E18" t="n">
-        <v>5.113847576397323</v>
+        <v>6.378049406536109</v>
       </c>
       <c r="F18" t="n">
-        <v>5.157150347881984</v>
+        <v>6.601243288743091</v>
       </c>
       <c r="G18" t="n">
-        <v>5.13792446463841</v>
+        <v>6.826851149692005</v>
       </c>
       <c r="H18" t="n">
-        <v>5.459938874188524</v>
+        <v>6.68321989286655</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C3H6*TIME</t>
+          <t>NF3*SPACE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.1350136639035986</v>
+        <v>-0.1800604136218498</v>
       </c>
       <c r="E19" t="n">
-        <v>5.080059332575027</v>
+        <v>6.518653380294135</v>
       </c>
       <c r="F19" t="n">
-        <v>5.438536191407025</v>
+        <v>6.794269345506652</v>
       </c>
       <c r="G19" t="n">
-        <v>5.160449960519941</v>
+        <v>6.670166621551459</v>
       </c>
       <c r="H19" t="n">
-        <v>5.248899491544742</v>
+        <v>6.585661759520276</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N2*TIME</t>
+          <t>C3H6*PRESSURE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.134154237113258</v>
+        <v>0.1750815144871565</v>
       </c>
       <c r="E20" t="n">
-        <v>5.256803603290541</v>
+        <v>6.747376524161013</v>
       </c>
       <c r="F20" t="n">
-        <v>5.299243609973964</v>
+        <v>6.69084406403881</v>
       </c>
       <c r="G20" t="n">
-        <v>5.042620446709599</v>
+        <v>6.433064883428115</v>
       </c>
       <c r="H20" t="n">
-        <v>5.353368927619538</v>
+        <v>6.726695452280225</v>
       </c>
     </row>
     <row r="21">
@@ -6769,62 +7638,62 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.1303419901178322</v>
+        <v>-0.1602691060156172</v>
       </c>
       <c r="E21" t="n">
-        <v>5.006095470760506</v>
+        <v>6.326669362214976</v>
       </c>
       <c r="F21" t="n">
-        <v>5.362755362495178</v>
+        <v>6.798155966937565</v>
       </c>
       <c r="G21" t="n">
-        <v>5.209759201729621</v>
+        <v>6.588808786262234</v>
       </c>
       <c r="H21" t="n">
-        <v>5.305735113228629</v>
+        <v>6.739757178953589</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C3H6*O2</t>
+          <t>AR*TIME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.1271947956611807</v>
+        <v>0.1433415885493905</v>
       </c>
       <c r="E22" t="n">
-        <v>5.086175142520657</v>
+        <v>6.46299721608697</v>
       </c>
       <c r="F22" t="n">
-        <v>5.434458984776605</v>
+        <v>6.581008367312788</v>
       </c>
       <c r="G22" t="n">
-        <v>5.157338692000635</v>
+        <v>6.497923550347572</v>
       </c>
       <c r="H22" t="n">
-        <v>5.251232942934221</v>
+        <v>6.902617878672171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>O2*PRESSURE</t>
+          <t>HE*PRESSURE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6833,126 +7702,126 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.09987384437980396</v>
+        <v>0.1389023772768314</v>
       </c>
       <c r="E23" t="n">
-        <v>5.142772245225986</v>
+        <v>6.514420782366702</v>
       </c>
       <c r="F23" t="n">
-        <v>5.119607290197082</v>
+        <v>6.510329038189361</v>
       </c>
       <c r="G23" t="n">
-        <v>5.228853970163413</v>
+        <v>6.58836871129099</v>
       </c>
       <c r="H23" t="n">
-        <v>5.405436703894116</v>
+        <v>6.862081721667312</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N2*O2</t>
+          <t>HE*TIME</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.09410642660742408</v>
+        <v>-0.122001743024442</v>
       </c>
       <c r="E24" t="n">
-        <v>5.229131169413876</v>
+        <v>6.253215570750273</v>
       </c>
       <c r="F24" t="n">
-        <v>5.317691899225075</v>
+        <v>6.684465845933647</v>
       </c>
       <c r="G24" t="n">
-        <v>5.062034674071822</v>
+        <v>6.637777980572037</v>
       </c>
       <c r="H24" t="n">
-        <v>5.338808257097869</v>
+        <v>6.825024769706527</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NF3*PRESSURE</t>
+          <t>C3H6*O2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.08431328727858833</v>
+        <v>-0.1109648069974329</v>
       </c>
       <c r="E25" t="n">
-        <v>5.296262412553652</v>
+        <v>6.523988109524446</v>
       </c>
       <c r="F25" t="n">
-        <v>5.283571895767676</v>
+        <v>6.839769673796521</v>
       </c>
       <c r="G25" t="n">
-        <v>5.12652719194497</v>
+        <v>6.547224094042345</v>
       </c>
       <c r="H25" t="n">
-        <v>5.28246324971617</v>
+        <v>6.641076044319554</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AR*PRESSURE</t>
+          <t>NF3*TIME</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.08349616113676861</v>
+        <v>0.1081130666912897</v>
       </c>
       <c r="E26" t="n">
-        <v>5.14248972904801</v>
+        <v>6.592767284215706</v>
       </c>
       <c r="F26" t="n">
-        <v>5.138055579448192</v>
+        <v>6.744860076225604</v>
       </c>
       <c r="G26" t="n">
-        <v>5.229042314282064</v>
+        <v>6.411410171595082</v>
       </c>
       <c r="H26" t="n">
-        <v>5.391600486955784</v>
+        <v>6.779729096987559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>HE*PRESSURE</t>
+          <t>AR*PRESSURE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -6961,30 +7830,30 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.07763490597947742</v>
+        <v>0.1060582292017647</v>
       </c>
       <c r="E27" t="n">
-        <v>5.087323540404059</v>
+        <v>6.513717147951234</v>
       </c>
       <c r="F27" t="n">
-        <v>5.092214929490858</v>
+        <v>6.547195079403278</v>
       </c>
       <c r="G27" t="n">
-        <v>5.265819773378031</v>
+        <v>6.588837800901302</v>
       </c>
       <c r="H27" t="n">
-        <v>5.425980974423784</v>
+        <v>6.834432190756875</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NF3*TIME</t>
+          <t>C3H6*TIME</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6993,94 +7862,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.07051622094944454</v>
+        <v>-0.09181878621131423</v>
       </c>
       <c r="E28" t="n">
-        <v>5.218450807508775</v>
+        <v>6.481938714617151</v>
       </c>
       <c r="F28" t="n">
-        <v>5.335446299130926</v>
+        <v>6.867802603734718</v>
       </c>
       <c r="G28" t="n">
-        <v>5.068188977230776</v>
+        <v>6.485295884660785</v>
       </c>
       <c r="H28" t="n">
-        <v>5.326216910751816</v>
+        <v>6.687522201355724</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AR*O2</t>
+          <t>NF3*PRESSURE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-0.06172625291078715</v>
+        <v>0.08717455574040356</v>
       </c>
       <c r="E29" t="n">
-        <v>4.972503899152883</v>
+        <v>6.655024756124728</v>
       </c>
       <c r="F29" t="n">
-        <v>5.251379466044942</v>
+        <v>6.703355094952923</v>
       </c>
       <c r="G29" t="n">
-        <v>5.233119520912484</v>
+        <v>6.494632728785639</v>
       </c>
       <c r="H29" t="n">
-        <v>5.388542581982969</v>
+        <v>6.717312179094641</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>C3H6*NF3</t>
+          <t>SPACE*RF_POWER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.05976568533632864</v>
+        <v>-0.08315114786048605</v>
       </c>
       <c r="E30" t="n">
-        <v>5.38262133674154</v>
+        <v>6.549288222457452</v>
       </c>
       <c r="F30" t="n">
-        <v>5.23682818862935</v>
+        <v>6.649743393442581</v>
       </c>
       <c r="G30" t="n">
-        <v>5.225999279642417</v>
+        <v>6.712691939077776</v>
       </c>
       <c r="H30" t="n">
-        <v>5.199737502202884</v>
+        <v>6.646844814341932</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N2*SPACE</t>
+          <t>PRESSURE*SPACE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7089,211 +7958,499 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.05780419360532152</v>
+        <v>-0.07720973516619045</v>
       </c>
       <c r="E31" t="n">
-        <v>5.297407083640135</v>
+        <v>6.462337103630102</v>
       </c>
       <c r="F31" t="n">
-        <v>5.272174623074235</v>
+        <v>6.623091163782057</v>
       </c>
       <c r="G31" t="n">
-        <v>5.168547620575425</v>
+        <v>6.707710805994147</v>
       </c>
       <c r="H31" t="n">
-        <v>5.258923547220168</v>
+        <v>6.714045395813722</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HE*O2</t>
+          <t>PRESSURE*RF_POWER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.04925704468235415</v>
+        <v>0.07232717033126734</v>
       </c>
       <c r="E32" t="n">
-        <v>4.999816218332768</v>
+        <v>6.606772550402987</v>
       </c>
       <c r="F32" t="n">
-        <v>5.150553144205052</v>
+        <v>6.526800865933467</v>
       </c>
       <c r="G32" t="n">
-        <v>5.214911308125894</v>
+        <v>6.674369053780754</v>
       </c>
       <c r="H32" t="n">
-        <v>5.464162323362887</v>
+        <v>6.739051709973769</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PRESSURE*SPACE</t>
+          <t>C3H6*NF3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.04499950013609766</v>
+        <v>0.05201942020945083</v>
       </c>
       <c r="E33" t="n">
-        <v>5.197938433869937</v>
+        <v>6.789425919068308</v>
       </c>
       <c r="F33" t="n">
-        <v>5.192076511067445</v>
+        <v>6.662811134100614</v>
       </c>
       <c r="G33" t="n">
-        <v>5.234860053755557</v>
+        <v>6.613754319657203</v>
       </c>
       <c r="H33" t="n">
-        <v>5.31899713122526</v>
+        <v>6.59117837510841</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AR*N2</t>
+          <t>NF3*RF_POWER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.03877925744406729</v>
+        <v>-0.04374192812732769</v>
       </c>
       <c r="E34" t="n">
-        <v>5.201354898468614</v>
+        <v>6.653758177653183</v>
       </c>
       <c r="F34" t="n">
-        <v>5.09881213316779</v>
+        <v>6.704199480600619</v>
       </c>
       <c r="G34" t="n">
-        <v>5.336209413188583</v>
+        <v>6.643045302280623</v>
       </c>
       <c r="H34" t="n">
-        <v>5.311225162775894</v>
+        <v>6.606002748973403</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HE*NF3</t>
+          <t>N2*RF_POWER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.03556000539182902</v>
+        <v>-0.04343948943737796</v>
       </c>
       <c r="E35" t="n">
-        <v>5.104419449444221</v>
+        <v>6.648821945310281</v>
       </c>
       <c r="F35" t="n">
-        <v>5.080817656797417</v>
+        <v>6.699152662723628</v>
       </c>
       <c r="G35" t="n">
-        <v>5.411467204507296</v>
+        <v>6.646336123842556</v>
       </c>
       <c r="H35" t="n">
-        <v>5.316745401076835</v>
+        <v>6.609787862381147</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>HE*C3H6</t>
+          <t>N2*O2</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0.02584280959009</v>
+        <v>0.0433148780579411</v>
       </c>
       <c r="E36" t="n">
-        <v>5.154451056746916</v>
+        <v>6.597441900989149</v>
       </c>
       <c r="F36" t="n">
-        <v>5.047463251928953</v>
+        <v>6.733406025604382</v>
       </c>
       <c r="G36" t="n">
-        <v>5.388941708625766</v>
+        <v>6.498254899732543</v>
       </c>
       <c r="H36" t="n">
-        <v>5.333639522987982</v>
+        <v>6.720848780463658</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>HE*NF3</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NF3</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>-0.03673669730043239</v>
+      </c>
+      <c r="E37" t="n">
+        <v>6.519357014709603</v>
+      </c>
+      <c r="F37" t="n">
+        <v>6.507038216627428</v>
+      </c>
+      <c r="G37" t="n">
+        <v>6.79380025589634</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.7080080632133</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AR*N2</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.0357162905366768</v>
+      </c>
+      <c r="E38" t="n">
+        <v>6.587831051872805</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6.497785810122231</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6.739813258348612</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6.721200597671391</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>N2*TIME</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.03562710925963586</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6.536451007551673</v>
+      </c>
+      <c r="F39" t="n">
+        <v>6.774066621229367</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6.44895435603777</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.757824188234737</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>O2*PRESSURE</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PRESSURE</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.02824986644184957</v>
+      </c>
+      <c r="E40" t="n">
+        <v>6.463040738045569</v>
+      </c>
+      <c r="F40" t="n">
+        <v>6.587855675028262</v>
+      </c>
+      <c r="G40" t="n">
+        <v>6.622622074171744</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.803936744038136</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AR*RF_POWER</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.02033542456675352</v>
+      </c>
+      <c r="E41" t="n">
+        <v>6.544351990114551</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6.526771851294401</v>
+      </c>
+      <c r="G41" t="n">
+        <v>6.715982760639711</v>
+      </c>
+      <c r="H41" t="n">
+        <v>6.739073470953068</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>N2*SPACE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SPACE</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.009703315325276129</v>
+      </c>
+      <c r="E42" t="n">
+        <v>6.64745452930924</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6.700064273390988</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.584299188874723</v>
+      </c>
+      <c r="H42" t="n">
+        <v>6.656315563607023</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HE*O2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>-0.007524957502555107</v>
+      </c>
+      <c r="E43" t="n">
+        <v>6.389586946580867</v>
+      </c>
+      <c r="F43" t="n">
+        <v>6.593551595379918</v>
+      </c>
+      <c r="G43" t="n">
+        <v>6.636824869338064</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6.825739603132006</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>O2*SPACE</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>SPACE</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>0.02374579235620322</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5.115459926046102</v>
-      </c>
-      <c r="F37" t="n">
-        <v>5.137815502983671</v>
-      </c>
-      <c r="G37" t="n">
-        <v>5.289845725638114</v>
-      </c>
-      <c r="H37" t="n">
-        <v>5.35969288728809</v>
+      <c r="D44" t="n">
+        <v>-0.003389776184276716</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6.492971945793419</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.567901536529696</v>
+      </c>
+      <c r="G44" t="n">
+        <v>6.687287577885269</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.755437616252992</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AR*O2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>O2</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.003030254153744139</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6.419518154328716</v>
+      </c>
+      <c r="F45" t="n">
+        <v>6.609994408484957</v>
+      </c>
+      <c r="G45" t="n">
+        <v>6.616870730839498</v>
+      </c>
+      <c r="H45" t="n">
+        <v>6.813407493303227</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HE*C3H6</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>C3H6</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>-0.002249468830591628</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6.574000737844537</v>
+      </c>
+      <c r="F46" t="n">
+        <v>6.470609067870804</v>
+      </c>
+      <c r="G46" t="n">
+        <v>6.806427921583126</v>
+      </c>
+      <c r="H46" t="n">
+        <v>6.69853731394821</v>
       </c>
     </row>
   </sheetData>
@@ -7307,7 +8464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7344,16 +8501,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.651234567901245</v>
+        <v>4.843779677113063</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.127697841726624</v>
+        <v>0.09519143734311387</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2820387130310874</v>
+        <v>0.80948198669312</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -7366,16 +8523,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6036155202821641</v>
+        <v>19.95489078822422</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3517471736896063</v>
+        <v>0.3921596073271577</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6132591985534163</v>
+        <v>0.643823464196747</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -7388,16 +8545,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.234567901234627</v>
+        <v>39.65859449192796</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.467625899280609</v>
+        <v>0.7793828093651755</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2568075998509573</v>
+        <v>0.5395675444566972</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -7410,19 +8567,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>36.31790123456795</v>
+        <v>5.436372269705553</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>21.16366906474822</v>
+        <v>0.1068372479307214</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04414546467910077</v>
+        <v>0.7988835429119767</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -7432,19 +8589,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>577.044091710758</v>
+        <v>736.0042735042737</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>336.2631038026719</v>
+        <v>14.46418073402201</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002960661432138027</v>
+        <v>0.1636863359156839</v>
       </c>
       <c r="F6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -7454,19 +8611,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1021.377425044092</v>
+        <v>1189.88081671415</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>595.1911613566288</v>
+        <v>23.38390115991528</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001675910031051741</v>
+        <v>0.1298203134895178</v>
       </c>
       <c r="F7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -7476,16 +8633,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.889329805996554</v>
+        <v>39.65859449192781</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>4.014645426515976</v>
+        <v>0.7793828093651725</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1830065359477109</v>
+        <v>0.5395675444566976</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -7498,16 +8655,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.139329805996431</v>
+        <v>53.28822412155756</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.577595066803675</v>
+        <v>1.047236452880194</v>
       </c>
       <c r="E9" t="n">
-        <v>0.199111420330889</v>
+        <v>0.4926548961367033</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -7520,16 +8677,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.12742504409171</v>
+        <v>16.25118708452032</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.232528263103802</v>
+        <v>0.3193732911545945</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1030357399166242</v>
+        <v>0.6725317017440855</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -7538,18 +8695,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>RF_POWER</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>466.3252611585942</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.16436643244403</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.2031107655003471</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Residual</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>3.4320987654321</v>
-      </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="b">
+      <c r="B12" t="n">
+        <v>50.88461538461538</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="b">
         <v>0</v>
       </c>
     </row>

--- a/[예제 015] 반도체 공정 DOE 분석 시스템/doe_results/doe_report.xlsx
+++ b/[예제 015] 반도체 공정 DOE 분석 시스템/doe_results/doe_report.xlsx
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.106837606837646</v>
+        <v>2.88888888888892</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1334166319589076</v>
+        <v>0.08333333333333427</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7770516808951565</v>
+        <v>0.8210876249779322</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -1385,16 +1385,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.88461538461548</v>
+        <v>11.55555555555563</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4510620574760556</v>
+        <v>0.3333333333333355</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6234915009749016</v>
+        <v>0.6666666666666657</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -1407,16 +1407,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34.8722697056032</v>
+        <v>38.83950617283967</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.132876733459832</v>
+        <v>1.120370370370376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.480156665869962</v>
+        <v>0.4819202867568524</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -1429,16 +1429,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7981956315289755</v>
+        <v>0.3209876543209957</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02593055362734703</v>
+        <v>0.009259259259259495</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8983578817426885</v>
+        <v>0.9389292606149483</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -1451,16 +1451,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>726.5759734093067</v>
+        <v>709.061728395062</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>23.60388418405916</v>
+        <v>20.45370370370372</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1292305068929173</v>
+        <v>0.1385358151369521</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -1473,16 +1473,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1256.946343779678</v>
+        <v>1233.876543209877</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8337421136256</v>
+        <v>35.59259259259262</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09882398758345072</v>
+        <v>0.1057259799817394</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -1495,16 +1495,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.68708452041786</v>
+        <v>20.54320987654322</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5745908340660543</v>
+        <v>0.5925925925925932</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5870803176366084</v>
+        <v>0.5823434503447228</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -1517,16 +1517,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.90930674264011</v>
+        <v>32.09876543209881</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.166566399802555</v>
+        <v>0.9259259259259276</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4755040506390953</v>
+        <v>0.5122457083553998</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -1539,16 +1539,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6500474833807974</v>
+        <v>1.283950617283927</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.02111774414981354</v>
+        <v>0.03703703703703639</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9081298559787105</v>
+        <v>0.8789622816763242</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>402.7735042735041</v>
+        <v>415.9999999999997</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>13.08468693599891</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1717057692021036</v>
+        <v>0.1789123750220669</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30.78205128205121</v>
+        <v>34.66666666666665</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -1652,19 +1652,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20.71428571428572</v>
+        <v>20.57142857142857</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>26.71428571428572</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="E2" t="n">
-        <v>3.086811657187163</v>
+        <v>3.065189928812817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01150631164613779</v>
+        <v>0.01193833999758694</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15.57142857142857</v>
+        <v>15.42857142857143</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>24.57142857142857</v>
+        <v>24.42857142857143</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95111288363113</v>
+        <v>1.93529741355558</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07960128923216458</v>
+        <v>0.08171481085940975</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.88571428571429</v>
+        <v>13.02857142857143</v>
       </c>
       <c r="C4" t="n">
-        <v>12.71428571428571</v>
+        <v>12.57142857142857</v>
       </c>
       <c r="D4" t="n">
         <v>25.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.525648961308716</v>
+        <v>-1.552940402449168</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1580817085374539</v>
+        <v>0.1514865992293275</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.314285714285717</v>
+        <v>4.457142857142859</v>
       </c>
       <c r="C5" t="n">
-        <v>16.28571428571428</v>
+        <v>16.14285714285714</v>
       </c>
       <c r="D5" t="n">
         <v>20.6</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4650086896519343</v>
+        <v>-0.4823866679072939</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6518859070789574</v>
+        <v>0.6399160211213678</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.285714285714285</v>
+        <v>3.428571428571427</v>
       </c>
       <c r="C6" t="n">
-        <v>16.71428571428572</v>
+        <v>16.57142857142857</v>
       </c>
       <c r="D6" t="n">
         <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3525484934147565</v>
+        <v>-0.3693164431004269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.731744332644083</v>
+        <v>0.7195919957214846</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -1777,19 +1777,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.885714285714286</v>
+        <v>2.742857142857144</v>
       </c>
       <c r="C7" t="n">
         <v>16.4</v>
       </c>
       <c r="D7" t="n">
-        <v>19.28571428571428</v>
+        <v>19.14285714285714</v>
       </c>
       <c r="E7" t="n">
-        <v>0.309190498657767</v>
+        <v>0.2947304468233088</v>
       </c>
       <c r="F7" t="n">
-        <v>0.763522638768531</v>
+        <v>0.774227622777265</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -1798,23 +1798,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.514285714285716</v>
+        <v>1.371428571428574</v>
       </c>
       <c r="C8" t="n">
-        <v>17.2</v>
+        <v>17.42857142857143</v>
       </c>
       <c r="D8" t="n">
-        <v>18.71428571428572</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1616894009082593</v>
+        <v>-0.1468875175899967</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8747706330526553</v>
+        <v>0.8861399404583311</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -1823,23 +1823,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.228571428571428</v>
+        <v>1.371428571428574</v>
       </c>
       <c r="C9" t="n">
-        <v>17.57142857142857</v>
+        <v>17.2</v>
       </c>
       <c r="D9" t="n">
-        <v>18.8</v>
+        <v>18.57142857142857</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1311234020864347</v>
+        <v>0.1468875175899967</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8982781440607277</v>
+        <v>0.8861399404583311</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -1852,19 +1852,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.485714285714284</v>
+        <v>0.3428571428571416</v>
       </c>
       <c r="C10" t="n">
         <v>17.8</v>
       </c>
       <c r="D10" t="n">
-        <v>18.28571428571428</v>
+        <v>18.14285714285714</v>
       </c>
       <c r="E10" t="n">
-        <v>0.05180192618701184</v>
+        <v>0.03668479615312004</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9597066946614535</v>
+        <v>0.9714583183493412</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -1877,19 +1877,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.1999999999999993</v>
+        <v>0.3428571428571416</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>17.85714285714286</v>
       </c>
       <c r="D11" t="n">
         <v>18.2</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02132782862022205</v>
+        <v>-0.03668479615312004</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9834037101675366</v>
+        <v>0.9714583183493412</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.25</v>
+        <v>22.125</v>
       </c>
       <c r="E2" t="n">
         <v>43.5</v>
@@ -1980,7 +1980,7 @@
         <v>13.66666666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="3">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.58333333333334</v>
+        <v>21.45833333333334</v>
       </c>
       <c r="E3" t="n">
         <v>35</v>
@@ -2012,7 +2012,7 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>24.5</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="4">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-16.75</v>
+        <v>-16.875</v>
       </c>
       <c r="E4" t="n">
         <v>6.5</v>
@@ -2044,7 +2044,7 @@
         <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="5">
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.95833333333334</v>
+        <v>14.83333333333334</v>
       </c>
       <c r="E5" t="n">
         <v>29.5</v>
@@ -2076,7 +2076,7 @@
         <v>11.66666666666667</v>
       </c>
       <c r="H5" t="n">
-        <v>22.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="6">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-14.04166666666667</v>
+        <v>-14.16666666666667</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
@@ -2108,7 +2108,7 @@
         <v>26</v>
       </c>
       <c r="H6" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.54166666666667</v>
+        <v>13.41666666666667</v>
       </c>
       <c r="E7" t="n">
         <v>18</v>
@@ -2140,7 +2140,7 @@
         <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="8">
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-12.625</v>
+        <v>-12.75</v>
       </c>
       <c r="E8" t="n">
         <v>9</v>
@@ -2172,7 +2172,7 @@
         <v>24.33333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="9">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.04166666666667</v>
+        <v>11.91666666666667</v>
       </c>
       <c r="E9" t="n">
         <v>15.5</v>
@@ -2204,7 +2204,7 @@
         <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>30.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-11.375</v>
+        <v>-11.5</v>
       </c>
       <c r="E10" t="n">
         <v>10.5</v>
@@ -2236,7 +2236,7 @@
         <v>24.33333333333333</v>
       </c>
       <c r="H10" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="11">
@@ -2256,7 +2256,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.79166666666667</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="E11" t="n">
         <v>28</v>
@@ -2268,7 +2268,7 @@
         <v>15.66666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>20.25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.79166666666667</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="E12" t="n">
         <v>24.5</v>
@@ -2300,7 +2300,7 @@
         <v>12.33333333333333</v>
       </c>
       <c r="H12" t="n">
-        <v>22.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="13">
@@ -2320,7 +2320,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.75</v>
+        <v>10.625</v>
       </c>
       <c r="E13" t="n">
         <v>11.5</v>
@@ -2332,7 +2332,7 @@
         <v>19.66666666666667</v>
       </c>
       <c r="H13" t="n">
-        <v>32</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="14">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>9.375</v>
+        <v>9.25</v>
       </c>
       <c r="E14" t="n">
         <v>13</v>
@@ -2364,7 +2364,7 @@
         <v>22.66666666666667</v>
       </c>
       <c r="H14" t="n">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="15">
@@ -2384,7 +2384,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>9.166666666666666</v>
+        <v>9.041666666666666</v>
       </c>
       <c r="E15" t="n">
         <v>32</v>
@@ -2396,18 +2396,18 @@
         <v>21.33333333333333</v>
       </c>
       <c r="H15" t="n">
-        <v>16</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N2*PRESSURE</t>
+          <t>O2*PRESSURE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2416,83 +2416,83 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>-8.916666666666666</v>
       </c>
       <c r="E16" t="n">
-        <v>25.5</v>
+        <v>4.5</v>
       </c>
       <c r="F16" t="n">
-        <v>11.66666666666667</v>
+        <v>12</v>
       </c>
       <c r="G16" t="n">
-        <v>16.33333333333333</v>
+        <v>30.33333333333333</v>
       </c>
       <c r="H16" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PRESSURE*TIME</t>
+          <t>N2*PRESSURE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>N2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>PRESSURE</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
       <c r="D17" t="n">
-        <v>8.791666666666666</v>
+        <v>8.875</v>
       </c>
       <c r="E17" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
       <c r="F17" t="n">
-        <v>15.33333333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>13.33333333333333</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>19.25</v>
+        <v>20.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O2*PRESSURE</t>
+          <t>PRESSURE*TIME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-8.791666666666666</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5</v>
+        <v>27</v>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>15.33333333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>30.33333333333333</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>20.25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-7.958333333333333</v>
+        <v>-8.083333333333332</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
@@ -2524,7 +2524,7 @@
         <v>32</v>
       </c>
       <c r="H19" t="n">
-        <v>22.75</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="20">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-7.750000000000002</v>
+        <v>-7.875000000000002</v>
       </c>
       <c r="E20" t="n">
         <v>11</v>
@@ -2556,7 +2556,7 @@
         <v>35.33333333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="21">
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7.708333333333334</v>
+        <v>7.583333333333334</v>
       </c>
       <c r="E21" t="n">
         <v>32</v>
@@ -2588,7 +2588,7 @@
         <v>21.33333333333333</v>
       </c>
       <c r="H21" t="n">
-        <v>14.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="22">
@@ -2608,7 +2608,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-6.958333333333332</v>
+        <v>-7.083333333333332</v>
       </c>
       <c r="E22" t="n">
         <v>16.5</v>
@@ -2620,7 +2620,7 @@
         <v>20.33333333333333</v>
       </c>
       <c r="H22" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.458333333333333</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="E23" t="n">
         <v>23.5</v>
@@ -2652,7 +2652,7 @@
         <v>11.66666666666667</v>
       </c>
       <c r="H23" t="n">
-        <v>19.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="24">
@@ -2672,7 +2672,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-6.125000000000001</v>
+        <v>-6.250000000000001</v>
       </c>
       <c r="E24" t="n">
         <v>7</v>
@@ -2684,7 +2684,7 @@
         <v>10.33333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>20.75</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="25">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6.125</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
         <v>24.5</v>
@@ -2716,7 +2716,7 @@
         <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>18.75</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="26">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-5.541666666666667</v>
+        <v>-5.666666666666667</v>
       </c>
       <c r="E26" t="n">
         <v>21</v>
@@ -2748,7 +2748,7 @@
         <v>28.66666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-5.500000000000001</v>
+        <v>-5.625000000000001</v>
       </c>
       <c r="E27" t="n">
         <v>9.5</v>
@@ -2780,7 +2780,7 @@
         <v>36.33333333333334</v>
       </c>
       <c r="H27" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="28">
@@ -2800,7 +2800,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-5.333333333333332</v>
+        <v>-5.458333333333332</v>
       </c>
       <c r="E28" t="n">
         <v>2</v>
@@ -2812,71 +2812,71 @@
         <v>8.666666666666666</v>
       </c>
       <c r="H28" t="n">
-        <v>25</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>O2*NF3</t>
+          <t>SPACE*RF_POWER</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5.25</v>
+        <v>-5.208333333333333</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>20.5</v>
       </c>
       <c r="F29" t="n">
-        <v>15</v>
+        <v>13.66666666666667</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="H29" t="n">
-        <v>35.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SPACE*RF_POWER</t>
+          <t>O2*NF3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-5.083333333333333</v>
+        <v>5.125</v>
       </c>
       <c r="E30" t="n">
-        <v>20.5</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>13.66666666666667</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>12</v>
+        <v>35.25</v>
       </c>
     </row>
     <row r="31">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-4.875000000000001</v>
+        <v>-5.000000000000001</v>
       </c>
       <c r="E31" t="n">
         <v>22.5</v>
@@ -2908,7 +2908,7 @@
         <v>27.66666666666667</v>
       </c>
       <c r="H31" t="n">
-        <v>10.75</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="32">
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-4.708333333333334</v>
+        <v>-4.833333333333334</v>
       </c>
       <c r="E32" t="n">
         <v>4.5</v>
@@ -2940,7 +2940,7 @@
         <v>12</v>
       </c>
       <c r="H32" t="n">
-        <v>23.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="33">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-4.666666666666666</v>
+        <v>-4.791666666666666</v>
       </c>
       <c r="E33" t="n">
         <v>14</v>
@@ -2972,114 +2972,114 @@
         <v>21</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AR*PRESSURE</t>
+          <t>SPACE*TIME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>4.583333333333333</v>
+        <v>-4.5</v>
       </c>
       <c r="E34" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F34" t="n">
-        <v>14.33333333333333</v>
+        <v>18</v>
       </c>
       <c r="G34" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H34" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SPACE*TIME</t>
+          <t>AR*SPACE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>SPACE</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
       <c r="D35" t="n">
-        <v>-4.375</v>
+        <v>-4.458333333333334</v>
       </c>
       <c r="E35" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G35" t="n">
-        <v>22</v>
+        <v>18.66666666666667</v>
       </c>
       <c r="H35" t="n">
-        <v>17.25</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N2*SPACE</t>
+          <t>AR*PRESSURE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4.333333333333334</v>
+        <v>4.458333333333333</v>
       </c>
       <c r="E36" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="F36" t="n">
-        <v>16.33333333333333</v>
+        <v>14.33333333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H36" t="n">
-        <v>21.5</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AR*SPACE</t>
+          <t>N2*SPACE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-4.333333333333334</v>
+        <v>4.208333333333334</v>
       </c>
       <c r="E37" t="n">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="F37" t="n">
-        <v>21</v>
+        <v>16.33333333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>18.66666666666667</v>
+        <v>15</v>
       </c>
       <c r="H37" t="n">
-        <v>18</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="38">
@@ -3120,7 +3120,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.958333333333334</v>
+        <v>2.833333333333334</v>
       </c>
       <c r="E38" t="n">
         <v>30.5</v>
@@ -3132,71 +3132,71 @@
         <v>22.33333333333333</v>
       </c>
       <c r="H38" t="n">
-        <v>11.75</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>O2*TIME</t>
+          <t>C3H6*O2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>C3H6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>TIME</t>
-        </is>
-      </c>
       <c r="D39" t="n">
-        <v>2.875</v>
+        <v>-2.750000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="F39" t="n">
-        <v>7.333333333333333</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="G39" t="n">
-        <v>23.66666666666667</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="H39" t="n">
-        <v>25.25</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C3H6*O2</t>
+          <t>O2*TIME</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-2.625000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="E40" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="F40" t="n">
-        <v>25.66666666666667</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="G40" t="n">
-        <v>10.33333333333333</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>23.75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-2.333333333333332</v>
+        <v>-2.458333333333332</v>
       </c>
       <c r="E41" t="n">
         <v>21</v>
@@ -3228,18 +3228,18 @@
         <v>19.33333333333333</v>
       </c>
       <c r="H41" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HE*NF3</t>
+          <t>N2*NF3</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3248,30 +3248,30 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.791666666666666</v>
+        <v>-1.875</v>
       </c>
       <c r="E42" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="F42" t="n">
-        <v>28</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>3.666666666666667</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="H42" t="n">
-        <v>25.75</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>N2*NF3</t>
+          <t>HE*NF3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3280,19 +3280,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-1.75</v>
+        <v>1.666666666666666</v>
       </c>
       <c r="E43" t="n">
-        <v>3.5</v>
+        <v>9.5</v>
       </c>
       <c r="F43" t="n">
-        <v>26.33333333333333</v>
+        <v>28</v>
       </c>
       <c r="G43" t="n">
-        <v>7.666666666666667</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="H43" t="n">
-        <v>27</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="44">
@@ -3312,7 +3312,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.6666666666666679</v>
+        <v>-0.7916666666666679</v>
       </c>
       <c r="E44" t="n">
         <v>16</v>
@@ -3324,7 +3324,7 @@
         <v>16.66666666666667</v>
       </c>
       <c r="H44" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="45">
@@ -3344,7 +3344,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.2916666666666679</v>
+        <v>0.1666666666666679</v>
       </c>
       <c r="E45" t="n">
         <v>21</v>
@@ -3356,7 +3356,7 @@
         <v>16.33333333333333</v>
       </c>
       <c r="H45" t="n">
-        <v>16.25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.2083333333333339</v>
+        <v>0.08333333333333393</v>
       </c>
       <c r="E46" t="n">
         <v>5.5</v>
@@ -3388,7 +3388,7 @@
         <v>6.333333333333333</v>
       </c>
       <c r="H46" t="n">
-        <v>27.25</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8845922637865976</v>
+        <v>0.8994591473792126</v>
       </c>
     </row>
     <row r="3">
@@ -3434,7 +3434,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.31841129455392</v>
+        <v>13.30621561232622</v>
       </c>
     </row>
     <row r="4">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.19040305111844</v>
+        <v>95.17968760976446</v>
       </c>
     </row>
     <row r="5">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.76155424118205</v>
+        <v>70.75052619882143</v>
       </c>
     </row>
     <row r="6">
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.44522909634792</v>
+        <v>5.460387832558212</v>
       </c>
     </row>
     <row r="7">
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.78470637712235</v>
+        <v>69.77366450100706</v>
       </c>
     </row>
     <row r="8">
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15.80543579374586</v>
+        <v>15.79334798134614</v>
       </c>
     </row>
     <row r="9">
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.385503749523426</v>
+        <v>2.403051135573891</v>
       </c>
     </row>
     <row r="10">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19.81756185643183</v>
+        <v>19.80706495374426</v>
       </c>
     </row>
     <row r="11">
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14.78628519436315</v>
+        <v>14.80699400209628</v>
       </c>
     </row>
     <row r="12">
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>162.6785625908007</v>
+        <v>162.6955725328786</v>
       </c>
     </row>
     <row r="13">
@@ -3534,7 +3534,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5000.000000014914</v>
+        <v>4999.999999985328</v>
       </c>
     </row>
     <row r="14">
@@ -3544,7 +3544,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.227893448146544</v>
+        <v>0.9352787130510244</v>
       </c>
     </row>
     <row r="15">
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18.55133309771782</v>
+        <v>18.50769611092936</v>
       </c>
     </row>
   </sheetData>
@@ -3568,7 +3568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3579,117 +3579,167 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>AR_raw</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>N2_raw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>HE_raw</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>C3H6_raw</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>O2_raw</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>NF3_raw</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PRESSURE_raw</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>SPACE_raw</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>TIME_raw</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>RF_POWER_raw</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>THICKNESS</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>UNIFORMITY</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>PARTICLE</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>AR_actual</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>AR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>N2_actual</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>N2</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>HE_actual</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>HE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>C3H6_actual</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>C3H6</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>O2_actual</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>O2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>NF3_actual</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>NF3</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>PRESSURE_actual</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
         <is>
           <t>PRESSURE</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>SPACE_actual</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>SPACE</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>TIME_actual</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>TIME</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>RF_POWER_actual</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
         <is>
           <t>RF_POWER</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>AR_actual</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>N2_actual</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>HE_actual</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>C3H6_actual</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>O2_actual</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>NF3_actual</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>PRESSURE_actual</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>SPACE_actual</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>TIME_actual</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>RF_POWER_actual</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>THICKNESS</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>UNIFORMITY</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>PARTICLE</t>
         </is>
       </c>
     </row>
@@ -3698,73 +3748,103 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K2" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L2" t="n">
+        <v>1384.34</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4.937370877094885</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="n">
         <v>100</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S2" t="n">
         <v>500</v>
       </c>
-      <c r="O2" t="n">
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
         <v>50</v>
       </c>
-      <c r="P2" t="n">
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>100</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC2" t="n">
         <v>5</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AD2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE2" t="n">
         <v>120</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
         <v>100</v>
       </c>
-      <c r="V2" t="n">
-        <v>1390.403219833868</v>
-      </c>
-      <c r="W2" t="n">
-        <v>5.382462144918832</v>
-      </c>
-      <c r="X2" t="n">
-        <v>14</v>
+      <c r="AH2" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
@@ -3772,73 +3852,103 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>493.7160000000001</v>
       </c>
       <c r="M3" t="n">
+        <v>3.017929335890448</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>200</v>
       </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U3" t="n">
         <v>50</v>
       </c>
-      <c r="P3" t="n">
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>100</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC3" t="n">
         <v>5</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AD3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE3" t="n">
         <v>10</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AF3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2000</v>
       </c>
-      <c r="V3" t="n">
-        <v>495.1236147571847</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3.561060246290614</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
+      <c r="AH3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -3846,73 +3956,103 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>213.208</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.611496754334709</v>
       </c>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S4" t="n">
         <v>500</v>
       </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W4" t="n">
         <v>100</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
         <v>100</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
         <v>10</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
         <v>5</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AD4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE4" t="n">
         <v>10</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AF4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG4" t="n">
         <v>100</v>
       </c>
-      <c r="V4" t="n">
-        <v>215.3518360631049</v>
-      </c>
-      <c r="W4" t="n">
-        <v>4.138336987027869</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
+      <c r="AH4" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -3920,73 +4060,103 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L5" t="n">
+        <v>385.492</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.904101771237923</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
         <v>100</v>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U5" t="n">
         <v>50</v>
       </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y5" t="n">
         <v>100</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
         <v>10</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
         <v>30</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
         <v>10</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AF5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG5" t="n">
         <v>100</v>
       </c>
-      <c r="V5" t="n">
-        <v>386.7894829261479</v>
-      </c>
-      <c r="W5" t="n">
-        <v>4.311456076713108</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
+      <c r="AH5" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="6">
@@ -3994,73 +4164,103 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K6" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2582.004</v>
       </c>
       <c r="M6" t="n">
+        <v>3.578615679913052</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>200</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W6" t="n">
         <v>100</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA6" t="n">
         <v>10</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AB6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" t="n">
         <v>30</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
         <v>120</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
         <v>100</v>
       </c>
-      <c r="V6" t="n">
-        <v>2588.557199950976</v>
-      </c>
-      <c r="W6" t="n">
-        <v>4.00603052985567</v>
-      </c>
-      <c r="X6" t="n">
-        <v>9</v>
+      <c r="AH6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="7">
@@ -4068,73 +4268,103 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2055.712</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.410010740803336</v>
       </c>
       <c r="N7" t="n">
+        <v>19</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S7" t="n">
         <v>500</v>
       </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y7" t="n">
         <v>100</v>
       </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC7" t="n">
         <v>30</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
         <v>120</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2000</v>
       </c>
-      <c r="V7" t="n">
-        <v>2085.784945025293</v>
-      </c>
-      <c r="W7" t="n">
-        <v>3.833718281476469</v>
-      </c>
-      <c r="X7" t="n">
-        <v>19</v>
+      <c r="AH7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -4142,73 +4372,103 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I8" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>23786.844</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.445889837256211</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U8" t="n">
         <v>50</v>
       </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" t="n">
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA8" t="n">
         <v>10</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
         <v>5</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AD8" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE8" t="n">
         <v>120</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
         <v>2000</v>
       </c>
-      <c r="V8" t="n">
-        <v>24070.326466242</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.975187961234396</v>
-      </c>
-      <c r="X8" t="n">
-        <v>45</v>
+      <c r="AH8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -4216,73 +4476,103 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J9" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L9" t="n">
+        <v>184.432</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5.42205257220704</v>
+      </c>
+      <c r="N9" t="n">
+        <v>22</v>
+      </c>
+      <c r="O9" t="n">
         <v>100</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W9" t="n">
         <v>100</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC9" t="n">
         <v>30</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
         <v>10</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AF9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG9" t="n">
         <v>2000</v>
       </c>
-      <c r="V9" t="n">
-        <v>181.6733958456488</v>
-      </c>
-      <c r="W9" t="n">
-        <v>6.192438555904352</v>
-      </c>
-      <c r="X9" t="n">
-        <v>22</v>
+      <c r="AH9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -4290,73 +4580,103 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="K10" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
+        <v>848.8880000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>6.214011742417012</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
         <v>100</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>200</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y10" t="n">
         <v>100</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC10" t="n">
         <v>5</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AD10" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE10" t="n">
         <v>120</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
         <v>100</v>
       </c>
-      <c r="V10" t="n">
-        <v>841.9209386379823</v>
-      </c>
-      <c r="W10" t="n">
-        <v>6.694495411481428</v>
-      </c>
-      <c r="X10" t="n">
-        <v>7</v>
+      <c r="AH10" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
@@ -4364,73 +4684,103 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2000</v>
       </c>
       <c r="L11" t="n">
+        <v>1115.58</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.63091844600897</v>
+      </c>
+      <c r="N11" t="n">
+        <v>42</v>
+      </c>
+      <c r="O11" t="n">
         <v>100</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>200</v>
       </c>
-      <c r="N11" t="n">
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
         <v>500</v>
       </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA11" t="n">
         <v>10</v>
       </c>
-      <c r="S11" t="n">
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" t="n">
         <v>5</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AD11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE11" t="n">
         <v>10</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AF11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG11" t="n">
         <v>2000</v>
       </c>
-      <c r="V11" t="n">
-        <v>1124.333554528524</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3.05422811547538</v>
-      </c>
-      <c r="X11" t="n">
-        <v>42</v>
+      <c r="AH11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -4438,73 +4788,103 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J12" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>85.536</v>
       </c>
       <c r="M12" t="n">
+        <v>1.870557426102049</v>
+      </c>
+      <c r="N12" t="n">
+        <v>28</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>200</v>
       </c>
-      <c r="N12" t="n">
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
         <v>500</v>
       </c>
-      <c r="O12" t="n">
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
         <v>50</v>
       </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC12" t="n">
         <v>30</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
         <v>10</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AF12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG12" t="n">
         <v>100</v>
       </c>
-      <c r="V12" t="n">
-        <v>86.71722759675947</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.455786896293087</v>
-      </c>
-      <c r="X12" t="n">
-        <v>28</v>
+      <c r="AH12" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -4512,73 +4892,103 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13" t="n">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>75.928</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>5.794963649735316</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC13" t="n">
         <v>5</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AD13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE13" t="n">
         <v>10</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AF13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG13" t="n">
         <v>100</v>
       </c>
-      <c r="V13" t="n">
-        <v>76.21561313205028</v>
-      </c>
-      <c r="W13" t="n">
-        <v>5.9891602346921</v>
-      </c>
-      <c r="X13" t="n">
-        <v>27</v>
+      <c r="AH13" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -4896,79 +5306,79 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>1458.461954034472</v>
+        <v>1452</v>
       </c>
       <c r="C4" t="n">
-        <v>1458.988106416898</v>
+        <v>1449.1</v>
       </c>
       <c r="D4" t="n">
-        <v>1471.613391032176</v>
+        <v>1457.9</v>
       </c>
       <c r="E4" t="n">
-        <v>1443.668015831196</v>
+        <v>1437.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1446.196709063262</v>
+        <v>1440.2</v>
       </c>
       <c r="G4" t="n">
-        <v>1444.261002803657</v>
+        <v>1430.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1430.453627024378</v>
+        <v>1420.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1417.051058431058</v>
+        <v>1412.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1434.357812880324</v>
+        <v>1425.1</v>
       </c>
       <c r="K4" t="n">
-        <v>1385.499564107821</v>
+        <v>1380.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1377.896824402427</v>
+        <v>1373.1</v>
       </c>
       <c r="M4" t="n">
-        <v>1397.292789980238</v>
+        <v>1389.5</v>
       </c>
       <c r="N4" t="n">
-        <v>1368.691310067595</v>
+        <v>1370</v>
       </c>
       <c r="O4" t="n">
-        <v>1342.086381794076</v>
+        <v>1342.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1361.206349845249</v>
+        <v>1356.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>1365.948408501049</v>
+        <v>1363.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1387.96869083661</v>
+        <v>1379.9</v>
       </c>
       <c r="S4" t="n">
-        <v>1337.178039868084</v>
+        <v>1334.3</v>
       </c>
       <c r="T4" t="n">
-        <v>1321.937537093541</v>
+        <v>1321.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1365.365405811919</v>
+        <v>1352.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1341.084209407329</v>
+        <v>1335.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1353.004332757791</v>
+        <v>1346.1</v>
       </c>
       <c r="X4" t="n">
-        <v>1335.835353486471</v>
+        <v>1335.1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1353.153232713001</v>
+        <v>1348.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>1360.880387656086</v>
+        <v>1353.8</v>
       </c>
     </row>
     <row r="5">
@@ -4976,79 +5386,79 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>504.503735861391</v>
+        <v>503.5</v>
       </c>
       <c r="C5" t="n">
-        <v>503.0958101056523</v>
+        <v>501.7</v>
       </c>
       <c r="D5" t="n">
-        <v>502.1087192738591</v>
+        <v>501.2</v>
       </c>
       <c r="E5" t="n">
-        <v>516.0847552004376</v>
+        <v>511.4</v>
       </c>
       <c r="F5" t="n">
-        <v>503.8838108148624</v>
+        <v>502</v>
       </c>
       <c r="G5" t="n">
-        <v>495.3218246806677</v>
+        <v>495.1</v>
       </c>
       <c r="H5" t="n">
-        <v>506.6414808174814</v>
+        <v>503.5</v>
       </c>
       <c r="I5" t="n">
-        <v>491.6612254231641</v>
+        <v>491.7</v>
       </c>
       <c r="J5" t="n">
-        <v>500.2218185652278</v>
+        <v>498.1</v>
       </c>
       <c r="K5" t="n">
-        <v>484.7136357591991</v>
+        <v>485.8</v>
       </c>
       <c r="L5" t="n">
-        <v>491.1249174305948</v>
+        <v>491.3</v>
       </c>
       <c r="M5" t="n">
-        <v>497.5593172092532</v>
+        <v>495.4</v>
       </c>
       <c r="N5" t="n">
-        <v>498.0689292835137</v>
+        <v>495.1</v>
       </c>
       <c r="O5" t="n">
-        <v>497.4343182062154</v>
+        <v>495.3</v>
       </c>
       <c r="P5" t="n">
-        <v>495.7245714990602</v>
+        <v>494.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>490.2811146779715</v>
+        <v>488.9</v>
       </c>
       <c r="R5" t="n">
-        <v>483.3288028284092</v>
+        <v>483.7</v>
       </c>
       <c r="S5" t="n">
-        <v>486.9706418490649</v>
+        <v>486.2</v>
       </c>
       <c r="T5" t="n">
-        <v>491.0222061634953</v>
+        <v>489.9</v>
       </c>
       <c r="U5" t="n">
-        <v>501.0808640157932</v>
+        <v>497.7</v>
       </c>
       <c r="V5" t="n">
-        <v>495.7874437157258</v>
+        <v>493.4</v>
       </c>
       <c r="W5" t="n">
-        <v>480.8214547701716</v>
+        <v>481.6</v>
       </c>
       <c r="X5" t="n">
-        <v>490.5743404792897</v>
+        <v>488.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>485.3702755214483</v>
+        <v>484.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>484.704354777666</v>
+        <v>483.9</v>
       </c>
     </row>
     <row r="6">
@@ -5056,79 +5466,79 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>220.7461198032251</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>216.6632627775616</v>
+        <v>215.1</v>
       </c>
       <c r="D6" t="n">
-        <v>217.677783341584</v>
+        <v>215.7</v>
       </c>
       <c r="E6" t="n">
-        <v>219.737424130258</v>
+        <v>217.3</v>
       </c>
       <c r="F6" t="n">
-        <v>221.8129022030749</v>
+        <v>219</v>
       </c>
       <c r="G6" t="n">
-        <v>215.9686669610144</v>
+        <v>214.1</v>
       </c>
       <c r="H6" t="n">
-        <v>216.7337474395577</v>
+        <v>214.7</v>
       </c>
       <c r="I6" t="n">
-        <v>215.4661797047319</v>
+        <v>214.1</v>
       </c>
       <c r="J6" t="n">
-        <v>215.2306816141811</v>
+        <v>213.9</v>
       </c>
       <c r="K6" t="n">
-        <v>217.880771649647</v>
+        <v>215.2</v>
       </c>
       <c r="L6" t="n">
-        <v>218.133437260719</v>
+        <v>215.1</v>
       </c>
       <c r="M6" t="n">
-        <v>215.5904227726055</v>
+        <v>213.5</v>
       </c>
       <c r="N6" t="n">
-        <v>219.5257254214879</v>
+        <v>216.7</v>
       </c>
       <c r="O6" t="n">
-        <v>214.3843763850908</v>
+        <v>212</v>
       </c>
       <c r="P6" t="n">
-        <v>211.8055749153305</v>
+        <v>210.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>216.2299166090993</v>
+        <v>213.9</v>
       </c>
       <c r="R6" t="n">
-        <v>219.2698329824783</v>
+        <v>216.1</v>
       </c>
       <c r="S6" t="n">
-        <v>212.0342492287446</v>
+        <v>210</v>
       </c>
       <c r="T6" t="n">
-        <v>215.0154927524208</v>
+        <v>211.9</v>
       </c>
       <c r="U6" t="n">
-        <v>203.9889328349473</v>
+        <v>203.6</v>
       </c>
       <c r="V6" t="n">
-        <v>213.1344013492119</v>
+        <v>210.5</v>
       </c>
       <c r="W6" t="n">
-        <v>212.3470233790555</v>
+        <v>210.2</v>
       </c>
       <c r="X6" t="n">
-        <v>212.4313219428873</v>
+        <v>210.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>213.87627288715</v>
+        <v>211.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>208.1113812315583</v>
+        <v>207.3</v>
       </c>
     </row>
     <row r="7">
@@ -5136,79 +5546,79 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>380.2983882297343</v>
+        <v>377.3</v>
       </c>
       <c r="C7" t="n">
-        <v>374.2747042267771</v>
+        <v>373.5</v>
       </c>
       <c r="D7" t="n">
-        <v>372.3208108860192</v>
+        <v>371.9</v>
       </c>
       <c r="E7" t="n">
-        <v>374.3493339298786</v>
+        <v>373.6</v>
       </c>
       <c r="F7" t="n">
-        <v>381.4097213781409</v>
+        <v>379</v>
       </c>
       <c r="G7" t="n">
-        <v>382.4158911588688</v>
+        <v>380.7</v>
       </c>
       <c r="H7" t="n">
-        <v>378.4916718284533</v>
+        <v>377.8</v>
       </c>
       <c r="I7" t="n">
-        <v>385.235581908166</v>
+        <v>383.3</v>
       </c>
       <c r="J7" t="n">
-        <v>383.3233856999593</v>
+        <v>381.9</v>
       </c>
       <c r="K7" t="n">
-        <v>391.7112294806747</v>
+        <v>389.2</v>
       </c>
       <c r="L7" t="n">
-        <v>382.0190342289881</v>
+        <v>381.5</v>
       </c>
       <c r="M7" t="n">
-        <v>385.6879062732492</v>
+        <v>384.7</v>
       </c>
       <c r="N7" t="n">
-        <v>387.324948066486</v>
+        <v>386.4</v>
       </c>
       <c r="O7" t="n">
-        <v>381.91022625227</v>
+        <v>382.3</v>
       </c>
       <c r="P7" t="n">
-        <v>390.1186564189822</v>
+        <v>388.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>393.1113286003432</v>
+        <v>391.4</v>
       </c>
       <c r="R7" t="n">
-        <v>391.9077355263499</v>
+        <v>390.5</v>
       </c>
       <c r="S7" t="n">
-        <v>393.746722826956</v>
+        <v>392.6</v>
       </c>
       <c r="T7" t="n">
-        <v>386.3501989005773</v>
+        <v>386.7</v>
       </c>
       <c r="U7" t="n">
-        <v>390.2840228176301</v>
+        <v>389.4</v>
       </c>
       <c r="V7" t="n">
-        <v>391.4091741603832</v>
+        <v>390.4</v>
       </c>
       <c r="W7" t="n">
-        <v>391.0568371091514</v>
+        <v>390.6</v>
       </c>
       <c r="X7" t="n">
-        <v>395.9266806056718</v>
+        <v>394.7</v>
       </c>
       <c r="Y7" t="n">
-        <v>399.3795544225135</v>
+        <v>397.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>405.6733282174756</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8">
@@ -5216,79 +5626,79 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>2496.891360027633</v>
+        <v>2491.1</v>
       </c>
       <c r="C8" t="n">
-        <v>2460.827304808399</v>
+        <v>2469</v>
       </c>
       <c r="D8" t="n">
-        <v>2522.358591362245</v>
+        <v>2516.1</v>
       </c>
       <c r="E8" t="n">
-        <v>2520.644377046963</v>
+        <v>2513.8</v>
       </c>
       <c r="F8" t="n">
-        <v>2588.811818479447</v>
+        <v>2563.7</v>
       </c>
       <c r="G8" t="n">
-        <v>2554.782539645865</v>
+        <v>2549.7</v>
       </c>
       <c r="H8" t="n">
-        <v>2569.959512963055</v>
+        <v>2561.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2546.495844095517</v>
+        <v>2540.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2511.829719562081</v>
+        <v>2514.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2625.187373910699</v>
+        <v>2609.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2626.170002043378</v>
+        <v>2613.6</v>
       </c>
       <c r="M8" t="n">
-        <v>2614.255094488228</v>
+        <v>2601.5</v>
       </c>
       <c r="N8" t="n">
-        <v>2548.542200940526</v>
+        <v>2549.1</v>
       </c>
       <c r="O8" t="n">
-        <v>2665.047499211178</v>
+        <v>2647.3</v>
       </c>
       <c r="P8" t="n">
-        <v>2576.838215317445</v>
+        <v>2581.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>2618.194028960041</v>
+        <v>2607</v>
       </c>
       <c r="R8" t="n">
-        <v>2668.224088234065</v>
+        <v>2644.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2609.432113985198</v>
+        <v>2610.6</v>
       </c>
       <c r="T8" t="n">
-        <v>2635.073193533367</v>
+        <v>2632.9</v>
       </c>
       <c r="U8" t="n">
-        <v>2661.350807032338</v>
+        <v>2653.8</v>
       </c>
       <c r="V8" t="n">
-        <v>2637.073274433562</v>
+        <v>2634.3</v>
       </c>
       <c r="W8" t="n">
-        <v>2591.681761662384</v>
+        <v>2597.3</v>
       </c>
       <c r="X8" t="n">
-        <v>2630.727290720211</v>
+        <v>2623.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>2590.028942398145</v>
+        <v>2591.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>2643.503043912424</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="9">
@@ -5296,79 +5706,79 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>2021.849914709946</v>
+        <v>1997.1</v>
       </c>
       <c r="C9" t="n">
-        <v>2029.715645090181</v>
+        <v>2002</v>
       </c>
       <c r="D9" t="n">
-        <v>2053.841571109251</v>
+        <v>2019</v>
       </c>
       <c r="E9" t="n">
-        <v>2007.494430771375</v>
+        <v>1985.6</v>
       </c>
       <c r="F9" t="n">
-        <v>2046.76689361683</v>
+        <v>2015.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2081.301947294123</v>
+        <v>2043</v>
       </c>
       <c r="H9" t="n">
-        <v>2009.631547662451</v>
+        <v>1990</v>
       </c>
       <c r="I9" t="n">
-        <v>2064.641780573391</v>
+        <v>2033.4</v>
       </c>
       <c r="J9" t="n">
-        <v>2066.502004209656</v>
+        <v>2034.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2101.678898139834</v>
+        <v>2066.2</v>
       </c>
       <c r="L9" t="n">
-        <v>2040.583851950331</v>
+        <v>2018.4</v>
       </c>
       <c r="M9" t="n">
-        <v>2049.151902641519</v>
+        <v>2027.4</v>
       </c>
       <c r="N9" t="n">
-        <v>2106.068349808203</v>
+        <v>2072.1</v>
       </c>
       <c r="O9" t="n">
-        <v>2099.414993328658</v>
+        <v>2066.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2098.24788512719</v>
+        <v>2066.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2118.218875325745</v>
+        <v>2085.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2092.235366555444</v>
+        <v>2065.9</v>
       </c>
       <c r="S9" t="n">
-        <v>2136.078633595541</v>
+        <v>2103.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2127.411952357047</v>
+        <v>2094.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2097.585355575154</v>
+        <v>2071.4</v>
       </c>
       <c r="V9" t="n">
-        <v>2167.42066827085</v>
+        <v>2124.1</v>
       </c>
       <c r="W9" t="n">
-        <v>2142.253809723799</v>
+        <v>2108</v>
       </c>
       <c r="X9" t="n">
-        <v>2109.752732441822</v>
+        <v>2086.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>2161.458123903271</v>
+        <v>2125.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>2115.316491850732</v>
+        <v>2090.6</v>
       </c>
     </row>
     <row r="10">
@@ -5376,79 +5786,79 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>23510.7787855585</v>
+        <v>23308.3</v>
       </c>
       <c r="C10" t="n">
-        <v>24145.80739560259</v>
+        <v>23810.2</v>
       </c>
       <c r="D10" t="n">
-        <v>23945.94872336816</v>
+        <v>23651.6</v>
       </c>
       <c r="E10" t="n">
-        <v>24105.32908752647</v>
+        <v>23780.2</v>
       </c>
       <c r="F10" t="n">
-        <v>24456.06771877287</v>
+        <v>24050.7</v>
       </c>
       <c r="G10" t="n">
-        <v>23843.30728639459</v>
+        <v>23596.7</v>
       </c>
       <c r="H10" t="n">
-        <v>23697.42934112041</v>
+        <v>23488.5</v>
       </c>
       <c r="I10" t="n">
-        <v>23784.12635223121</v>
+        <v>23584.2</v>
       </c>
       <c r="J10" t="n">
-        <v>23805.3891796037</v>
+        <v>23600</v>
       </c>
       <c r="K10" t="n">
-        <v>24010.75072630388</v>
+        <v>23750.4</v>
       </c>
       <c r="L10" t="n">
-        <v>24005.04016372374</v>
+        <v>23715</v>
       </c>
       <c r="M10" t="n">
-        <v>24112.78301350445</v>
+        <v>23826.1</v>
       </c>
       <c r="N10" t="n">
-        <v>24398.60974805798</v>
+        <v>24069.2</v>
       </c>
       <c r="O10" t="n">
-        <v>23954.86963188774</v>
+        <v>23688.7</v>
       </c>
       <c r="P10" t="n">
-        <v>24368.89816242436</v>
+        <v>23995.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>24077.88641031575</v>
+        <v>23830.2</v>
       </c>
       <c r="R10" t="n">
-        <v>24943.05369606543</v>
+        <v>24471.9</v>
       </c>
       <c r="S10" t="n">
-        <v>24251.598541532</v>
+        <v>23938.4</v>
       </c>
       <c r="T10" t="n">
-        <v>23705.88025029821</v>
+        <v>23504.3</v>
       </c>
       <c r="U10" t="n">
-        <v>23595.94472380713</v>
+        <v>23410.6</v>
       </c>
       <c r="V10" t="n">
-        <v>24090.92608188196</v>
+        <v>23789.9</v>
       </c>
       <c r="W10" t="n">
-        <v>24006.32688595984</v>
+        <v>23756.5</v>
       </c>
       <c r="X10" t="n">
-        <v>24396.7633262346</v>
+        <v>24075.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>24376.27928750586</v>
+        <v>24072.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>24168.36713636864</v>
+        <v>23906</v>
       </c>
     </row>
     <row r="11">
@@ -5456,79 +5866,79 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>173.2450203840194</v>
+        <v>176.3</v>
       </c>
       <c r="C11" t="n">
-        <v>175.9847229620977</v>
+        <v>178.4</v>
       </c>
       <c r="D11" t="n">
-        <v>174.3336544121995</v>
+        <v>177</v>
       </c>
       <c r="E11" t="n">
-        <v>171.5905517363487</v>
+        <v>175</v>
       </c>
       <c r="F11" t="n">
-        <v>174.8648538486428</v>
+        <v>177.6</v>
       </c>
       <c r="G11" t="n">
-        <v>177.1090734135416</v>
+        <v>179.8</v>
       </c>
       <c r="H11" t="n">
-        <v>174.4240997101361</v>
+        <v>177.7</v>
       </c>
       <c r="I11" t="n">
-        <v>177.5525791197846</v>
+        <v>180.3</v>
       </c>
       <c r="J11" t="n">
-        <v>177.3494436726173</v>
+        <v>180.2</v>
       </c>
       <c r="K11" t="n">
-        <v>178.0022192860314</v>
+        <v>181.5</v>
       </c>
       <c r="L11" t="n">
-        <v>180.3255573245206</v>
+        <v>183</v>
       </c>
       <c r="M11" t="n">
-        <v>181.6920939699488</v>
+        <v>184.3</v>
       </c>
       <c r="N11" t="n">
-        <v>183.758115060013</v>
+        <v>186.1</v>
       </c>
       <c r="O11" t="n">
-        <v>184.4773243575187</v>
+        <v>186.9</v>
       </c>
       <c r="P11" t="n">
-        <v>179.1619248032678</v>
+        <v>182.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>181.599185211815</v>
+        <v>185.1</v>
       </c>
       <c r="R11" t="n">
-        <v>184.8012802466647</v>
+        <v>187.5</v>
       </c>
       <c r="S11" t="n">
-        <v>187.8957038540988</v>
+        <v>190.6</v>
       </c>
       <c r="T11" t="n">
-        <v>187.0244561974122</v>
+        <v>189.7</v>
       </c>
       <c r="U11" t="n">
-        <v>194.090578556744</v>
+        <v>195</v>
       </c>
       <c r="V11" t="n">
-        <v>187.1490140450001</v>
+        <v>189.8</v>
       </c>
       <c r="W11" t="n">
-        <v>189.289069939357</v>
+        <v>191.7</v>
       </c>
       <c r="X11" t="n">
-        <v>189.7638658240807</v>
+        <v>192.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>189.4442694851042</v>
+        <v>192.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>186.906238720256</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="12">
@@ -5536,79 +5946,79 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>891.5078901097343</v>
+        <v>899.3</v>
       </c>
       <c r="C12" t="n">
-        <v>879.8039312654183</v>
+        <v>888.1</v>
       </c>
       <c r="D12" t="n">
-        <v>887.3809579838202</v>
+        <v>894.2</v>
       </c>
       <c r="E12" t="n">
-        <v>909.5387632757561</v>
+        <v>910.6</v>
       </c>
       <c r="F12" t="n">
-        <v>863.6118757460252</v>
+        <v>875.5</v>
       </c>
       <c r="G12" t="n">
-        <v>874.4960439323892</v>
+        <v>879.7</v>
       </c>
       <c r="H12" t="n">
-        <v>850.5677507020032</v>
+        <v>861.6</v>
       </c>
       <c r="I12" t="n">
-        <v>857.7684165854723</v>
+        <v>865.8</v>
       </c>
       <c r="J12" t="n">
-        <v>873.9264305080264</v>
+        <v>878.1</v>
       </c>
       <c r="K12" t="n">
-        <v>843.9202016162443</v>
+        <v>850.5</v>
       </c>
       <c r="L12" t="n">
-        <v>836.9587436070977</v>
+        <v>846.4</v>
       </c>
       <c r="M12" t="n">
-        <v>836.0314092304212</v>
+        <v>844.5</v>
       </c>
       <c r="N12" t="n">
-        <v>845.4536174039833</v>
+        <v>850.5</v>
       </c>
       <c r="O12" t="n">
-        <v>826.652368433148</v>
+        <v>835.1</v>
       </c>
       <c r="P12" t="n">
-        <v>836.127758276063</v>
+        <v>842.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>826.8854166971337</v>
+        <v>833.4</v>
       </c>
       <c r="R12" t="n">
-        <v>819.9714195226589</v>
+        <v>828.1</v>
       </c>
       <c r="S12" t="n">
-        <v>831.5280089752858</v>
+        <v>832.9</v>
       </c>
       <c r="T12" t="n">
-        <v>821.2534322085256</v>
+        <v>826.2</v>
       </c>
       <c r="U12" t="n">
-        <v>797.026937755036</v>
+        <v>808.4</v>
       </c>
       <c r="V12" t="n">
-        <v>816.8769411771178</v>
+        <v>822.9</v>
       </c>
       <c r="W12" t="n">
-        <v>804.2336962443071</v>
+        <v>812.3</v>
       </c>
       <c r="X12" t="n">
-        <v>814.522533095643</v>
+        <v>818.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>796.8140460648469</v>
+        <v>805.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>805.1648755333982</v>
+        <v>811.9</v>
       </c>
     </row>
     <row r="13">
@@ -5616,79 +6026,79 @@
         <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>1086.991183134066</v>
+        <v>1081.8</v>
       </c>
       <c r="C13" t="n">
-        <v>1105.547043816369</v>
+        <v>1097.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1105.613197955739</v>
+        <v>1097.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1101.300244911298</v>
+        <v>1094.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1131.529271995915</v>
+        <v>1116.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1128.089763772783</v>
+        <v>1117.3</v>
       </c>
       <c r="H13" t="n">
-        <v>1105.647874371893</v>
+        <v>1100.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1129.034521405954</v>
+        <v>1116.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1145.173043567071</v>
+        <v>1128.5</v>
       </c>
       <c r="K13" t="n">
-        <v>1142.027848178264</v>
+        <v>1129</v>
       </c>
       <c r="L13" t="n">
-        <v>1113.222000008633</v>
+        <v>1109</v>
       </c>
       <c r="M13" t="n">
-        <v>1121.496864000493</v>
+        <v>1113.7</v>
       </c>
       <c r="N13" t="n">
-        <v>1139.268681077283</v>
+        <v>1125.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1127.665786610856</v>
+        <v>1120.6</v>
       </c>
       <c r="P13" t="n">
-        <v>1143.381177790528</v>
+        <v>1132.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>1138.357785354095</v>
+        <v>1126.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1115.327990621125</v>
+        <v>1109.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1138.161246168817</v>
+        <v>1128.8</v>
       </c>
       <c r="T13" t="n">
-        <v>1099.972101234701</v>
+        <v>1101.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1132.669920060715</v>
+        <v>1126.7</v>
       </c>
       <c r="V13" t="n">
-        <v>1141.018435671906</v>
+        <v>1132.3</v>
       </c>
       <c r="W13" t="n">
-        <v>1121.920497237667</v>
+        <v>1116.8</v>
       </c>
       <c r="X13" t="n">
-        <v>1155.670606202364</v>
+        <v>1140.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1111.769899567801</v>
+        <v>1107.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>1127.481878496764</v>
+        <v>1119.5</v>
       </c>
     </row>
     <row r="14">
@@ -5696,79 +6106,79 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>86.38409403915772</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>88.64088153591672</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>87.58397858596592</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>86.39101723404725</v>
+        <v>85.5</v>
       </c>
       <c r="F14" t="n">
-        <v>87.75203172493886</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>87.38908728600016</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>86.55290807877951</v>
+        <v>85.5</v>
       </c>
       <c r="I14" t="n">
-        <v>86.79144216998715</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>86.31783711684409</v>
+        <v>85.2</v>
       </c>
       <c r="K14" t="n">
-        <v>86.76625340667871</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>87.79800017722198</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>88.29732691267489</v>
+        <v>86.7</v>
       </c>
       <c r="N14" t="n">
-        <v>84.91029069450441</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>89.10793036322656</v>
+        <v>87.3</v>
       </c>
       <c r="P14" t="n">
-        <v>84.84874973890226</v>
+        <v>84.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>85.98698406119672</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="R14" t="n">
-        <v>86.75204754164741</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>86.64490109154853</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>86.13669880629078</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>86.74676696924008</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>86.27176980563615</v>
+        <v>85.2</v>
       </c>
       <c r="W14" t="n">
-        <v>85.7429986546352</v>
+        <v>84.7</v>
       </c>
       <c r="X14" t="n">
-        <v>86.7981454895741</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y14" t="n">
-        <v>86.11083399357969</v>
+        <v>84.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>85.20771444079223</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="15">
@@ -5776,79 +6186,79 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>81.35935333294833</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>80.3567568624313</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>78.82232776154525</v>
+        <v>78.8</v>
       </c>
       <c r="E15" t="n">
-        <v>79.21804925930367</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>80.61046622262295</v>
+        <v>80.2</v>
       </c>
       <c r="G15" t="n">
-        <v>78.31348019567312</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>77.7245486363114</v>
+        <v>77.5</v>
       </c>
       <c r="I15" t="n">
-        <v>78.27763095688665</v>
+        <v>78</v>
       </c>
       <c r="J15" t="n">
-        <v>79.36604021341397</v>
+        <v>78.8</v>
       </c>
       <c r="K15" t="n">
-        <v>75.45762753178947</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>76.07376708741496</v>
+        <v>75.7</v>
       </c>
       <c r="M15" t="n">
-        <v>75.81272748337045</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>76.2170392776037</v>
+        <v>76</v>
       </c>
       <c r="O15" t="n">
-        <v>75.46184319405579</v>
+        <v>75</v>
       </c>
       <c r="P15" t="n">
-        <v>75.21752515714431</v>
+        <v>74.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>75.89195081864652</v>
+        <v>75.5</v>
       </c>
       <c r="R15" t="n">
-        <v>76.33565730630518</v>
+        <v>75.8</v>
       </c>
       <c r="S15" t="n">
-        <v>73.07772604076578</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>73.25771434904782</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>72.23000294422539</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>72.94573981356385</v>
+        <v>72.7</v>
       </c>
       <c r="W15" t="n">
-        <v>72.94521378246964</v>
+        <v>72.8</v>
       </c>
       <c r="X15" t="n">
-        <v>73.53969665960773</v>
+        <v>73.3</v>
       </c>
       <c r="Y15" t="n">
-        <v>74.144464829984</v>
+        <v>73.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>72.7329785841257</v>
+        <v>72.7</v>
       </c>
     </row>
   </sheetData>
@@ -5899,16 +6309,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31890685.84360693</v>
+        <v>31052693.06941877</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6951912342089134</v>
+        <v>0.6935674380392769</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5575476132176215</v>
+        <v>0.5579136904736154</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>
@@ -5921,16 +6331,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24609349.18030107</v>
+        <v>23899032.68323008</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5364639667403474</v>
+        <v>0.5337891574386108</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5975508073435446</v>
+        <v>0.5983089852382707</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -5943,16 +6353,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25942627.79938571</v>
+        <v>25425777.55179068</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.565528365458245</v>
+        <v>0.5678892763770873</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5895137914008687</v>
+        <v>0.5888766117692767</v>
       </c>
       <c r="F4" t="b">
         <v>0</v>
@@ -5965,16 +6375,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50449295.84264806</v>
+        <v>49207835.19310945</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.099753966214932</v>
+        <v>1.099065775391786</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4848722134274491</v>
+        <v>0.484971726919541</v>
       </c>
       <c r="F5" t="b">
         <v>0</v>
@@ -5987,16 +6397,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26124638.33701597</v>
+        <v>25406789.02861444</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5694960484022471</v>
+        <v>0.5674651643252902</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5884442692884269</v>
+        <v>0.5889909057538578</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -6009,16 +6419,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31254953.37546286</v>
+        <v>30560353.15610483</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6813327790686532</v>
+        <v>0.682570938265223</v>
       </c>
       <c r="E7" t="n">
-        <v>0.560697240290876</v>
+        <v>0.5604134900206549</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -6031,16 +6441,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>67419746.66590938</v>
+        <v>65902425.07794887</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.469696108907036</v>
+        <v>1.471942417996016</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4390916177123735</v>
+        <v>0.4388530019684514</v>
       </c>
       <c r="F8" t="b">
         <v>0</v>
@@ -6053,16 +6463,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23537142.28094554</v>
+        <v>22980446.21664007</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5130907209799489</v>
+        <v>0.5132723648748826</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6042871314272791</v>
+        <v>0.6042337924865535</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -6075,16 +6485,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>93688136.82485932</v>
+        <v>91713649.67966744</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.042325831103574</v>
+        <v>2.048440722978791</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3886896628167406</v>
+        <v>0.3882427632060966</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -6097,16 +6507,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>63495400.18590403</v>
+        <v>61856147.75442415</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.384148520301468</v>
+        <v>1.381568092310324</v>
       </c>
       <c r="E11" t="n">
-        <v>0.4484874203779403</v>
+        <v>0.4487805467805362</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -6119,7 +6529,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45873256.55781125</v>
+        <v>44772420.62748086</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -6188,19 +6598,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5828.797878959536</v>
+        <v>5766.715885714287</v>
       </c>
       <c r="C2" t="n">
-        <v>366.6006749784886</v>
+        <v>364.8417142857143</v>
       </c>
       <c r="D2" t="n">
-        <v>6195.398553938025</v>
+        <v>6131.557600000001</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.570094108516167</v>
+        <v>-1.572677138019948</v>
       </c>
       <c r="F2" t="n">
-        <v>0.147466162342779</v>
+        <v>0.1468689788991523</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -6213,19 +6623,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4940.237571538039</v>
+        <v>4883.975314285715</v>
       </c>
       <c r="C3" t="n">
-        <v>736.8341364041124</v>
+        <v>732.6502857142858</v>
       </c>
       <c r="D3" t="n">
-        <v>5677.071707942151</v>
+        <v>5616.625600000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.286820641559092</v>
+        <v>-1.287679543384453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2271462003970856</v>
+        <v>0.2268585836851959</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -6238,19 +6648,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4793.454749831032</v>
+        <v>4730.771657142858</v>
       </c>
       <c r="C4" t="n">
-        <v>797.9936454486984</v>
+        <v>796.4851428571429</v>
       </c>
       <c r="D4" t="n">
-        <v>5591.448395279731</v>
+        <v>5527.256800000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.242578903000419</v>
+        <v>-1.240949662930497</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2423709622040996</v>
+        <v>0.2429471237350457</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -6263,19 +6673,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4269.609504673539</v>
+        <v>4216.363885714286</v>
       </c>
       <c r="C5" t="n">
-        <v>1016.262497597654</v>
+        <v>1010.821714285714</v>
       </c>
       <c r="D5" t="n">
-        <v>5285.872002271193</v>
+        <v>5227.185600000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.08954232463289</v>
+        <v>-1.088905145091741</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3014735104909068</v>
+        <v>0.3017411583244411</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -6288,19 +6698,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3446.129724898047</v>
+        <v>3400.960457142858</v>
       </c>
       <c r="C6" t="n">
-        <v>785.0241183544342</v>
+        <v>783.7464</v>
       </c>
       <c r="D6" t="n">
-        <v>4231.153843252481</v>
+        <v>4184.706857142858</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8617551951946382</v>
+        <v>0.8606750668145231</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4090110624938978</v>
+        <v>0.4095781841667187</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -6313,19 +6723,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3411.89536182232</v>
+        <v>3374.120228571429</v>
       </c>
       <c r="C7" t="n">
-        <v>804.9941634819427</v>
+        <v>799.4032000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>4216.889525304262</v>
+        <v>4173.52342857143</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8525687780958346</v>
+        <v>0.8533858764344532</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4138516282270882</v>
+        <v>0.4134194952847382</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -6334,23 +6744,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3121.790750722523</v>
+        <v>3080.168228571429</v>
       </c>
       <c r="C8" t="n">
-        <v>974.2218532901564</v>
+        <v>970.8751999999998</v>
       </c>
       <c r="D8" t="n">
-        <v>4096.01260401268</v>
+        <v>4051.043428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7755014082989631</v>
+        <v>0.774354424491552</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4559912622117772</v>
+        <v>0.456638941405678</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -6359,23 +6769,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3110.997087889346</v>
+        <v>3079.028571428572</v>
       </c>
       <c r="C9" t="n">
-        <v>980.51815660951</v>
+        <v>971.5400000000002</v>
       </c>
       <c r="D9" t="n">
-        <v>4091.515244498856</v>
+        <v>4050.568571428572</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7726597248794179</v>
+        <v>0.7740507449012427</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4575969980306159</v>
+        <v>0.4568105233056091</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -6388,19 +6798,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3030.74734420116</v>
+        <v>2987.134628571429</v>
       </c>
       <c r="C10" t="n">
-        <v>1027.330507094285</v>
+        <v>1025.1448</v>
       </c>
       <c r="D10" t="n">
-        <v>4058.077851295445</v>
+        <v>4012.279428571429</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7515869283459204</v>
+        <v>0.7496298049530131</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4696185730260661</v>
+        <v>0.4707452394681902</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -6413,19 +6823,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2964.620584473138</v>
+        <v>2929.722514285715</v>
       </c>
       <c r="C11" t="n">
-        <v>1065.904450268965</v>
+        <v>1058.6352</v>
       </c>
       <c r="D11" t="n">
-        <v>4030.525034742102</v>
+        <v>3988.357714285715</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7342937331160553</v>
+        <v>0.7344368905838197</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4796333595961253</v>
+        <v>0.4795499047435794</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -6504,19 +6914,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5762.256485128881</v>
+        <v>5696.626833333335</v>
       </c>
       <c r="E2" t="n">
-        <v>13329.44183309649</v>
+        <v>13184.424</v>
       </c>
       <c r="F2" t="n">
-        <v>575.4916245059256</v>
+        <v>571.4266666666666</v>
       </c>
       <c r="G2" t="n">
-        <v>1439.369701165715</v>
+        <v>1429.646666666667</v>
       </c>
       <c r="H2" t="n">
-        <v>209.9324628329108</v>
+        <v>209.903</v>
       </c>
     </row>
     <row r="3">
@@ -6536,19 +6946,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5730.667914430104</v>
+        <v>5666.628166666668</v>
       </c>
       <c r="E3" t="n">
-        <v>12282.72504049959</v>
+        <v>12140.28</v>
       </c>
       <c r="F3" t="n">
-        <v>621.3033101189252</v>
+        <v>618.456</v>
       </c>
       <c r="G3" t="n">
-        <v>1130.597298466489</v>
+        <v>1118.574666666667</v>
       </c>
       <c r="H3" t="n">
-        <v>930.5113969460284</v>
+        <v>930.0070000000001</v>
       </c>
     </row>
     <row r="4">
@@ -6568,83 +6978,83 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5605.858717664655</v>
+        <v>5539.181833333335</v>
       </c>
       <c r="E4" t="n">
-        <v>12597.33001038526</v>
+        <v>12451.212</v>
       </c>
       <c r="F4" t="n">
-        <v>1063.566172980076</v>
+        <v>1060.234666666667</v>
       </c>
       <c r="G4" t="n">
-        <v>920.8606518760422</v>
+        <v>911.2866666666667</v>
       </c>
       <c r="H4" t="n">
-        <v>598.8142498001652</v>
+        <v>598.673</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TIME*RF_POWER</t>
+          <t>C3H6*PRESSURE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5530.993468855885</v>
+        <v>5459.64</v>
       </c>
       <c r="E5" t="n">
-        <v>13078.05570563365</v>
+        <v>12086.168</v>
       </c>
       <c r="F5" t="n">
-        <v>1606.960452807609</v>
+        <v>654.5306666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>600.3768550437858</v>
+        <v>1303.597333333333</v>
       </c>
       <c r="H5" t="n">
-        <v>191.2685399295156</v>
+        <v>791.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C3H6*PRESSURE</t>
+          <t>TIME*RF_POWER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5529.063906750423</v>
+        <v>5454.166166666668</v>
       </c>
       <c r="E6" t="n">
-        <v>12228.55797458408</v>
+        <v>12921.278</v>
       </c>
       <c r="F6" t="n">
-        <v>657.4146873959374</v>
+        <v>1605.077333333333</v>
       </c>
       <c r="G6" t="n">
-        <v>1309.414196847535</v>
+        <v>597.9093333333334</v>
       </c>
       <c r="H6" t="n">
-        <v>796.3987231602438</v>
+        <v>190.041</v>
       </c>
     </row>
     <row r="7">
@@ -6664,19 +7074,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5484.063653316077</v>
+        <v>5416.214833333334</v>
       </c>
       <c r="E7" t="n">
-        <v>12730.36484303794</v>
+        <v>12585.592</v>
       </c>
       <c r="F7" t="n">
-        <v>322.876775093364</v>
+        <v>321.5813333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>1838.75436120475</v>
+        <v>1828.868</v>
       </c>
       <c r="H7" t="n">
-        <v>399.393599892332</v>
+        <v>397.287</v>
       </c>
     </row>
     <row r="8">
@@ -6696,19 +7106,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-4902.638209836636</v>
+        <v>-4845.597166666668</v>
       </c>
       <c r="E8" t="n">
-        <v>338.3985053014167</v>
+        <v>339.0740000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>1398.10408528265</v>
+        <v>1393.184</v>
       </c>
       <c r="G8" t="n">
-        <v>9093.481655265274</v>
+        <v>8986.045333333335</v>
       </c>
       <c r="H8" t="n">
-        <v>347.910815573235</v>
+        <v>348.961</v>
       </c>
     </row>
     <row r="9">
@@ -6728,19 +7138,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-4833.596274725306</v>
+        <v>-4781.169500000002</v>
       </c>
       <c r="E9" t="n">
-        <v>301.0706594946264</v>
+        <v>299.35</v>
       </c>
       <c r="F9" t="n">
-        <v>1140.943166140153</v>
+        <v>1132.772</v>
       </c>
       <c r="G9" t="n">
-        <v>9261.072406907168</v>
+        <v>9161.476000000002</v>
       </c>
       <c r="H9" t="n">
-        <v>433.7523641020817</v>
+        <v>432.559</v>
       </c>
     </row>
     <row r="10">
@@ -6760,19 +7170,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-4734.707053183228</v>
+        <v>-4681.717166666668</v>
       </c>
       <c r="E10" t="n">
-        <v>236.7533552614537</v>
+        <v>235.514</v>
       </c>
       <c r="F10" t="n">
-        <v>8651.951100277685</v>
+        <v>8554.966666666669</v>
       </c>
       <c r="G10" t="n">
-        <v>1618.671846940639</v>
+        <v>1607.382666666667</v>
       </c>
       <c r="H10" t="n">
-        <v>564.4554855904154</v>
+        <v>563.4010000000001</v>
       </c>
     </row>
     <row r="11">
@@ -6792,19 +7202,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-4601.716709339836</v>
+        <v>-4556.218333333334</v>
       </c>
       <c r="E11" t="n">
-        <v>290.9204211769721</v>
+        <v>289.626</v>
       </c>
       <c r="F11" t="n">
-        <v>1518.270564372494</v>
+        <v>1515.490666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>8615.839723000674</v>
+        <v>8518.892000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>639.7564475165244</v>
+        <v>632.3200000000001</v>
       </c>
     </row>
     <row r="12">
@@ -6824,19 +7234,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-4567.141713984659</v>
+        <v>-4514.087166666667</v>
       </c>
       <c r="E12" t="n">
-        <v>669.8426952958145</v>
+        <v>664.394</v>
       </c>
       <c r="F12" t="n">
-        <v>1187.63513081864</v>
+        <v>1175.196</v>
       </c>
       <c r="G12" t="n">
-        <v>9015.224383039709</v>
+        <v>8918.113333333335</v>
       </c>
       <c r="H12" t="n">
-        <v>398.7333905932165</v>
+        <v>400.7410000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6856,19 +7266,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-4405.653764691499</v>
+        <v>-4351.4885</v>
       </c>
       <c r="E13" t="n">
-        <v>1116.162079235925</v>
+        <v>1116.614</v>
       </c>
       <c r="F13" t="n">
-        <v>564.2654777667735</v>
+        <v>561.8346666666666</v>
       </c>
       <c r="G13" t="n">
-        <v>9581.556203739425</v>
+        <v>9474.853333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>218.3520728872748</v>
+        <v>217.097</v>
       </c>
     </row>
     <row r="14">
@@ -6888,19 +7298,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4312.370717567288</v>
+        <v>-4264.207666666668</v>
       </c>
       <c r="E14" t="n">
-        <v>809.7285846428543</v>
+        <v>804.648</v>
       </c>
       <c r="F14" t="n">
-        <v>1172.398455395239</v>
+        <v>1172.142666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>8779.261602370983</v>
+        <v>8675.662666666669</v>
       </c>
       <c r="H14" t="n">
-        <v>517.1900379887928</v>
+        <v>514.742</v>
       </c>
     </row>
     <row r="15">
@@ -6920,19 +7330,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-4181.034472384008</v>
+        <v>-4131.244500000001</v>
       </c>
       <c r="E15" t="n">
-        <v>653.0034751870865</v>
+        <v>650.006</v>
       </c>
       <c r="F15" t="n">
-        <v>873.0378804659995</v>
+        <v>872.9066666666668</v>
       </c>
       <c r="G15" t="n">
-        <v>8883.745008674827</v>
+        <v>8778.757333333335</v>
       </c>
       <c r="H15" t="n">
-        <v>741.7104691857227</v>
+        <v>739.1690000000001</v>
       </c>
     </row>
     <row r="16">
@@ -6952,19 +7362,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-4160.611241668019</v>
+        <v>-4119.156500000001</v>
       </c>
       <c r="E16" t="n">
-        <v>755.561518727336</v>
+        <v>750.5359999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>804.6658514391665</v>
+        <v>805.8866666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>8958.078500752028</v>
+        <v>8860.685333333335</v>
       </c>
       <c r="H16" t="n">
-        <v>685.9603501278219</v>
+        <v>677.723</v>
       </c>
     </row>
     <row r="17">
@@ -6984,19 +7394,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-4064.925027380185</v>
+        <v>-4014.543000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>440.9565488416663</v>
+        <v>439.604</v>
       </c>
       <c r="F17" t="n">
-        <v>8515.815637890877</v>
+        <v>8418.906666666668</v>
       </c>
       <c r="G17" t="n">
-        <v>1047.68590657546</v>
+        <v>1039.269333333333</v>
       </c>
       <c r="H17" t="n">
-        <v>992.6949408642997</v>
+        <v>989.4860000000001</v>
       </c>
     </row>
     <row r="18">
@@ -7016,83 +7426,83 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-3942.21469182519</v>
+        <v>-3898.766166666667</v>
       </c>
       <c r="E18" t="n">
-        <v>1463.852941831638</v>
+        <v>1452.3</v>
       </c>
       <c r="F18" t="n">
-        <v>365.7549779154792</v>
+        <v>364.1386666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>9349.762295342283</v>
+        <v>9251.062666666669</v>
       </c>
       <c r="H18" t="n">
-        <v>367.2349477757457</v>
+        <v>365.369</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N2*TIME</t>
+          <t>SPACE*RF_POWER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-3910.324845687497</v>
+        <v>-3866.197166666668</v>
       </c>
       <c r="E19" t="n">
-        <v>1715.239069294479</v>
+        <v>1120.072</v>
       </c>
       <c r="F19" t="n">
-        <v>568.7247989608227</v>
+        <v>1017.677333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>9182.17154370039</v>
+        <v>8465.380000000003</v>
       </c>
       <c r="H19" t="n">
-        <v>215.007581991738</v>
+        <v>630.591</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPACE*RF_POWER</t>
+          <t>N2*TIME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-3909.623554824154</v>
+        <v>-3855.182500000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1133.729170435471</v>
+        <v>1715.446</v>
       </c>
       <c r="F20" t="n">
-        <v>1020.687970157961</v>
+        <v>564.9440000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>8563.26121184257</v>
+        <v>9075.632000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>630.9729019167514</v>
+        <v>214.765</v>
       </c>
     </row>
     <row r="21">
@@ -7112,19 +7522,19 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-3899.292311286888</v>
+        <v>-3846.216500000001</v>
       </c>
       <c r="E21" t="n">
-        <v>738.5602237153139</v>
+        <v>734.938</v>
       </c>
       <c r="F21" t="n">
-        <v>1141.823445205641</v>
+        <v>1128.166666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>8317.413187975113</v>
+        <v>8222.017333333335</v>
       </c>
       <c r="H21" t="n">
-        <v>922.0917868916644</v>
+        <v>922.8130000000001</v>
       </c>
     </row>
     <row r="22">
@@ -7144,19 +7554,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-3809.678899289139</v>
+        <v>-3769.551000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>1738.094082429581</v>
+        <v>1720.026</v>
       </c>
       <c r="F22" t="n">
-        <v>475.4675393961294</v>
+        <v>471.4413333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>9166.934868276987</v>
+        <v>9072.578666666668</v>
       </c>
       <c r="H22" t="n">
-        <v>284.9505266652579</v>
+        <v>284.8920000000001</v>
       </c>
     </row>
     <row r="23">
@@ -7176,19 +7586,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-3600.822344707529</v>
+        <v>-3558.058500000001</v>
       </c>
       <c r="E23" t="n">
-        <v>942.7634172955264</v>
+        <v>939.028</v>
       </c>
       <c r="F23" t="n">
-        <v>8181.277725588305</v>
+        <v>8085.957333333335</v>
       </c>
       <c r="G23" t="n">
-        <v>995.1941439532433</v>
+        <v>993.2146666666669</v>
       </c>
       <c r="H23" t="n">
-        <v>1032.063762830963</v>
+        <v>1024.027</v>
       </c>
     </row>
     <row r="24">
@@ -7208,19 +7618,19 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-3533.069976869139</v>
+        <v>-3481.319000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1487.673341438562</v>
+        <v>1483.748</v>
       </c>
       <c r="F24" t="n">
-        <v>8470.003952277877</v>
+        <v>8371.877333333336</v>
       </c>
       <c r="G24" t="n">
-        <v>784.7251894892339</v>
+        <v>775.2266666666668</v>
       </c>
       <c r="H24" t="n">
-        <v>700.9158465902714</v>
+        <v>700.7180000000001</v>
       </c>
     </row>
     <row r="25">
@@ -7240,19 +7650,19 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-3520.801189469698</v>
+        <v>-3476.339666666668</v>
       </c>
       <c r="E25" t="n">
-        <v>1401.95451800704</v>
+        <v>1397.606</v>
       </c>
       <c r="F25" t="n">
-        <v>689.0667434789005</v>
+        <v>687.4960000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>8527.149834565558</v>
+        <v>8429.305333333336</v>
       </c>
       <c r="H25" t="n">
-        <v>772.6596810980215</v>
+        <v>766.5160000000001</v>
       </c>
     </row>
     <row r="26">
@@ -7272,19 +7682,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3458.243071675079</v>
+        <v>3418.263000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>1541.84040735408</v>
+        <v>1537.86</v>
       </c>
       <c r="F26" t="n">
-        <v>684.3239069210886</v>
+        <v>683.3346666666666</v>
       </c>
       <c r="G26" t="n">
-        <v>595.8094839142074</v>
+        <v>593.9933333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>6654.779126831374</v>
+        <v>6575.994000000002</v>
       </c>
     </row>
     <row r="27">
@@ -7304,25 +7714,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-3444.366443042723</v>
+        <v>-3397.730333333334</v>
       </c>
       <c r="E27" t="n">
-        <v>1989.480209892422</v>
+        <v>1983.172</v>
       </c>
       <c r="F27" t="n">
-        <v>297.3829488886461</v>
+        <v>297.1186666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>8999.344116635093</v>
+        <v>8897.148000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>418.5139695458704</v>
+        <v>415.634</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AR*C3H6</t>
+          <t>AR*HE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -7332,29 +7742,29 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-3401.645657973252</v>
+        <v>3363.413500000001</v>
       </c>
       <c r="E28" t="n">
-        <v>888.5963513800081</v>
+        <v>1249.96</v>
       </c>
       <c r="F28" t="n">
-        <v>715.9759630040517</v>
+        <v>472.9373333333335</v>
       </c>
       <c r="G28" t="n">
-        <v>8217.389102865316</v>
+        <v>784.8186666666667</v>
       </c>
       <c r="H28" t="n">
-        <v>1241.477398542856</v>
+        <v>6734.623000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AR*HE</t>
+          <t>AR*C3H6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -7364,23 +7774,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3399.422417668386</v>
+        <v>-3360.851500000001</v>
       </c>
       <c r="E29" t="n">
-        <v>1257.368387181196</v>
+        <v>884.9159999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>470.1279391365931</v>
+        <v>716.3000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>795.951336228386</v>
+        <v>8122.032000000002</v>
       </c>
       <c r="H29" t="n">
-        <v>6807.555723520554</v>
+        <v>1231.713</v>
       </c>
     </row>
     <row r="30">
@@ -7400,19 +7810,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-3307.102148197409</v>
+        <v>-3269.074333333334</v>
       </c>
       <c r="E30" t="n">
-        <v>1290.454279891239</v>
+        <v>1274.714</v>
       </c>
       <c r="F30" t="n">
-        <v>481.3540858757451</v>
+        <v>482.5293333333334</v>
       </c>
       <c r="G30" t="n">
-        <v>8458.777805538726</v>
+        <v>8362.285333333335</v>
       </c>
       <c r="H30" t="n">
-        <v>1035.473315128413</v>
+        <v>1031.952</v>
       </c>
     </row>
     <row r="31">
@@ -7432,19 +7842,19 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3218.999439955024</v>
+        <v>3176.955666666667</v>
       </c>
       <c r="E31" t="n">
-        <v>1150.568390544199</v>
+        <v>1134.46</v>
       </c>
       <c r="F31" t="n">
-        <v>867.151333986384</v>
+        <v>861.8186666666667</v>
       </c>
       <c r="G31" t="n">
-        <v>574.6113454404383</v>
+        <v>576.032</v>
       </c>
       <c r="H31" t="n">
-        <v>6729.193168792671</v>
+        <v>6657.302000000001</v>
       </c>
     </row>
     <row r="32">
@@ -7464,19 +7874,19 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>3215.912761562974</v>
+        <v>3171.006833333333</v>
       </c>
       <c r="E32" t="n">
-        <v>1236.287213975721</v>
+        <v>1220.602</v>
       </c>
       <c r="F32" t="n">
-        <v>517.4654631527573</v>
+        <v>518.6040000000002</v>
       </c>
       <c r="G32" t="n">
-        <v>952.3159411311281</v>
+        <v>950.6573333333336</v>
       </c>
       <c r="H32" t="n">
-        <v>6665.319713434112</v>
+        <v>6590.673000000001</v>
       </c>
     </row>
     <row r="33">
@@ -7496,19 +7906,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>3179.962166149666</v>
+        <v>3150.346666666667</v>
       </c>
       <c r="E33" t="n">
-        <v>1385.115297898312</v>
+        <v>1383.218</v>
       </c>
       <c r="F33" t="n">
-        <v>700.2928902180525</v>
+        <v>697.0880000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>853.0972185160668</v>
+        <v>842.2466666666668</v>
       </c>
       <c r="H33" t="n">
-        <v>6528.19914313514</v>
+        <v>6456.810000000001</v>
       </c>
     </row>
     <row r="34">
@@ -7528,19 +7938,19 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-3117.384264170413</v>
+        <v>-3078.650666666667</v>
       </c>
       <c r="E34" t="n">
-        <v>1605.059249776909</v>
+        <v>1585.646</v>
       </c>
       <c r="F34" t="n">
-        <v>564.1574278312441</v>
+        <v>561.028</v>
       </c>
       <c r="G34" t="n">
-        <v>8249.041158948279</v>
+        <v>8154.997333333336</v>
       </c>
       <c r="H34" t="n">
-        <v>973.3708086617891</v>
+        <v>973.0780000000002</v>
       </c>
     </row>
     <row r="35">
@@ -7560,19 +7970,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-3085.50817495956</v>
+        <v>-3049.189000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>2337.171072488135</v>
+        <v>2318.858</v>
       </c>
       <c r="F35" t="n">
-        <v>218.3933687895187</v>
+        <v>218.4866666666667</v>
       </c>
       <c r="G35" t="n">
-        <v>8767.550208237952</v>
+        <v>8673.357333333335</v>
       </c>
       <c r="H35" t="n">
-        <v>477.756154620216</v>
+        <v>474.6079999999999</v>
       </c>
     </row>
     <row r="36">
@@ -7592,19 +8002,19 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3035.251426842349</v>
+        <v>3002.121666666667</v>
       </c>
       <c r="E36" t="n">
-        <v>1337.637213773868</v>
+        <v>1333.77</v>
       </c>
       <c r="F36" t="n">
-        <v>820.459369307897</v>
+        <v>819.3946666666667</v>
       </c>
       <c r="G36" t="n">
-        <v>884.7492745990299</v>
+        <v>875.2120000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>6438.074283817758</v>
+        <v>6365.080000000001</v>
       </c>
     </row>
     <row r="37">
@@ -7624,19 +8034,19 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-2954.389259021048</v>
+        <v>-2915.333166666668</v>
       </c>
       <c r="E37" t="n">
-        <v>1856.44537723975</v>
+        <v>1848.792</v>
       </c>
       <c r="F37" t="n">
-        <v>474.5872603306422</v>
+        <v>476.0466666666668</v>
       </c>
       <c r="G37" t="n">
-        <v>8224.155928410419</v>
+        <v>8128.514666666669</v>
       </c>
       <c r="H37" t="n">
-        <v>933.5192934592152</v>
+        <v>925.103</v>
       </c>
     </row>
     <row r="38">
@@ -7656,83 +8066,83 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2942.646124031002</v>
+        <v>2904.991833333333</v>
       </c>
       <c r="E38" t="n">
-        <v>983.1272465832532</v>
+        <v>982.234</v>
       </c>
       <c r="F38" t="n">
-        <v>652.9553662018883</v>
+        <v>651.4213333333333</v>
       </c>
       <c r="G38" t="n">
-        <v>1056.799347434973</v>
+        <v>1053.752</v>
       </c>
       <c r="H38" t="n">
-        <v>6611.919715115613</v>
+        <v>6532.923000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HE*SPACE</t>
+          <t>AR*NF3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2747.389090726954</v>
+        <v>2717.052666666667</v>
       </c>
       <c r="E39" t="n">
-        <v>1086.251086311026</v>
+        <v>617.1900000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>910.029536808499</v>
+        <v>894.784</v>
       </c>
       <c r="G39" t="n">
-        <v>1052.340026240924</v>
+        <v>920.8786666666666</v>
       </c>
       <c r="H39" t="n">
-        <v>6370.896658192305</v>
+        <v>6632.578000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AR*NF3</t>
+          <t>HE*SPACE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2744.459574413986</v>
+        <v>2708.474666666667</v>
       </c>
       <c r="E40" t="n">
-        <v>614.3552107820651</v>
+        <v>1070.624</v>
       </c>
       <c r="F40" t="n">
-        <v>898.8033900693471</v>
+        <v>904.3759999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>932.0867986151943</v>
+        <v>1050.642666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>6705.454126730448</v>
+        <v>6301.344000000001</v>
       </c>
     </row>
     <row r="41">
@@ -7752,19 +8162,19 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2740.886914275407</v>
+        <v>2702.880833333334</v>
       </c>
       <c r="E41" t="n">
-        <v>786.0383078397585</v>
+        <v>784.386</v>
       </c>
       <c r="F41" t="n">
-        <v>784.3479920308847</v>
+        <v>783.3200000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1099.677550257088</v>
+        <v>1096.309333333333</v>
       </c>
       <c r="H41" t="n">
-        <v>6579.761062999028</v>
+        <v>6501.005000000001</v>
       </c>
     </row>
     <row r="42">
@@ -7784,19 +8194,19 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2479.647003640785</v>
+        <v>2450.367666666667</v>
       </c>
       <c r="E42" t="n">
-        <v>802.8775279484865</v>
+        <v>798.774</v>
       </c>
       <c r="F42" t="n">
-        <v>1098.945242383526</v>
+        <v>1085.609333333333</v>
       </c>
       <c r="G42" t="n">
-        <v>1088.451403517936</v>
+        <v>1086.717333333333</v>
       </c>
       <c r="H42" t="n">
-        <v>6343.813125234547</v>
+        <v>6274.288</v>
       </c>
     </row>
     <row r="43">
@@ -7816,19 +8226,19 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2467.832767548688</v>
+        <v>2441.672</v>
       </c>
       <c r="E43" t="n">
-        <v>668.5222766975835</v>
+        <v>671.3020000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1266.53599402542</v>
+        <v>1261.04</v>
       </c>
       <c r="G43" t="n">
-        <v>895.9754213381821</v>
+        <v>884.8040000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>6429.654673763393</v>
+        <v>6357.886000000001</v>
       </c>
     </row>
     <row r="44">
@@ -7848,19 +8258,19 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2122.614689588151</v>
+        <v>2091.388</v>
       </c>
       <c r="E44" t="n">
-        <v>605.5253910626418</v>
+        <v>600.558</v>
       </c>
       <c r="F44" t="n">
-        <v>1308.533917782048</v>
+        <v>1308.202666666667</v>
       </c>
       <c r="G44" t="n">
-        <v>1230.513333640755</v>
+        <v>1217.753333333333</v>
       </c>
       <c r="H44" t="n">
-        <v>6178.751239536464</v>
+        <v>6108.174000000001</v>
       </c>
     </row>
     <row r="45">
@@ -7880,19 +8290,19 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2101.463106689171</v>
+        <v>2069.572333333334</v>
       </c>
       <c r="E45" t="n">
-        <v>355.2377254101448</v>
+        <v>353.462</v>
       </c>
       <c r="F45" t="n">
-        <v>1386.877938543498</v>
+        <v>1383.592</v>
       </c>
       <c r="G45" t="n">
-        <v>1104.831788863141</v>
+        <v>1096.697333333334</v>
       </c>
       <c r="H45" t="n">
-        <v>6339.398215374835</v>
+        <v>6265.972000000002</v>
       </c>
     </row>
     <row r="46">
@@ -7912,19 +8322,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1896.290063371675</v>
+        <v>1868.349666666667</v>
       </c>
       <c r="E46" t="n">
-        <v>284.2314393858983</v>
+        <v>284.962</v>
       </c>
       <c r="F46" t="n">
-        <v>1118.885904333458</v>
+        <v>1116.269333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>1587.019790857676</v>
+        <v>1574.417333333334</v>
       </c>
       <c r="H46" t="n">
-        <v>6214.254382548586</v>
+        <v>6142.424000000001</v>
       </c>
     </row>
   </sheetData>
@@ -7975,19 +8385,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.691034551242235</v>
+        <v>3.34260036063773</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>236.4935545841599</v>
+        <v>95.67784098741616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.041338951490516</v>
+        <v>0.06485869472457505</v>
       </c>
       <c r="F2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7997,16 +8407,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.962220579605335</v>
+        <v>2.119150177627428</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>125.7242416202463</v>
+        <v>60.65807809725966</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05662694247783161</v>
+        <v>0.08129542536593232</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -8019,19 +8429,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.666074786582786</v>
+        <v>3.756832778873711</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>234.8943217988936</v>
+        <v>107.5347365680334</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04147904034247805</v>
+        <v>0.06120190138717354</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8041,19 +8451,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.06375212804891</v>
+        <v>4.407663385396913</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>260.3744756027235</v>
+        <v>126.1639654803375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.039402688464051</v>
+        <v>0.05652869316426988</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8063,16 +8473,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3446907458458269</v>
+        <v>0.1510568746941142</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>22.08517384100614</v>
+        <v>4.323818009246573</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1334750288673053</v>
+        <v>0.2853721646461492</v>
       </c>
       <c r="F6" t="b">
         <v>0</v>
@@ -8085,16 +8495,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02793453827998301</v>
+        <v>0.02446719158559484</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.78983376118142</v>
+        <v>0.7003433893869859</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4086333816144101</v>
+        <v>0.5563912159325349</v>
       </c>
       <c r="F7" t="b">
         <v>0</v>
@@ -8107,19 +8517,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.535157399083493</v>
+        <v>4.419153297960609</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>290.5785570462736</v>
+        <v>126.4928501535321</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03730361221330764</v>
+        <v>0.05645554247923722</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8129,16 +8539,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6698903601063623</v>
+        <v>0.9234289543417797</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>42.92150350906304</v>
+        <v>26.4320227141459</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09642806496540125</v>
+        <v>0.1222998183419088</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -8151,16 +8561,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.1347134676954138</v>
+        <v>0.1592840749645329</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>8.63141928999948</v>
+        <v>4.559311539527461</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2088593376265934</v>
+        <v>0.2788335642145892</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -8173,16 +8583,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.215903698441542</v>
+        <v>2.802229504594784</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>141.9783356089842</v>
+        <v>80.21038713096803</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05330311075666577</v>
+        <v>0.07078963602572848</v>
       </c>
       <c r="F11" t="b">
         <v>0</v>
@@ -8195,7 +8605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.01560733677386004</v>
+        <v>0.03493599276636436</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -8264,19 +8674,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.275690184202877</v>
+        <v>1.231767735502435</v>
       </c>
       <c r="C2" t="n">
-        <v>3.851325876695743</v>
+        <v>3.389923346290732</v>
       </c>
       <c r="D2" t="n">
-        <v>5.127016060898621</v>
+        <v>4.621691081793166</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.7172712643119</v>
+        <v>-1.615265521781642</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1166839015318673</v>
+        <v>0.1373265156923052</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
@@ -8289,19 +8699,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.17568374751827</v>
+        <v>1.146780694285553</v>
       </c>
       <c r="C3" t="n">
-        <v>3.697047934061284</v>
+        <v>3.234204497750173</v>
       </c>
       <c r="D3" t="n">
-        <v>4.872731681579554</v>
+        <v>4.380985192035726</v>
       </c>
       <c r="E3" t="n">
-        <v>1.548622725843045</v>
+        <v>1.478343655061706</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1525136304839501</v>
+        <v>0.1701083483430979</v>
       </c>
       <c r="G3" t="b">
         <v>0</v>
@@ -8314,19 +8724,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.106867637183317</v>
+        <v>1.145125805543616</v>
       </c>
       <c r="C4" t="n">
-        <v>3.737190665090007</v>
+        <v>3.235169849516303</v>
       </c>
       <c r="D4" t="n">
-        <v>4.844058302273324</v>
+        <v>4.380295655059919</v>
       </c>
       <c r="E4" t="n">
-        <v>1.438507089512495</v>
+        <v>1.475745279716324</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1808425892558987</v>
+        <v>0.1707913424258531</v>
       </c>
       <c r="G4" t="b">
         <v>0</v>
@@ -8339,19 +8749,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.04564051727191</v>
+        <v>1.047581235225067</v>
       </c>
       <c r="C5" t="n">
-        <v>3.772906485038328</v>
+        <v>3.29207084886879</v>
       </c>
       <c r="D5" t="n">
-        <v>4.818547002310238</v>
+        <v>4.339652084093857</v>
       </c>
       <c r="E5" t="n">
-        <v>1.344058212236319</v>
+        <v>1.32668005545052</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2086272592760429</v>
+        <v>0.2141120389440786</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
@@ -8364,19 +8774,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7877774080640569</v>
+        <v>0.8876566565432191</v>
       </c>
       <c r="C6" t="n">
-        <v>3.923326632076242</v>
+        <v>3.385360186433201</v>
       </c>
       <c r="D6" t="n">
-        <v>4.711104040140299</v>
+        <v>4.27301684297642</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9752301117087762</v>
+        <v>1.097245766681572</v>
       </c>
       <c r="F6" t="n">
-        <v>0.352446749845946</v>
+        <v>0.2982521127751773</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
@@ -8389,19 +8799,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7346455089732102</v>
+        <v>0.7555772171721831</v>
       </c>
       <c r="C7" t="n">
-        <v>3.954320239879236</v>
+        <v>3.462406526066306</v>
       </c>
       <c r="D7" t="n">
-        <v>4.688965748852446</v>
+        <v>4.217983743238489</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9038702633420962</v>
+        <v>0.9188684804379076</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3873202846996188</v>
+        <v>0.3797944849178694</v>
       </c>
       <c r="G7" t="b">
         <v>0</v>
@@ -8410,23 +8820,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4683466960329001</v>
+        <v>0.4561581680526841</v>
       </c>
       <c r="C8" t="n">
-        <v>4.187718996766567</v>
+        <v>3.63706763805268</v>
       </c>
       <c r="D8" t="n">
-        <v>4.656065692799467</v>
+        <v>4.093225806105364</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5627464232490966</v>
+        <v>0.5404307814737639</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5860016432428774</v>
+        <v>0.60072863057245</v>
       </c>
       <c r="G8" t="b">
         <v>0</v>
@@ -8435,23 +8845,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3822469463972658</v>
+        <v>0.3668912104231192</v>
       </c>
       <c r="C9" t="n">
-        <v>4.159886068048537</v>
+        <v>3.75028856507378</v>
       </c>
       <c r="D9" t="n">
-        <v>4.542133014445803</v>
+        <v>4.117179775496899</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4568833970764342</v>
+        <v>-0.4324481625181414</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6575186378565503</v>
+        <v>0.6745928089152555</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
@@ -8460,23 +8870,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.3351692783081432</v>
+        <v>0.3605710990936242</v>
       </c>
       <c r="C10" t="n">
-        <v>4.243209587485215</v>
+        <v>3.752921944794402</v>
       </c>
       <c r="D10" t="n">
-        <v>4.578378865793359</v>
+        <v>4.113493043888027</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3996504554975298</v>
+        <v>-0.4248630910836123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6978167086547643</v>
+        <v>0.6799331366265443</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
@@ -8489,19 +8899,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2141999094016382</v>
+        <v>0.2200288563198964</v>
       </c>
       <c r="C11" t="n">
-        <v>4.293613491196259</v>
+        <v>3.811481212616789</v>
       </c>
       <c r="D11" t="n">
-        <v>4.507813400597898</v>
+        <v>4.031510068936686</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.254210371272262</v>
+        <v>-0.257805070140035</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8044838351360291</v>
+        <v>0.8017851082142466</v>
       </c>
       <c r="G11" t="b">
         <v>0</v>
@@ -8580,19 +8990,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.888137752299858</v>
+        <v>1.869744123465559</v>
       </c>
       <c r="E2" t="n">
-        <v>5.01307841869041</v>
+        <v>4.416031656505188</v>
       </c>
       <c r="F2" t="n">
-        <v>3.591091167620622</v>
+        <v>3.117758292417675</v>
       </c>
       <c r="G2" t="n">
-        <v>3.196825441000129</v>
+        <v>2.698245873051876</v>
       </c>
       <c r="H2" t="n">
-        <v>5.551113694530057</v>
+        <v>5.13946075589548</v>
       </c>
     </row>
     <row r="3">
@@ -8612,19 +9022,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.710314859511657</v>
+        <v>1.73762092182924</v>
       </c>
       <c r="E3" t="n">
-        <v>5.350262970668549</v>
+        <v>4.896313711165032</v>
       </c>
       <c r="F3" t="n">
-        <v>3.02369175268636</v>
+        <v>2.506468402667156</v>
       </c>
       <c r="G3" t="n">
-        <v>4.063789462543232</v>
+        <v>3.597757151718144</v>
       </c>
       <c r="H3" t="n">
-        <v>5.157847963584357</v>
+        <v>4.683153686878747</v>
       </c>
     </row>
     <row r="4">
@@ -8644,19 +9054,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.498035545396457</v>
+        <v>1.465403083546873</v>
       </c>
       <c r="E4" t="n">
-        <v>5.127777828886021</v>
+        <v>4.61597053915373</v>
       </c>
       <c r="F4" t="n">
-        <v>3.172015180541379</v>
+        <v>2.69336385067469</v>
       </c>
       <c r="G4" t="n">
-        <v>4.094503781739149</v>
+        <v>3.641869755458656</v>
       </c>
       <c r="H4" t="n">
-        <v>5.13481222418742</v>
+        <v>4.650069234073363</v>
       </c>
     </row>
     <row r="5">
@@ -8676,19 +9086,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.335955457433486</v>
+        <v>-1.327546204834767</v>
       </c>
       <c r="E5" t="n">
-        <v>3.849698616659241</v>
+        <v>3.314713045112578</v>
       </c>
       <c r="F5" t="n">
-        <v>5.193643743559618</v>
+        <v>4.646013043071659</v>
       </c>
       <c r="G5" t="n">
-        <v>4.946556589890335</v>
+        <v>4.50937475148609</v>
       </c>
       <c r="H5" t="n">
-        <v>3.618590801923741</v>
+        <v>3.185582339775636</v>
       </c>
     </row>
     <row r="6">
@@ -8708,51 +9118,51 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.174163240425035</v>
+        <v>1.15812971707802</v>
       </c>
       <c r="E6" t="n">
-        <v>3.919124520605959</v>
+        <v>3.403964151598467</v>
       </c>
       <c r="F6" t="n">
-        <v>3.675427794659905</v>
+        <v>3.217475313715672</v>
       </c>
       <c r="G6" t="n">
-        <v>3.615901428079372</v>
+        <v>3.12264031479486</v>
       </c>
       <c r="H6" t="n">
-        <v>5.720531182983388</v>
+        <v>5.252410911068105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AR*PRESSURE</t>
+          <t>PRESSURE*SPACE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.076771843012602</v>
+        <v>1.134392850644566</v>
       </c>
       <c r="E7" t="n">
-        <v>3.682842096094244</v>
+        <v>3.741358725575488</v>
       </c>
       <c r="F7" t="n">
-        <v>6.089798704101537</v>
+        <v>2.896101679199963</v>
       </c>
       <c r="G7" t="n">
-        <v>3.706518492705978</v>
+        <v>3.567540246370809</v>
       </c>
       <c r="H7" t="n">
-        <v>3.959931414688067</v>
+        <v>4.991068901284415</v>
       </c>
     </row>
     <row r="8">
@@ -8772,94 +9182,94 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.025943472619209</v>
+        <v>1.110407082784057</v>
       </c>
       <c r="E8" t="n">
-        <v>4.76039956597335</v>
+        <v>4.274433815714797</v>
       </c>
       <c r="F8" t="n">
-        <v>3.114577764414979</v>
+        <v>2.637162204304785</v>
       </c>
       <c r="G8" t="n">
-        <v>4.586509777350212</v>
+        <v>4.006199196003513</v>
       </c>
       <c r="H8" t="n">
-        <v>4.992574921030258</v>
+        <v>4.589741750161616</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PRESSURE*SPACE</t>
+          <t>AR*TIME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.007819440079807</v>
+        <v>1.009449209398034</v>
       </c>
       <c r="E9" t="n">
-        <v>4.158743303284389</v>
+        <v>5.575691309755948</v>
       </c>
       <c r="F9" t="n">
-        <v>3.389251021245882</v>
+        <v>3.985690929817977</v>
       </c>
       <c r="G9" t="n">
-        <v>4.160647911224636</v>
+        <v>3.144838752657533</v>
       </c>
       <c r="H9" t="n">
-        <v>5.406794509345743</v>
+        <v>3.57373679151563</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TIME*RF_POWER</t>
+          <t>AR*PRESSURE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-1.001050082302559</v>
+        <v>-0.9728018788257007</v>
       </c>
       <c r="E10" t="n">
-        <v>3.404453121355432</v>
+        <v>3.267510108623447</v>
       </c>
       <c r="F10" t="n">
-        <v>5.360996028751977</v>
+        <v>5.524478397239645</v>
       </c>
       <c r="G10" t="n">
-        <v>4.269242305890114</v>
+        <v>3.21200075716799</v>
       </c>
       <c r="H10" t="n">
-        <v>4.223685048681541</v>
+        <v>3.523365288132787</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AR*TIME</t>
+          <t>HE*TIME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -8868,30 +9278,30 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9751058478614618</v>
+        <v>0.9623113396030629</v>
       </c>
       <c r="E11" t="n">
-        <v>6.03847877820013</v>
+        <v>4.173690808949111</v>
       </c>
       <c r="F11" t="n">
-        <v>4.519374249364279</v>
+        <v>2.704324208815243</v>
       </c>
       <c r="G11" t="n">
-        <v>3.604978924188844</v>
+        <v>4.079505753195424</v>
       </c>
       <c r="H11" t="n">
-        <v>4.036086091075918</v>
+        <v>4.534761832267682</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>O2*RF_POWER</t>
+          <t>TIME*RF_POWER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8900,19 +9310,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9714096912814376</v>
+        <v>-0.9385346808974315</v>
       </c>
       <c r="E12" t="n">
-        <v>4.876749401097483</v>
+        <v>2.927950289029774</v>
       </c>
       <c r="F12" t="n">
-        <v>4.50894322060079</v>
+        <v>4.90999943314165</v>
       </c>
       <c r="G12" t="n">
-        <v>3.287711452728748</v>
+        <v>3.690300118035486</v>
       </c>
       <c r="H12" t="n">
-        <v>4.862724654794931</v>
+        <v>3.795279900352499</v>
       </c>
     </row>
     <row r="13">
@@ -8932,83 +9342,83 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.9416144646804214</v>
+        <v>0.9273122048799862</v>
       </c>
       <c r="E13" t="n">
-        <v>5.09923454288001</v>
+        <v>4.500334126060046</v>
       </c>
       <c r="F13" t="n">
-        <v>4.360619792745772</v>
+        <v>3.855598989106681</v>
       </c>
       <c r="G13" t="n">
-        <v>3.533653751494221</v>
+        <v>3.061556646047769</v>
       </c>
       <c r="H13" t="n">
-        <v>4.678267930720826</v>
+        <v>4.271445918854377</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HE*TIME</t>
+          <t>C3H6*PRESSURE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.9234651789042083</v>
+        <v>0.9181463203781859</v>
       </c>
       <c r="E14" t="n">
-        <v>4.60809021319765</v>
+        <v>3.174995804247067</v>
       </c>
       <c r="F14" t="n">
-        <v>3.216117332932112</v>
+        <v>3.275285879695794</v>
       </c>
       <c r="G14" t="n">
-        <v>4.558571300857165</v>
+        <v>3.273676960085577</v>
       </c>
       <c r="H14" t="n">
-        <v>5.013528778400043</v>
+        <v>5.210259676290676</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C3H6*PRESSURE</t>
+          <t>O2*RF_POWER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.894070083287595</v>
+        <v>0.8972327448090491</v>
       </c>
       <c r="E15" t="n">
-        <v>3.643322018973752</v>
+        <v>4.219990954048744</v>
       </c>
       <c r="F15" t="n">
-        <v>3.799769762500844</v>
+        <v>4.042494437114216</v>
       </c>
       <c r="G15" t="n">
-        <v>3.732865210786306</v>
+        <v>2.828939674689506</v>
       </c>
       <c r="H15" t="n">
-        <v>5.677453120888588</v>
+        <v>4.445908647373075</v>
       </c>
     </row>
     <row r="16">
@@ -9028,19 +9438,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.7916498269983689</v>
+        <v>-0.8069942415765905</v>
       </c>
       <c r="E16" t="n">
-        <v>2.755007505884233</v>
+        <v>2.25073793605551</v>
       </c>
       <c r="F16" t="n">
-        <v>4.753862062542571</v>
+        <v>4.270185586073503</v>
       </c>
       <c r="G16" t="n">
-        <v>4.451505804474389</v>
+        <v>3.98629279074431</v>
       </c>
       <c r="H16" t="n">
-        <v>4.867060707135989</v>
+        <v>4.391751957609123</v>
       </c>
     </row>
     <row r="17">
@@ -9060,121 +9470,121 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.7810828241950083</v>
+        <v>0.7882497566072209</v>
       </c>
       <c r="E17" t="n">
-        <v>5.264106846478948</v>
+        <v>4.812011241610174</v>
       </c>
       <c r="F17" t="n">
-        <v>4.003617770010529</v>
+        <v>3.511175953821027</v>
       </c>
       <c r="G17" t="n">
-        <v>4.121226878669632</v>
+        <v>3.653958798088049</v>
       </c>
       <c r="H17" t="n">
-        <v>4.42290345059123</v>
+        <v>3.929623023513344</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HE*PRESSURE</t>
+          <t>C3H6*O2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.7753452665899472</v>
+        <v>0.7729441187750818</v>
       </c>
       <c r="E18" t="n">
-        <v>3.596282551251624</v>
+        <v>3.977650106492667</v>
       </c>
       <c r="F18" t="n">
-        <v>3.890655774229463</v>
+        <v>2.740183011532061</v>
       </c>
       <c r="G18" t="n">
-        <v>3.764224855934391</v>
+        <v>4.2040550021516</v>
       </c>
       <c r="H18" t="n">
-        <v>5.609288612092124</v>
+        <v>4.512476144741158</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N2*SPACE</t>
+          <t>HE*PRESSURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.6818016753688863</v>
+        <v>0.7589657405492372</v>
       </c>
       <c r="E19" t="n">
-        <v>3.230908713074379</v>
+        <v>3.121207600171839</v>
       </c>
       <c r="F19" t="n">
-        <v>4.436594591082474</v>
+        <v>3.405979681333424</v>
       </c>
       <c r="G19" t="n">
-        <v>4.779204304697976</v>
+        <v>3.309535762802395</v>
       </c>
       <c r="H19" t="n">
-        <v>4.621286831968299</v>
+        <v>5.112239325062454</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C3H6*O2</t>
+          <t>AR*C3H6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>C3H6</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>O2</t>
-        </is>
-      </c>
       <c r="D20" t="n">
-        <v>0.6691246853549533</v>
+        <v>0.6595274552012158</v>
       </c>
       <c r="E20" t="n">
-        <v>4.471761195604723</v>
+        <v>4.420736324166404</v>
       </c>
       <c r="F20" t="n">
-        <v>3.247476978080197</v>
+        <v>4.755660920211007</v>
       </c>
       <c r="G20" t="n">
-        <v>4.778935357595963</v>
+        <v>2.444792199749569</v>
       </c>
       <c r="H20" t="n">
-        <v>4.892900510781344</v>
+        <v>4.098771706196604</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N2*O2</t>
+          <t>N2*SPACE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9184,34 +9594,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.622495005215745</v>
+        <v>-0.6388290184543728</v>
       </c>
       <c r="E21" t="n">
-        <v>3.783545388073142</v>
+        <v>2.72458655300755</v>
       </c>
       <c r="F21" t="n">
-        <v>4.068170141083299</v>
+        <v>3.954286508105476</v>
       </c>
       <c r="G21" t="n">
-        <v>5.237745895950351</v>
+        <v>4.2453883614161</v>
       </c>
       <c r="H21" t="n">
-        <v>4.277380638529018</v>
+        <v>4.19743027960528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPACE*TIME</t>
+          <t>PRESSURE*TIME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9220,19 +9630,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.6158524403220875</v>
+        <v>-0.5986708030319663</v>
       </c>
       <c r="E22" t="n">
-        <v>3.919874405666069</v>
+        <v>3.012252758584631</v>
       </c>
       <c r="F22" t="n">
-        <v>4.319893842970182</v>
+        <v>3.382172323860534</v>
       </c>
       <c r="G22" t="n">
-        <v>5.017381839211552</v>
+        <v>4.853797786771744</v>
       </c>
       <c r="H22" t="n">
-        <v>4.18569639587149</v>
+        <v>4.026375745983714</v>
       </c>
     </row>
     <row r="23">
@@ -9252,51 +9662,51 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.5941424872756316</v>
+        <v>0.5824550666540644</v>
       </c>
       <c r="E23" t="n">
-        <v>4.224896531870488</v>
+        <v>3.757799262786316</v>
       </c>
       <c r="F23" t="n">
-        <v>4.69642464641617</v>
+        <v>4.213983939703598</v>
       </c>
       <c r="G23" t="n">
-        <v>3.345148868855148</v>
+        <v>2.885141321059411</v>
       </c>
       <c r="H23" t="n">
-        <v>5.004961957952093</v>
+        <v>4.506236131284822</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PRESSURE*TIME</t>
+          <t>N2*O2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.5490058050954789</v>
+        <v>-0.5208942991974714</v>
       </c>
       <c r="E24" t="n">
-        <v>3.490609245545032</v>
+        <v>3.29827250790175</v>
       </c>
       <c r="F24" t="n">
-        <v>3.834673726405452</v>
+        <v>3.571829204842677</v>
       </c>
       <c r="G24" t="n">
-        <v>5.303558612625577</v>
+        <v>4.656973401212212</v>
       </c>
       <c r="H24" t="n">
-        <v>4.549611483295038</v>
+        <v>3.888741499758196</v>
       </c>
     </row>
     <row r="25">
@@ -9316,153 +9726,153 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-0.5392944588278294</v>
+        <v>-0.5098513210773767</v>
       </c>
       <c r="E25" t="n">
-        <v>3.144752588884778</v>
+        <v>2.640284083452693</v>
       </c>
       <c r="F25" t="n">
-        <v>4.191675749140694</v>
+        <v>3.726595359146188</v>
       </c>
       <c r="G25" t="n">
-        <v>4.836641720824377</v>
+        <v>4.301590007786005</v>
       </c>
       <c r="H25" t="n">
-        <v>4.804975963424634</v>
+        <v>4.368198641324747</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AR*C3H6</t>
+          <t>SPACE*TIME</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.5138524450929556</v>
+        <v>-0.5032605759605753</v>
       </c>
       <c r="E26" t="n">
-        <v>4.84695911081597</v>
+        <v>3.494313210358194</v>
       </c>
       <c r="F26" t="n">
-        <v>5.313720694287053</v>
+        <v>3.732237256515671</v>
       </c>
       <c r="G26" t="n">
-        <v>2.997345034606032</v>
+        <v>4.532424152256035</v>
       </c>
       <c r="H26" t="n">
-        <v>4.491811508263027</v>
+        <v>3.763827046492361</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AR*O2</t>
+          <t>N2*PRESSURE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.506188952443791</v>
+        <v>0.4872687835875193</v>
       </c>
       <c r="E27" t="n">
-        <v>5.787450350411592</v>
+        <v>3.104767062961011</v>
       </c>
       <c r="F27" t="n">
-        <v>4.686726534556638</v>
+        <v>3.700832834803169</v>
       </c>
       <c r="G27" t="n">
-        <v>3.901809254391384</v>
+        <v>3.320496120942947</v>
       </c>
       <c r="H27" t="n">
-        <v>3.813463343424012</v>
+        <v>4.891099459960144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NF3*RF_POWER</t>
+          <t>AR*O2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.4831492436443576</v>
+        <v>0.4538546140955766</v>
       </c>
       <c r="E28" t="n">
-        <v>3.697389263883541</v>
+        <v>5.179711724650963</v>
       </c>
       <c r="F28" t="n">
-        <v>5.048096158407469</v>
+        <v>4.249677319887968</v>
       </c>
       <c r="G28" t="n">
-        <v>4.07395154420471</v>
+        <v>3.402680590046069</v>
       </c>
       <c r="H28" t="n">
-        <v>4.458359951439922</v>
+        <v>3.380355413474228</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AR*SPACE</t>
+          <t>N2*C3H6</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.4711549402265098</v>
+        <v>-0.4498809038548344</v>
       </c>
       <c r="E29" t="n">
-        <v>5.25194731630873</v>
+        <v>2.444243380996248</v>
       </c>
       <c r="F29" t="n">
-        <v>5.043728557291879</v>
+        <v>4.141181956113011</v>
       </c>
       <c r="G29" t="n">
-        <v>3.431845235875075</v>
+        <v>3.762454161863006</v>
       </c>
       <c r="H29" t="n">
-        <v>4.165936357311244</v>
+        <v>4.5596309292701</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AR*HE</t>
+          <t>AR*SPACE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9472,221 +9882,221 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-0.4287695982084019</v>
+        <v>0.4167427142901088</v>
       </c>
       <c r="E30" t="n">
-        <v>4.218345130197106</v>
+        <v>4.663077171722481</v>
       </c>
       <c r="F30" t="n">
-        <v>5.732796681366295</v>
+        <v>4.594100355173622</v>
       </c>
       <c r="G30" t="n">
-        <v>3.475947388265809</v>
+        <v>2.953061282272813</v>
       </c>
       <c r="H30" t="n">
-        <v>4.132859743018194</v>
+        <v>3.717569894304171</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>N2*PRESSURE</t>
+          <t>NF3*RF_POWER</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.4170664669499813</v>
+        <v>-0.408405047297868</v>
       </c>
       <c r="E31" t="n">
-        <v>3.530129322665525</v>
+        <v>3.213970038346892</v>
       </c>
       <c r="F31" t="n">
-        <v>4.237114184688377</v>
+        <v>4.576536755996547</v>
       </c>
       <c r="G31" t="n">
-        <v>3.808327008325124</v>
+        <v>3.499620285157407</v>
       </c>
       <c r="H31" t="n">
-        <v>5.349444804247939</v>
+        <v>4.045376908211326</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>N2*C3H6</t>
+          <t>AR*NF3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.3805581635796111</v>
+        <v>0.4024852481496644</v>
       </c>
       <c r="E32" t="n">
-        <v>3.00842357129185</v>
+        <v>5.059056756827467</v>
       </c>
       <c r="F32" t="n">
-        <v>4.584918018937493</v>
+        <v>4.330113965103632</v>
       </c>
       <c r="G32" t="n">
-        <v>4.223035394288778</v>
+        <v>3.346478943676164</v>
       </c>
       <c r="H32" t="n">
-        <v>5.038413514775198</v>
+        <v>3.422506648251657</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>C3H6*TIME</t>
+          <t>HE*RF_POWER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.3674251061573741</v>
+        <v>0.3958111016350989</v>
       </c>
       <c r="E33" t="n">
-        <v>4.178825053076614</v>
+        <v>3.020464593406153</v>
       </c>
       <c r="F33" t="n">
-        <v>3.442767739765603</v>
+        <v>3.473141685843881</v>
       </c>
       <c r="G33" t="n">
-        <v>4.844748074271188</v>
+        <v>3.628623915117899</v>
       </c>
       <c r="H33" t="n">
-        <v>4.843540973274925</v>
+        <v>4.872923210825825</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AR*NF3</t>
+          <t>C3H6*TIME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.3193845196257885</v>
+        <v>0.3623729903128916</v>
       </c>
       <c r="E34" t="n">
-        <v>5.502975744097268</v>
+        <v>3.691630357175548</v>
       </c>
       <c r="F34" t="n">
-        <v>4.876376272099521</v>
+        <v>2.93086284441014</v>
       </c>
       <c r="G34" t="n">
-        <v>3.844371838264983</v>
+        <v>4.400879387711133</v>
       </c>
       <c r="H34" t="n">
-        <v>3.856541405518813</v>
+        <v>4.364857855571509</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NF3*SPACE</t>
+          <t>AR*N2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.2966013745546872</v>
+        <v>0.3305897261317927</v>
       </c>
       <c r="E35" t="n">
-        <v>4.072587179094788</v>
+        <v>4.422465094212991</v>
       </c>
       <c r="F35" t="n">
-        <v>4.797964214933303</v>
+        <v>4.754508406846615</v>
       </c>
       <c r="G35" t="n">
-        <v>4.218085327351036</v>
+        <v>2.822367480635183</v>
       </c>
       <c r="H35" t="n">
-        <v>4.350259614080177</v>
+        <v>3.815590245532393</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PRESSURE*RF_POWER</t>
+          <t>AR*HE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.267914674444055</v>
+        <v>-0.3252913575583356</v>
       </c>
       <c r="E36" t="n">
-        <v>3.014708038354888</v>
+        <v>3.784144661551927</v>
       </c>
       <c r="F36" t="n">
-        <v>4.151941197865549</v>
+        <v>5.180055361953991</v>
       </c>
       <c r="G36" t="n">
-        <v>4.529072361223811</v>
+        <v>2.964021640413364</v>
       </c>
       <c r="H36" t="n">
-        <v>5.130476171846362</v>
+        <v>3.709349625698756</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>O2*TIME</t>
+          <t>O2*PRESSURE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -9696,279 +10106,279 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-0.2424208231455198</v>
+        <v>0.2323439134949081</v>
       </c>
       <c r="E37" t="n">
-        <v>4.69424633738725</v>
+        <v>3.59505621712388</v>
       </c>
       <c r="F37" t="n">
-        <v>4.630611929740945</v>
+        <v>4.459117595064124</v>
       </c>
       <c r="G37" t="n">
-        <v>4.501133884730764</v>
+        <v>2.993636684834368</v>
       </c>
       <c r="H37" t="n">
-        <v>3.952657830793418</v>
+        <v>4.322385889764428</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AR*N2</t>
+          <t>PRESSURE*RF_POWER</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>PRESSURE</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.2360255731304457</v>
+        <v>-0.2027194429961314</v>
       </c>
       <c r="E38" t="n">
-        <v>4.874361763478404</v>
+        <v>2.53840414163259</v>
       </c>
       <c r="F38" t="n">
-        <v>5.295452259178764</v>
+        <v>3.698071401828561</v>
       </c>
       <c r="G38" t="n">
-        <v>3.340959224146457</v>
+        <v>3.949997549633608</v>
       </c>
       <c r="H38" t="n">
-        <v>4.234100866107708</v>
+        <v>4.704225923837315</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HE*RF_POWER</t>
+          <t>C3H6*NF3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.2295839155525585</v>
+        <v>0.1606036739304395</v>
       </c>
       <c r="E39" t="n">
-        <v>3.443973198475924</v>
+        <v>3.461015553564185</v>
       </c>
       <c r="F39" t="n">
-        <v>3.992195342746596</v>
+        <v>3.084606046817715</v>
       </c>
       <c r="G39" t="n">
-        <v>4.242895587809787</v>
+        <v>4.411839745851686</v>
       </c>
       <c r="H39" t="n">
-        <v>5.250285563185576</v>
+        <v>4.356637586966094</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>N2*RF_POWER</t>
+          <t>HE*NF3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>N2</t>
+          <t>HE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-0.2281105851804135</v>
+        <v>0.1480854913815821</v>
       </c>
       <c r="E40" t="n">
-        <v>3.307644180882996</v>
+        <v>3.510753747569022</v>
       </c>
       <c r="F40" t="n">
-        <v>4.385437612543395</v>
+        <v>3.146282249735302</v>
       </c>
       <c r="G40" t="n">
-        <v>4.333781599538406</v>
+        <v>4.378680949848461</v>
       </c>
       <c r="H40" t="n">
-        <v>4.955353860837977</v>
+        <v>4.310380434777905</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>O2*PRESSURE</t>
+          <t>NF3*SPACE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>O2</t>
+          <t>NF3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PRESSURE</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.1615981321243229</v>
+        <v>-0.1477729392051474</v>
       </c>
       <c r="E41" t="n">
-        <v>4.072183758441769</v>
+        <v>3.657056256020629</v>
       </c>
       <c r="F41" t="n">
-        <v>5.0453203157046</v>
+        <v>4.281145944214056</v>
       </c>
       <c r="G41" t="n">
-        <v>3.446957384474294</v>
+        <v>3.623741892740714</v>
       </c>
       <c r="H41" t="n">
-        <v>4.743290205985771</v>
+        <v>3.952285702523845</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>C3H6*SPACE</t>
+          <t>N2*RF_POWER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>N2</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SPACE</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-0.1488112831105759</v>
+        <v>-0.1303194227579081</v>
       </c>
       <c r="E42" t="n">
-        <v>3.383621486503097</v>
+        <v>2.824423890949709</v>
       </c>
       <c r="F42" t="n">
-        <v>3.972903450814613</v>
+        <v>3.887728282810704</v>
       </c>
       <c r="G42" t="n">
-        <v>4.67739578907883</v>
+        <v>3.759317716755529</v>
       </c>
       <c r="H42" t="n">
-        <v>4.969055187169194</v>
+        <v>4.561983263100708</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HE*NF3</t>
+          <t>AR*RF_POWER</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HE</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>RF_POWER</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>0.1451178288081578</v>
+        <v>-0.1180221074686589</v>
       </c>
       <c r="E43" t="n">
-        <v>3.986027634252169</v>
+        <v>4.026485509108005</v>
       </c>
       <c r="F43" t="n">
-        <v>3.630825718895766</v>
+        <v>5.018494796916606</v>
       </c>
       <c r="G43" t="n">
-        <v>4.855670578161717</v>
+        <v>2.957943304649998</v>
       </c>
       <c r="H43" t="n">
-        <v>4.79070432042163</v>
+        <v>3.713908377521282</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>C3H6*NF3</t>
+          <t>O2*TIME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>C3H6</t>
+          <t>O2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NF3</t>
+          <t>TIME</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0.1266966465031876</v>
+        <v>-0.1161675295972757</v>
       </c>
       <c r="E44" t="n">
-        <v>3.93625816150186</v>
+        <v>4.257993278503968</v>
       </c>
       <c r="F44" t="n">
-        <v>3.604479000815438</v>
+        <v>4.017159554144065</v>
       </c>
       <c r="G44" t="n">
-        <v>4.888850226661922</v>
+        <v>4.02330410682552</v>
       </c>
       <c r="H44" t="n">
-        <v>4.810464358981875</v>
+        <v>3.550135323271065</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AR*RF_POWER</t>
+          <t>C3H6*SPACE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>C3H6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>RF_POWER</t>
+          <t>SPACE</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-0.07439902152395006</v>
+        <v>-0.07688955046383517</v>
       </c>
       <c r="E45" t="n">
-        <v>4.623333335689866</v>
+        <v>2.887329598669986</v>
       </c>
       <c r="F45" t="n">
-        <v>5.462804544371122</v>
+        <v>3.467063350080515</v>
       </c>
       <c r="G45" t="n">
-        <v>3.456655496333826</v>
+        <v>4.136892997641143</v>
       </c>
       <c r="H45" t="n">
-        <v>4.147328661967181</v>
+        <v>4.562847648124001</v>
       </c>
     </row>
     <row r="46">
@@ -9988,19 +10398,19 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>0.03254993546651397</v>
+        <v>0.07000546601097524</v>
       </c>
       <c r="E46" t="n">
-        <v>3.268124103762505</v>
+        <v>2.731909586573329</v>
       </c>
       <c r="F46" t="n">
-        <v>4.049901705975009</v>
+        <v>3.570676691478285</v>
       </c>
       <c r="G46" t="n">
-        <v>4.360128317618734</v>
+        <v>3.820993919673116</v>
       </c>
       <c r="H46" t="n">
-        <v>5.207005790764266</v>
+        <v>4.799771956600022</v>
       </c>
     </row>
   </sheetData>
